--- a/Engagement Rankings 2026-08.xlsx
+++ b/Engagement Rankings 2026-08.xlsx
@@ -1094,7 +1094,7 @@
         <v>26</v>
       </c>
       <c r="C50">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D50">
         <v>28</v>
@@ -14759,7 +14759,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -14831,9 +14831,23 @@
         <v>1</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>kelly_ottoni</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-08.xlsx
+++ b/Engagement Rankings 2026-08.xlsx
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C6">
         <v>17</v>
       </c>
       <c r="D6">
-        <v>758</v>
+        <v>759</v>
       </c>
     </row>
     <row r="7">
@@ -1004,30 +1004,30 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>n.daily22</v>
+        <v>leonardomesquitamma</v>
       </c>
       <c r="B44">
         <v>35</v>
       </c>
       <c r="C44">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D44">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>leonardomesquitamma</v>
+        <v>n.daily22</v>
       </c>
       <c r="B45">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D45">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46">
@@ -14759,7 +14759,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -14777,10 +14777,10 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>combintel</v>
+        <v>quemuel_ottoni</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -14791,7 +14791,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>masonharper_mma</v>
+        <v>combintel</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -14805,7 +14805,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>quemuel_ottoni</v>
+        <v>masonharper_mma</v>
       </c>
       <c r="B4">
         <v>1</v>
@@ -14814,40 +14814,54 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>johnmma9</v>
+        <v>leonardomesquitamma</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
+        <v>johnmma9</v>
+      </c>
+      <c r="B6">
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
         <v>kelly_ottoni</v>
       </c>
-      <c r="B6">
-        <v>0</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-08.xlsx
+++ b/Engagement Rankings 2026-08.xlsx
@@ -475,7 +475,7 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C6">
         <v>17</v>
@@ -786,10 +786,10 @@
         <v>33</v>
       </c>
       <c r="C28">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D28">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29">
@@ -1094,7 +1094,7 @@
         <v>26</v>
       </c>
       <c r="C50">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D50">
         <v>28</v>
@@ -15571,7 +15571,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D73"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -15592,7 +15592,7 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -16177,21 +16177,21 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>blogfabiocosta</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B44">
         <v>0</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D44">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>leo_sousa_cabeleleiro</v>
+        <v>blogfabiocosta</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -16205,7 +16205,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>markiim_guerreiro</v>
+        <v>leo_sousa_cabeleleiro</v>
       </c>
       <c r="B46">
         <v>0</v>
@@ -16219,7 +16219,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>mvp_lutas</v>
+        <v>markiim_guerreiro</v>
       </c>
       <c r="B47">
         <v>0</v>
@@ -16233,7 +16233,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>kelly_ottoni</v>
+        <v>mvp_lutas</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -16242,12 +16242,12 @@
         <v>1</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>fe.souza89</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B49">
         <v>0</v>
@@ -16256,12 +16256,12 @@
         <v>1</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>fe.souza89</v>
       </c>
       <c r="B50">
         <v>0</v>
@@ -16275,7 +16275,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>yuri.t.bechelli</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -16289,7 +16289,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>wellington_silva_1995</v>
+        <v>yuri.t.bechelli</v>
       </c>
       <c r="B52">
         <v>0</v>
@@ -16303,7 +16303,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>ricardolopes4921</v>
+        <v>wellington_silva_1995</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -16317,7 +16317,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>nicollebertolinie</v>
+        <v>ricardolopes4921</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -16331,7 +16331,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>leticia_araujo447</v>
+        <v>nicollebertolinie</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -16345,7 +16345,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>__paulaprada__</v>
+        <v>leticia_araujo447</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -16359,7 +16359,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>alexandresagat.oficial</v>
+        <v>__paulaprada__</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -16373,7 +16373,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>annamarya_silveira</v>
+        <v>alexandresagat.oficial</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -16387,7 +16387,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>sousamaevia</v>
+        <v>annamarya_silveira</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -16401,7 +16401,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>eneido_neto</v>
+        <v>sousamaevia</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -16415,7 +16415,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>genillsson_177</v>
+        <v>eneido_neto</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -16429,7 +16429,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>alesiqueira_personal</v>
+        <v>genillsson_177</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -16443,7 +16443,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>anaclaudialc73</v>
+        <v>alesiqueira_personal</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -16457,7 +16457,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>fernandohf32</v>
+        <v>anaclaudialc73</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -16471,7 +16471,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>gleydeolyveeira</v>
+        <v>fernandohf32</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -16485,7 +16485,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>rbueno81</v>
+        <v>gleydeolyveeira</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -16499,7 +16499,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>rafamakita</v>
+        <v>rbueno81</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -16513,7 +16513,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>biia_sousah</v>
+        <v>rafamakita</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -16527,7 +16527,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>ronygoto</v>
+        <v>biia_sousah</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -16541,7 +16541,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>igorpatrao</v>
+        <v>ronygoto</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -16555,7 +16555,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>fideles8080</v>
+        <v>igorpatrao</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -16569,21 +16569,35 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
+        <v>fideles8080</v>
+      </c>
+      <c r="B72">
+        <v>0</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
         <v>nadiabarakkat</v>
       </c>
-      <c r="B72">
-        <v>0</v>
-      </c>
-      <c r="C72">
-        <v>1</v>
-      </c>
-      <c r="D72">
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>1</v>
+      </c>
+      <c r="D73">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D72"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D73"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-08.xlsx
+++ b/Engagement Rankings 2026-08.xlsx
@@ -1976,7 +1976,7 @@
         <v>7</v>
       </c>
       <c r="C113">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D113">
         <v>4</v>
@@ -15613,7 +15613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D90"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -16861,9 +16861,23 @@
         <v>0</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="str">
+        <v>_oliveira09_</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D89"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D90"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-08.xlsx
+++ b/Engagement Rankings 2026-08.xlsx
@@ -433,13 +433,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>3683</v>
+        <v>3684</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>1562</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="4">
@@ -1094,7 +1094,7 @@
         <v>26</v>
       </c>
       <c r="C50">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D50">
         <v>28</v>
@@ -15648,13 +15648,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
+        <v>4</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>3</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -15897,13 +15897,13 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>alexandroscorreia</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -15911,7 +15911,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>lucifit50</v>
+        <v>alexandroscorreia</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -15925,7 +15925,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>martinscdione</v>
+        <v>lucifit50</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -15939,7 +15939,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>gustavotoi</v>
+        <v>martinscdione</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -15953,7 +15953,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>erivaldosilva3333</v>
+        <v>gustavotoi</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -15967,7 +15967,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>marcos_r_s_</v>
+        <v>erivaldosilva3333</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -15981,7 +15981,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>biazon87</v>
+        <v>marcos_r_s_</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -15995,7 +15995,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>moys158</v>
+        <v>biazon87</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -16009,7 +16009,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>viviane_moota</v>
+        <v>moys158</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -16023,7 +16023,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>ra.imundo8575</v>
+        <v>viviane_moota</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -16037,7 +16037,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>caio.lazzuri</v>
+        <v>ra.imundo8575</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -16051,7 +16051,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>sambagabrieloficial</v>
+        <v>caio.lazzuri</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -16065,7 +16065,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>rafaella_olliveira08</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -16079,7 +16079,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>antoniomarcos84</v>
+        <v>rafaella_olliveira08</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -16093,7 +16093,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>hipolito.netoo</v>
+        <v>antoniomarcos84</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -16107,7 +16107,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>febcm</v>
+        <v>hipolito.netoo</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -16121,7 +16121,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>gabriel_angello_</v>
+        <v>febcm</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -16135,7 +16135,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>dronearcariri</v>
+        <v>gabriel_angello_</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -16149,7 +16149,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>roncy_068</v>
+        <v>dronearcariri</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -16163,7 +16163,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>mmapalpitex</v>
+        <v>roncy_068</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -16177,7 +16177,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>gustavo_vivancos</v>
+        <v>mmapalpitex</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -16191,7 +16191,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>jo.aopedro748</v>
+        <v>gustavo_vivancos</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -16205,7 +16205,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>marcoscesarbodo</v>
+        <v>jo.aopedro748</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -16219,7 +16219,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>mardonio9549</v>
+        <v>marcoscesarbodo</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -16233,7 +16233,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>driigallinucci</v>
+        <v>mardonio9549</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -16247,7 +16247,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>araujodiana1231</v>
+        <v>driigallinucci</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -16261,7 +16261,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>mr.disciplina</v>
+        <v>araujodiana1231</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -16275,7 +16275,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>jvxz______</v>
+        <v>mr.disciplina</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -16289,7 +16289,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>carlos_hm_iglesias</v>
+        <v>jvxz______</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -16303,7 +16303,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>_franklinxavier</v>
+        <v>carlos_hm_iglesias</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -16317,7 +16317,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>claudiaottoni2025</v>
+        <v>_franklinxavier</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -16331,7 +16331,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>claudiaottoni2025</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -16345,7 +16345,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>thiagoauper</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -16359,7 +16359,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>pedromadeira.s</v>
+        <v>thiagoauper</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -16373,13 +16373,13 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>kelly_ottoni</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C55">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D55">
         <v>0</v>

--- a/Engagement Rankings 2026-08.xlsx
+++ b/Engagement Rankings 2026-08.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1086"/>
+  <dimension ref="A1:D1087"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,13 +433,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>3684</v>
+        <v>3685</v>
       </c>
       <c r="C3">
         <v>6</v>
       </c>
       <c r="D3">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="4">
@@ -1094,7 +1094,7 @@
         <v>26</v>
       </c>
       <c r="C50">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D50">
         <v>28</v>
@@ -1158,35 +1158,35 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>leandrosolano_mma</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B55">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C55">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="D55">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>figh_grappler</v>
+        <v>leandrosolano_mma</v>
       </c>
       <c r="B56">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="D56">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>galler_peace</v>
+        <v>figh_grappler</v>
       </c>
       <c r="B57">
         <v>25</v>
@@ -1200,7 +1200,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>thundergrapple</v>
+        <v>galler_peace</v>
       </c>
       <c r="B58">
         <v>25</v>
@@ -1214,16 +1214,16 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ninjatheorist</v>
+        <v>thundergrapple</v>
       </c>
       <c r="B59">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60">
@@ -2026,55 +2026,55 @@
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>cayan.pascoalbjj</v>
+        <v>aj_mma_</v>
       </c>
       <c r="B117">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C117">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D117">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>luigimoraess</v>
+        <v>cayan.pascoalbjj</v>
       </c>
       <c r="B118">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C118">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D118">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>bruno_murata</v>
+        <v>luigimoraess</v>
       </c>
       <c r="B119">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C119">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D119">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>aj_mma_</v>
+        <v>bruno_murata</v>
       </c>
       <c r="B120">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C120">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D120">
         <v>3</v>
@@ -11364,35 +11364,35 @@
     </row>
     <row r="784">
       <c r="A784" t="str">
-        <v>luizcosta_mma</v>
+        <v>pro_mmabetting</v>
       </c>
       <c r="B784">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C784">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D784">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>taylor_71kg</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B785">
         <v>0</v>
       </c>
       <c r="C785">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D785">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>_vpft</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B786">
         <v>0</v>
@@ -11406,21 +11406,21 @@
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>viniciustbf</v>
+        <v>_vpft</v>
       </c>
       <c r="B787">
         <v>0</v>
       </c>
       <c r="C787">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D787">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>dayanaa1511</v>
+        <v>viniciustbf</v>
       </c>
       <c r="B788">
         <v>0</v>
@@ -11429,40 +11429,40 @@
         <v>2</v>
       </c>
       <c r="D788">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>danielfranzesilva</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B789">
         <v>0</v>
       </c>
       <c r="C789">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D789">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>ednilsonkaicai</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B790">
         <v>0</v>
       </c>
       <c r="C790">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D790">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>vanessamelomma</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B791">
         <v>0</v>
@@ -11476,21 +11476,21 @@
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>michelle_mirele</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B792">
         <v>0</v>
       </c>
       <c r="C792">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D792">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>geyziellsouza</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B793">
         <v>0</v>
@@ -11504,21 +11504,21 @@
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>guerreirammaofc</v>
+        <v>geyziellsouza</v>
       </c>
       <c r="B794">
         <v>0</v>
       </c>
       <c r="C794">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D794">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>kalaga_vito</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B795">
         <v>0</v>
@@ -11532,13 +11532,13 @@
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>bryandazuera</v>
+        <v>kalaga_vito</v>
       </c>
       <c r="B796">
         <v>0</v>
       </c>
       <c r="C796">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D796">
         <v>1</v>
@@ -11546,7 +11546,7 @@
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>danilofernandescf</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B797">
         <v>0</v>
@@ -11560,21 +11560,21 @@
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>4lissson</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B798">
         <v>0</v>
       </c>
       <c r="C798">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D798">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>vitorshowman</v>
+        <v>4lissson</v>
       </c>
       <c r="B799">
         <v>0</v>
@@ -11588,7 +11588,7 @@
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>orlando_alfa09</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B800">
         <v>0</v>
@@ -11602,7 +11602,7 @@
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B801">
         <v>0</v>
@@ -11616,7 +11616,7 @@
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>manumito.oficial</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B802">
         <v>0</v>
@@ -11630,63 +11630,63 @@
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>coutz11</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B803">
         <v>0</v>
       </c>
       <c r="C803">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D803">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>eglaudiomma</v>
+        <v>coutz11</v>
       </c>
       <c r="B804">
         <v>0</v>
       </c>
       <c r="C804">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D804">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>lokomemo_protetores</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B805">
         <v>0</v>
       </c>
       <c r="C805">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D805">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>carlosnoelblack</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B806">
         <v>0</v>
       </c>
       <c r="C806">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D806">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>rafaelcmjj</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B807">
         <v>0</v>
@@ -11700,21 +11700,21 @@
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>rahikikhalid</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B808">
         <v>0</v>
       </c>
       <c r="C808">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D808">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>leonardopateira</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B809">
         <v>0</v>
@@ -11728,21 +11728,21 @@
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>tpapereira</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B810">
         <v>0</v>
       </c>
       <c r="C810">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D810">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>thalytabjj</v>
+        <v>tpapereira</v>
       </c>
       <c r="B811">
         <v>0</v>
@@ -11756,7 +11756,7 @@
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>rafaelantonio.rj</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B812">
         <v>0</v>
@@ -11770,35 +11770,35 @@
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>yasminreis_oficiall</v>
+        <v>rafaelantonio.rj</v>
       </c>
       <c r="B813">
         <v>0</v>
       </c>
       <c r="C813">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D813">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>armysenju</v>
+        <v>yasminreis_oficiall</v>
       </c>
       <c r="B814">
         <v>0</v>
       </c>
       <c r="C814">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D814">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>dnoxsport</v>
+        <v>armysenju</v>
       </c>
       <c r="B815">
         <v>0</v>
@@ -11812,7 +11812,7 @@
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>kamtalksmma</v>
+        <v>dnoxsport</v>
       </c>
       <c r="B816">
         <v>0</v>
@@ -11826,21 +11826,21 @@
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>arleyleboss</v>
+        <v>kamtalksmma</v>
       </c>
       <c r="B817">
         <v>0</v>
       </c>
       <c r="C817">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D817">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>janjaovix</v>
+        <v>arleyleboss</v>
       </c>
       <c r="B818">
         <v>0</v>
@@ -11854,7 +11854,7 @@
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>dra.izabeldelfino_</v>
+        <v>janjaovix</v>
       </c>
       <c r="B819">
         <v>0</v>
@@ -11868,35 +11868,35 @@
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>jj_miguel05</v>
+        <v>dra.izabeldelfino_</v>
       </c>
       <c r="B820">
         <v>0</v>
       </c>
       <c r="C820">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D820">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>jj_miguel05</v>
       </c>
       <c r="B821">
         <v>0</v>
       </c>
       <c r="C821">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D821">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>edsonbahienseb</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B822">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>paulomartins.mma</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B823">
         <v>0</v>
@@ -11924,27 +11924,27 @@
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>daniel_natel</v>
+        <v>paulomartins.mma</v>
       </c>
       <c r="B824">
         <v>0</v>
       </c>
       <c r="C824">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D824">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>dhuks11</v>
+        <v>daniel_natel</v>
       </c>
       <c r="B825">
         <v>0</v>
       </c>
       <c r="C825">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D825">
         <v>0</v>
@@ -11952,7 +11952,7 @@
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>macksomlee</v>
+        <v>dhuks11</v>
       </c>
       <c r="B826">
         <v>0</v>
@@ -11961,40 +11961,40 @@
         <v>1</v>
       </c>
       <c r="D826">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>y_nichimura</v>
+        <v>macksomlee</v>
       </c>
       <c r="B827">
         <v>0</v>
       </c>
       <c r="C827">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D827">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>patascubo</v>
+        <v>y_nichimura</v>
       </c>
       <c r="B828">
         <v>0</v>
       </c>
       <c r="C828">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D828">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>mayconzilli</v>
+        <v>patascubo</v>
       </c>
       <c r="B829">
         <v>0</v>
@@ -12008,7 +12008,7 @@
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>jeffesonmeirelles</v>
+        <v>mayconzilli</v>
       </c>
       <c r="B830">
         <v>0</v>
@@ -12022,7 +12022,7 @@
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>denilson.unit</v>
+        <v>jeffesonmeirelles</v>
       </c>
       <c r="B831">
         <v>0</v>
@@ -12036,7 +12036,7 @@
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>vieirabjj____</v>
+        <v>denilson.unit</v>
       </c>
       <c r="B832">
         <v>0</v>
@@ -12050,7 +12050,7 @@
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>bruno_pontes1992</v>
+        <v>vieirabjj____</v>
       </c>
       <c r="B833">
         <v>0</v>
@@ -12064,7 +12064,7 @@
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>leandro__parpinelli</v>
+        <v>bruno_pontes1992</v>
       </c>
       <c r="B834">
         <v>0</v>
@@ -12078,7 +12078,7 @@
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>allan10adm</v>
+        <v>leandro__parpinelli</v>
       </c>
       <c r="B835">
         <v>0</v>
@@ -12092,7 +12092,7 @@
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>gaby_alves07</v>
+        <v>allan10adm</v>
       </c>
       <c r="B836">
         <v>0</v>
@@ -12106,7 +12106,7 @@
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>blogfabiocosta</v>
+        <v>gaby_alves07</v>
       </c>
       <c r="B837">
         <v>0</v>
@@ -12120,7 +12120,7 @@
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>leo_sousa_cabeleleiro</v>
+        <v>blogfabiocosta</v>
       </c>
       <c r="B838">
         <v>0</v>
@@ -12134,7 +12134,7 @@
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>markiim_guerreiro</v>
+        <v>leo_sousa_cabeleleiro</v>
       </c>
       <c r="B839">
         <v>0</v>
@@ -12148,7 +12148,7 @@
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>roginbrito</v>
+        <v>markiim_guerreiro</v>
       </c>
       <c r="B840">
         <v>0</v>
@@ -12157,12 +12157,12 @@
         <v>1</v>
       </c>
       <c r="D840">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>raulcarvalho1010</v>
+        <v>roginbrito</v>
       </c>
       <c r="B841">
         <v>0</v>
@@ -12176,7 +12176,7 @@
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B842">
         <v>0</v>
@@ -12190,7 +12190,7 @@
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>douglas_vitor8</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B843">
         <v>0</v>
@@ -12204,7 +12204,7 @@
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>kevin.mota95</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B844">
         <v>0</v>
@@ -12218,7 +12218,7 @@
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>guilhermews1994</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B845">
         <v>0</v>
@@ -12232,7 +12232,7 @@
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>tamysregina</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B846">
         <v>0</v>
@@ -12246,7 +12246,7 @@
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>aline.amaral21</v>
+        <v>tamysregina</v>
       </c>
       <c r="B847">
         <v>0</v>
@@ -12260,7 +12260,7 @@
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>katlembrenda</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B848">
         <v>0</v>
@@ -12274,7 +12274,7 @@
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>dudu.acabamentos</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B849">
         <v>0</v>
@@ -12288,7 +12288,7 @@
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>isadoragolimpio</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B850">
         <v>0</v>
@@ -12302,7 +12302,7 @@
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>audizioandrade</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B851">
         <v>0</v>
@@ -12316,7 +12316,7 @@
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>boradepodcastoficial</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B852">
         <v>0</v>
@@ -12330,7 +12330,7 @@
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B853">
         <v>0</v>
@@ -12344,7 +12344,7 @@
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>natalves5</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B854">
         <v>0</v>
@@ -12358,7 +12358,7 @@
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>barbaracontadora</v>
+        <v>natalves5</v>
       </c>
       <c r="B855">
         <v>0</v>
@@ -12372,7 +12372,7 @@
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>vidaldanin</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B856">
         <v>0</v>
@@ -12386,7 +12386,7 @@
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>andrey_m_s_</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B857">
         <v>0</v>
@@ -12400,7 +12400,7 @@
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>deivssonmanin</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B858">
         <v>0</v>
@@ -12414,7 +12414,7 @@
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>rejr_mma</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B859">
         <v>0</v>
@@ -12428,7 +12428,7 @@
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>felipeocalmon</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B860">
         <v>0</v>
@@ -12442,7 +12442,7 @@
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>igorbrasileiro01</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B861">
         <v>0</v>
@@ -12456,7 +12456,7 @@
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>joaolauar_</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B862">
         <v>0</v>
@@ -12470,7 +12470,7 @@
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>michele_mixa</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B863">
         <v>0</v>
@@ -12484,7 +12484,7 @@
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B864">
         <v>0</v>
@@ -12498,7 +12498,7 @@
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>benicius_edu</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B865">
         <v>0</v>
@@ -12512,7 +12512,7 @@
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>andreza.thais.1</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B866">
         <v>0</v>
@@ -12526,7 +12526,7 @@
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>julckreis</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B867">
         <v>0</v>
@@ -12540,7 +12540,7 @@
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>alineanne_</v>
+        <v>julckreis</v>
       </c>
       <c r="B868">
         <v>0</v>
@@ -12554,7 +12554,7 @@
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>romulerasilva</v>
+        <v>alineanne_</v>
       </c>
       <c r="B869">
         <v>0</v>
@@ -12568,7 +12568,7 @@
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>higorsaantana</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B870">
         <v>0</v>
@@ -12582,7 +12582,7 @@
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>vitorcosta_mma</v>
+        <v>higorsaantana</v>
       </c>
       <c r="B871">
         <v>0</v>
@@ -12596,7 +12596,7 @@
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>paulo.titoo</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B872">
         <v>0</v>
@@ -12610,7 +12610,7 @@
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>1000ton_n</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B873">
         <v>0</v>
@@ -12624,7 +12624,7 @@
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>anamatias.m</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B874">
         <v>0</v>
@@ -12638,7 +12638,7 @@
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>taporondebruno</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B875">
         <v>0</v>
@@ -12652,7 +12652,7 @@
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>ricardotofanello</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B876">
         <v>0</v>
@@ -12666,7 +12666,7 @@
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>strong_stg_oficial</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B877">
         <v>0</v>
@@ -12680,7 +12680,7 @@
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B878">
         <v>0</v>
@@ -12694,7 +12694,7 @@
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>sabrinaalsilva</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B879">
         <v>0</v>
@@ -12708,7 +12708,7 @@
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>caioparangole</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B880">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>leaoanaalice</v>
+        <v>caioparangole</v>
       </c>
       <c r="B881">
         <v>0</v>
@@ -12736,7 +12736,7 @@
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>pe.mirandas</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B882">
         <v>0</v>
@@ -12750,7 +12750,7 @@
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>doraasivla</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B883">
         <v>0</v>
@@ -12764,7 +12764,7 @@
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>doraasivla</v>
       </c>
       <c r="B884">
         <v>0</v>
@@ -12778,7 +12778,7 @@
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>cristianomarcello</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B885">
         <v>0</v>
@@ -12792,7 +12792,7 @@
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>herrickmarinho</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B886">
         <v>0</v>
@@ -12806,7 +12806,7 @@
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>kfcampeoes</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B887">
         <v>0</v>
@@ -12820,7 +12820,7 @@
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>sejamotivadorofc</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B888">
         <v>0</v>
@@ -12834,7 +12834,7 @@
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B889">
         <v>0</v>
@@ -12848,7 +12848,7 @@
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>dandraco_</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B890">
         <v>0</v>
@@ -12862,7 +12862,7 @@
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>chubotaru_lilu</v>
+        <v>dandraco_</v>
       </c>
       <c r="B891">
         <v>0</v>
@@ -12876,7 +12876,7 @@
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>esteticaluharruda</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B892">
         <v>0</v>
@@ -12890,7 +12890,7 @@
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>dadwillians</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B893">
         <v>0</v>
@@ -12904,7 +12904,7 @@
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>vanemessina</v>
+        <v>dadwillians</v>
       </c>
       <c r="B894">
         <v>0</v>
@@ -12918,7 +12918,7 @@
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>geanne_franca_</v>
+        <v>vanemessina</v>
       </c>
       <c r="B895">
         <v>0</v>
@@ -12932,7 +12932,7 @@
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>victor_brunopersonal</v>
+        <v>geanne_franca_</v>
       </c>
       <c r="B896">
         <v>0</v>
@@ -12946,7 +12946,7 @@
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>omar_alneaimi</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B897">
         <v>0</v>
@@ -12960,7 +12960,7 @@
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>jimmy_indioap</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B898">
         <v>0</v>
@@ -12974,7 +12974,7 @@
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>_kainanlima</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B899">
         <v>0</v>
@@ -12988,7 +12988,7 @@
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B900">
         <v>0</v>
@@ -13002,7 +13002,7 @@
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>leziamorbeck50</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B901">
         <v>0</v>
@@ -13016,7 +13016,7 @@
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>andrearschack</v>
+        <v>leziamorbeck50</v>
       </c>
       <c r="B902">
         <v>0</v>
@@ -13030,7 +13030,7 @@
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>martinpakciarz</v>
+        <v>andrearschack</v>
       </c>
       <c r="B903">
         <v>0</v>
@@ -13044,7 +13044,7 @@
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>rafaelbipolarufc</v>
+        <v>martinpakciarz</v>
       </c>
       <c r="B904">
         <v>0</v>
@@ -13058,7 +13058,7 @@
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>meirelesmma</v>
+        <v>rafaelbipolarufc</v>
       </c>
       <c r="B905">
         <v>0</v>
@@ -13072,7 +13072,7 @@
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>teamsilverio</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B906">
         <v>0</v>
@@ -13086,7 +13086,7 @@
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>tatiaradias</v>
+        <v>teamsilverio</v>
       </c>
       <c r="B907">
         <v>0</v>
@@ -13100,7 +13100,7 @@
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>miltoncjr28</v>
+        <v>tatiaradias</v>
       </c>
       <c r="B908">
         <v>0</v>
@@ -13114,7 +13114,7 @@
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>leafarlemos</v>
+        <v>miltoncjr28</v>
       </c>
       <c r="B909">
         <v>0</v>
@@ -13128,7 +13128,7 @@
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>thiagopssantos</v>
+        <v>leafarlemos</v>
       </c>
       <c r="B910">
         <v>0</v>
@@ -13142,7 +13142,7 @@
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>daniloacordeon_oficial</v>
+        <v>thiagopssantos</v>
       </c>
       <c r="B911">
         <v>0</v>
@@ -13156,7 +13156,7 @@
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>dorgivan13_bjj</v>
+        <v>daniloacordeon_oficial</v>
       </c>
       <c r="B912">
         <v>0</v>
@@ -13170,7 +13170,7 @@
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>ryu_artes_marciais</v>
+        <v>dorgivan13_bjj</v>
       </c>
       <c r="B913">
         <v>0</v>
@@ -13184,7 +13184,7 @@
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>marques.__bjj</v>
+        <v>ryu_artes_marciais</v>
       </c>
       <c r="B914">
         <v>0</v>
@@ -13198,7 +13198,7 @@
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>foryousaudeespecializada</v>
+        <v>marques.__bjj</v>
       </c>
       <c r="B915">
         <v>0</v>
@@ -13212,7 +13212,7 @@
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>soniarmurata</v>
+        <v>foryousaudeespecializada</v>
       </c>
       <c r="B916">
         <v>0</v>
@@ -13226,7 +13226,7 @@
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>almeidajjwk</v>
+        <v>soniarmurata</v>
       </c>
       <c r="B917">
         <v>0</v>
@@ -13240,7 +13240,7 @@
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>dvlucc2k26_</v>
+        <v>almeidajjwk</v>
       </c>
       <c r="B918">
         <v>0</v>
@@ -13254,7 +13254,7 @@
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>otaviocarneiromma</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B919">
         <v>0</v>
@@ -13268,7 +13268,7 @@
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>ayman__falil_06</v>
+        <v>otaviocarneiromma</v>
       </c>
       <c r="B920">
         <v>0</v>
@@ -13282,7 +13282,7 @@
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>lurochachef</v>
+        <v>ayman__falil_06</v>
       </c>
       <c r="B921">
         <v>0</v>
@@ -13296,7 +13296,7 @@
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>thayanne_rodrigues_bjj</v>
+        <v>lurochachef</v>
       </c>
       <c r="B922">
         <v>0</v>
@@ -13310,7 +13310,7 @@
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>galindofrontado</v>
+        <v>thayanne_rodrigues_bjj</v>
       </c>
       <c r="B923">
         <v>0</v>
@@ -13324,7 +13324,7 @@
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>laureanucalvo</v>
+        <v>galindofrontado</v>
       </c>
       <c r="B924">
         <v>0</v>
@@ -13338,7 +13338,7 @@
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>gisbedejose</v>
+        <v>laureanucalvo</v>
       </c>
       <c r="B925">
         <v>0</v>
@@ -13352,7 +13352,7 @@
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>mauriciogeorge</v>
+        <v>gisbedejose</v>
       </c>
       <c r="B926">
         <v>0</v>
@@ -13366,7 +13366,7 @@
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>viniciusmorais.bjj</v>
+        <v>mauriciogeorge</v>
       </c>
       <c r="B927">
         <v>0</v>
@@ -13380,7 +13380,7 @@
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>gandrapaulino</v>
+        <v>viniciusmorais.bjj</v>
       </c>
       <c r="B928">
         <v>0</v>
@@ -13394,7 +13394,7 @@
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>chalakakavinda</v>
+        <v>gandrapaulino</v>
       </c>
       <c r="B929">
         <v>0</v>
@@ -13408,7 +13408,7 @@
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>pgmarquesantos</v>
+        <v>chalakakavinda</v>
       </c>
       <c r="B930">
         <v>0</v>
@@ -13422,7 +13422,7 @@
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>uluukyrgyz_tima</v>
+        <v>pgmarquesantos</v>
       </c>
       <c r="B931">
         <v>0</v>
@@ -13436,7 +13436,7 @@
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>kells2vallone</v>
+        <v>uluukyrgyz_tima</v>
       </c>
       <c r="B932">
         <v>0</v>
@@ -13450,7 +13450,7 @@
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>personaljakeline</v>
+        <v>kells2vallone</v>
       </c>
       <c r="B933">
         <v>0</v>
@@ -13464,7 +13464,7 @@
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>marcaojudobjjmaster</v>
+        <v>personaljakeline</v>
       </c>
       <c r="B934">
         <v>0</v>
@@ -13478,7 +13478,7 @@
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>sergiorenatocruz1</v>
+        <v>marcaojudobjjmaster</v>
       </c>
       <c r="B935">
         <v>0</v>
@@ -13492,7 +13492,7 @@
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>bjjfalkenberg</v>
+        <v>sergiorenatocruz1</v>
       </c>
       <c r="B936">
         <v>0</v>
@@ -13506,7 +13506,7 @@
     </row>
     <row r="937">
       <c r="A937" t="str">
-        <v>covil.045</v>
+        <v>bjjfalkenberg</v>
       </c>
       <c r="B937">
         <v>0</v>
@@ -13520,7 +13520,7 @@
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v>indio_mma</v>
+        <v>covil.045</v>
       </c>
       <c r="B938">
         <v>0</v>
@@ -13534,7 +13534,7 @@
     </row>
     <row r="939">
       <c r="A939" t="str">
-        <v>alomaraujo</v>
+        <v>indio_mma</v>
       </c>
       <c r="B939">
         <v>0</v>
@@ -13548,7 +13548,7 @@
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>allandelano</v>
+        <v>alomaraujo</v>
       </c>
       <c r="B940">
         <v>0</v>
@@ -13562,7 +13562,7 @@
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>theanimallifemovement</v>
+        <v>allandelano</v>
       </c>
       <c r="B941">
         <v>0</v>
@@ -13576,7 +13576,7 @@
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>tombg_64</v>
+        <v>theanimallifemovement</v>
       </c>
       <c r="B942">
         <v>0</v>
@@ -13590,7 +13590,7 @@
     </row>
     <row r="943">
       <c r="A943" t="str">
-        <v>andreichubotaru94</v>
+        <v>tombg_64</v>
       </c>
       <c r="B943">
         <v>0</v>
@@ -13604,7 +13604,7 @@
     </row>
     <row r="944">
       <c r="A944" t="str">
-        <v>michaeloliveiramma</v>
+        <v>andreichubotaru94</v>
       </c>
       <c r="B944">
         <v>0</v>
@@ -13618,7 +13618,7 @@
     </row>
     <row r="945">
       <c r="A945" t="str">
-        <v>helaynecrisl</v>
+        <v>michaeloliveiramma</v>
       </c>
       <c r="B945">
         <v>0</v>
@@ -13632,7 +13632,7 @@
     </row>
     <row r="946">
       <c r="A946" t="str">
-        <v>carinhakkz</v>
+        <v>helaynecrisl</v>
       </c>
       <c r="B946">
         <v>0</v>
@@ -13646,7 +13646,7 @@
     </row>
     <row r="947">
       <c r="A947" t="str">
-        <v>lmk_sport</v>
+        <v>carinhakkz</v>
       </c>
       <c r="B947">
         <v>0</v>
@@ -13660,7 +13660,7 @@
     </row>
     <row r="948">
       <c r="A948" t="str">
-        <v>mirnacaroline</v>
+        <v>lmk_sport</v>
       </c>
       <c r="B948">
         <v>0</v>
@@ -13674,7 +13674,7 @@
     </row>
     <row r="949">
       <c r="A949" t="str">
-        <v>udilimaheroi</v>
+        <v>mirnacaroline</v>
       </c>
       <c r="B949">
         <v>0</v>
@@ -13688,7 +13688,7 @@
     </row>
     <row r="950">
       <c r="A950" t="str">
-        <v>oliveiraa_00.11</v>
+        <v>udilimaheroi</v>
       </c>
       <c r="B950">
         <v>0</v>
@@ -13702,7 +13702,7 @@
     </row>
     <row r="951">
       <c r="A951" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>oliveiraa_00.11</v>
       </c>
       <c r="B951">
         <v>0</v>
@@ -13716,7 +13716,7 @@
     </row>
     <row r="952">
       <c r="A952" t="str">
-        <v>fher.nando_</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B952">
         <v>0</v>
@@ -13730,7 +13730,7 @@
     </row>
     <row r="953">
       <c r="A953" t="str">
-        <v>heloisa_elohim</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B953">
         <v>0</v>
@@ -13744,7 +13744,7 @@
     </row>
     <row r="954">
       <c r="A954" t="str">
-        <v>raulbasilioo</v>
+        <v>heloisa_elohim</v>
       </c>
       <c r="B954">
         <v>0</v>
@@ -13758,7 +13758,7 @@
     </row>
     <row r="955">
       <c r="A955" t="str">
-        <v>djuliaarianamma</v>
+        <v>raulbasilioo</v>
       </c>
       <c r="B955">
         <v>0</v>
@@ -13772,7 +13772,7 @@
     </row>
     <row r="956">
       <c r="A956" t="str">
-        <v>adrianaramosalvesribeiro</v>
+        <v>djuliaarianamma</v>
       </c>
       <c r="B956">
         <v>0</v>
@@ -13786,7 +13786,7 @@
     </row>
     <row r="957">
       <c r="A957" t="str">
-        <v>alexandrefideliis</v>
+        <v>adrianaramosalvesribeiro</v>
       </c>
       <c r="B957">
         <v>0</v>
@@ -13800,7 +13800,7 @@
     </row>
     <row r="958">
       <c r="A958" t="str">
-        <v>massoterapeuta_bemestarr</v>
+        <v>alexandrefideliis</v>
       </c>
       <c r="B958">
         <v>0</v>
@@ -13814,7 +13814,7 @@
     </row>
     <row r="959">
       <c r="A959" t="str">
-        <v>ellida_guimaraes</v>
+        <v>massoterapeuta_bemestarr</v>
       </c>
       <c r="B959">
         <v>0</v>
@@ -13828,7 +13828,7 @@
     </row>
     <row r="960">
       <c r="A960" t="str">
-        <v>hostonhugo</v>
+        <v>ellida_guimaraes</v>
       </c>
       <c r="B960">
         <v>0</v>
@@ -13842,7 +13842,7 @@
     </row>
     <row r="961">
       <c r="A961" t="str">
-        <v>pammygaryo</v>
+        <v>hostonhugo</v>
       </c>
       <c r="B961">
         <v>0</v>
@@ -13856,7 +13856,7 @@
     </row>
     <row r="962">
       <c r="A962" t="str">
-        <v>bastazinifilho</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B962">
         <v>0</v>
@@ -13870,7 +13870,7 @@
     </row>
     <row r="963">
       <c r="A963" t="str">
-        <v>beatrizosilveira</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B963">
         <v>0</v>
@@ -13884,7 +13884,7 @@
     </row>
     <row r="964">
       <c r="A964" t="str">
-        <v>danieldias7s</v>
+        <v>beatrizosilveira</v>
       </c>
       <c r="B964">
         <v>0</v>
@@ -13898,7 +13898,7 @@
     </row>
     <row r="965">
       <c r="A965" t="str">
-        <v>pepefightteam</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B965">
         <v>0</v>
@@ -13912,7 +13912,7 @@
     </row>
     <row r="966">
       <c r="A966" t="str">
-        <v>ildemarmarajo</v>
+        <v>pepefightteam</v>
       </c>
       <c r="B966">
         <v>0</v>
@@ -13926,7 +13926,7 @@
     </row>
     <row r="967">
       <c r="A967" t="str">
-        <v>tavaresguu</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B967">
         <v>0</v>
@@ -13940,7 +13940,7 @@
     </row>
     <row r="968">
       <c r="A968" t="str">
-        <v>zeferinomma</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B968">
         <v>0</v>
@@ -13954,7 +13954,7 @@
     </row>
     <row r="969">
       <c r="A969" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B969">
         <v>0</v>
@@ -13968,7 +13968,7 @@
     </row>
     <row r="970">
       <c r="A970" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B970">
         <v>0</v>
@@ -13982,7 +13982,7 @@
     </row>
     <row r="971">
       <c r="A971" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B971">
         <v>0</v>
@@ -13996,7 +13996,7 @@
     </row>
     <row r="972">
       <c r="A972" t="str">
-        <v>marcusvgsz</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B972">
         <v>0</v>
@@ -14010,7 +14010,7 @@
     </row>
     <row r="973">
       <c r="A973" t="str">
-        <v>ganemfelipe</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B973">
         <v>0</v>
@@ -14024,7 +14024,7 @@
     </row>
     <row r="974">
       <c r="A974" t="str">
-        <v>ale.lagonegro</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B974">
         <v>0</v>
@@ -14038,7 +14038,7 @@
     </row>
     <row r="975">
       <c r="A975" t="str">
-        <v>ianrochaf</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B975">
         <v>0</v>
@@ -14052,7 +14052,7 @@
     </row>
     <row r="976">
       <c r="A976" t="str">
-        <v>marcotulio_matuto</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B976">
         <v>0</v>
@@ -14066,7 +14066,7 @@
     </row>
     <row r="977">
       <c r="A977" t="str">
-        <v>anselmo.azevedo</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B977">
         <v>0</v>
@@ -14080,7 +14080,7 @@
     </row>
     <row r="978">
       <c r="A978" t="str">
-        <v>lincoln__puig77</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B978">
         <v>0</v>
@@ -14094,7 +14094,7 @@
     </row>
     <row r="979">
       <c r="A979" t="str">
-        <v>sougustavorosa</v>
+        <v>lincoln__puig77</v>
       </c>
       <c r="B979">
         <v>0</v>
@@ -14108,7 +14108,7 @@
     </row>
     <row r="980">
       <c r="A980" t="str">
-        <v>sem_saida.12</v>
+        <v>sougustavorosa</v>
       </c>
       <c r="B980">
         <v>0</v>
@@ -14122,7 +14122,7 @@
     </row>
     <row r="981">
       <c r="A981" t="str">
-        <v>lyviaestherbjj</v>
+        <v>sem_saida.12</v>
       </c>
       <c r="B981">
         <v>0</v>
@@ -14136,7 +14136,7 @@
     </row>
     <row r="982">
       <c r="A982" t="str">
-        <v>macio.almeida_89</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B982">
         <v>0</v>
@@ -14150,7 +14150,7 @@
     </row>
     <row r="983">
       <c r="A983" t="str">
-        <v>helman_mma70</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B983">
         <v>0</v>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="984">
       <c r="A984" t="str">
-        <v>brun_oguerreiro</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B984">
         <v>0</v>
@@ -14178,7 +14178,7 @@
     </row>
     <row r="985">
       <c r="A985" t="str">
-        <v>ohanna.anselmo</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B985">
         <v>0</v>
@@ -14192,7 +14192,7 @@
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v>malene_elleen</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B986">
         <v>0</v>
@@ -14206,7 +14206,7 @@
     </row>
     <row r="987">
       <c r="A987" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B987">
         <v>0</v>
@@ -14220,7 +14220,7 @@
     </row>
     <row r="988">
       <c r="A988" t="str">
-        <v>caioleonjj</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B988">
         <v>0</v>
@@ -14234,7 +14234,7 @@
     </row>
     <row r="989">
       <c r="A989" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B989">
         <v>0</v>
@@ -14248,7 +14248,7 @@
     </row>
     <row r="990">
       <c r="A990" t="str">
-        <v>fdanieljj</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B990">
         <v>0</v>
@@ -14262,7 +14262,7 @@
     </row>
     <row r="991">
       <c r="A991" t="str">
-        <v>makelele_bjj</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B991">
         <v>0</v>
@@ -14276,7 +14276,7 @@
     </row>
     <row r="992">
       <c r="A992" t="str">
-        <v>dreamartpro</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B992">
         <v>0</v>
@@ -14290,7 +14290,7 @@
     </row>
     <row r="993">
       <c r="A993" t="str">
-        <v>andressa_bjj_</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B993">
         <v>0</v>
@@ -14304,7 +14304,7 @@
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v>karine_killer_ufc</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B994">
         <v>0</v>
@@ -14318,7 +14318,7 @@
     </row>
     <row r="995">
       <c r="A995" t="str">
-        <v>wendel_bjj14</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B995">
         <v>0</v>
@@ -14332,7 +14332,7 @@
     </row>
     <row r="996">
       <c r="A996" t="str">
-        <v>tamarapq</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B996">
         <v>0</v>
@@ -14346,7 +14346,7 @@
     </row>
     <row r="997">
       <c r="A997" t="str">
-        <v>thaynara_victoria_</v>
+        <v>tamarapq</v>
       </c>
       <c r="B997">
         <v>0</v>
@@ -14360,7 +14360,7 @@
     </row>
     <row r="998">
       <c r="A998" t="str">
-        <v>mma.fisio</v>
+        <v>thaynara_victoria_</v>
       </c>
       <c r="B998">
         <v>0</v>
@@ -14374,7 +14374,7 @@
     </row>
     <row r="999">
       <c r="A999" t="str">
-        <v>danielplayboymt</v>
+        <v>mma.fisio</v>
       </c>
       <c r="B999">
         <v>0</v>
@@ -14388,7 +14388,7 @@
     </row>
     <row r="1000">
       <c r="A1000" t="str">
-        <v>chunco_424</v>
+        <v>danielplayboymt</v>
       </c>
       <c r="B1000">
         <v>0</v>
@@ -14402,7 +14402,7 @@
     </row>
     <row r="1001">
       <c r="A1001" t="str">
-        <v>fix.pec</v>
+        <v>chunco_424</v>
       </c>
       <c r="B1001">
         <v>0</v>
@@ -14416,7 +14416,7 @@
     </row>
     <row r="1002">
       <c r="A1002" t="str">
-        <v>roxostrike</v>
+        <v>fix.pec</v>
       </c>
       <c r="B1002">
         <v>0</v>
@@ -14430,7 +14430,7 @@
     </row>
     <row r="1003">
       <c r="A1003" t="str">
-        <v>josita_bjj</v>
+        <v>roxostrike</v>
       </c>
       <c r="B1003">
         <v>0</v>
@@ -14444,7 +14444,7 @@
     </row>
     <row r="1004">
       <c r="A1004" t="str">
-        <v>priscilaapbatista</v>
+        <v>josita_bjj</v>
       </c>
       <c r="B1004">
         <v>0</v>
@@ -14458,7 +14458,7 @@
     </row>
     <row r="1005">
       <c r="A1005" t="str">
-        <v>denisalagoanobjj</v>
+        <v>priscilaapbatista</v>
       </c>
       <c r="B1005">
         <v>0</v>
@@ -14472,7 +14472,7 @@
     </row>
     <row r="1006">
       <c r="A1006" t="str">
-        <v>shirleypalestrina6</v>
+        <v>denisalagoanobjj</v>
       </c>
       <c r="B1006">
         <v>0</v>
@@ -14486,7 +14486,7 @@
     </row>
     <row r="1007">
       <c r="A1007" t="str">
-        <v>flipebiano</v>
+        <v>shirleypalestrina6</v>
       </c>
       <c r="B1007">
         <v>0</v>
@@ -14500,7 +14500,7 @@
     </row>
     <row r="1008">
       <c r="A1008" t="str">
-        <v>lyvia_genuina</v>
+        <v>flipebiano</v>
       </c>
       <c r="B1008">
         <v>0</v>
@@ -14514,7 +14514,7 @@
     </row>
     <row r="1009">
       <c r="A1009" t="str">
-        <v>horadopower</v>
+        <v>lyvia_genuina</v>
       </c>
       <c r="B1009">
         <v>0</v>
@@ -14528,7 +14528,7 @@
     </row>
     <row r="1010">
       <c r="A1010" t="str">
-        <v>manoel.brum</v>
+        <v>horadopower</v>
       </c>
       <c r="B1010">
         <v>0</v>
@@ -14542,7 +14542,7 @@
     </row>
     <row r="1011">
       <c r="A1011" t="str">
-        <v>babimaciel1</v>
+        <v>manoel.brum</v>
       </c>
       <c r="B1011">
         <v>0</v>
@@ -14556,7 +14556,7 @@
     </row>
     <row r="1012">
       <c r="A1012" t="str">
-        <v>ruanmiqueias</v>
+        <v>babimaciel1</v>
       </c>
       <c r="B1012">
         <v>0</v>
@@ -14570,7 +14570,7 @@
     </row>
     <row r="1013">
       <c r="A1013" t="str">
-        <v>delariva_belem</v>
+        <v>ruanmiqueias</v>
       </c>
       <c r="B1013">
         <v>0</v>
@@ -14584,7 +14584,7 @@
     </row>
     <row r="1014">
       <c r="A1014" t="str">
-        <v>joseochoa.mma</v>
+        <v>delariva_belem</v>
       </c>
       <c r="B1014">
         <v>0</v>
@@ -14598,7 +14598,7 @@
     </row>
     <row r="1015">
       <c r="A1015" t="str">
-        <v>reynitaoblitasbustamante</v>
+        <v>joseochoa.mma</v>
       </c>
       <c r="B1015">
         <v>0</v>
@@ -14612,7 +14612,7 @@
     </row>
     <row r="1016">
       <c r="A1016" t="str">
-        <v>sthefany_ochoao</v>
+        <v>reynitaoblitasbustamante</v>
       </c>
       <c r="B1016">
         <v>0</v>
@@ -14626,7 +14626,7 @@
     </row>
     <row r="1017">
       <c r="A1017" t="str">
-        <v>_matheustiberio</v>
+        <v>sthefany_ochoao</v>
       </c>
       <c r="B1017">
         <v>0</v>
@@ -14640,7 +14640,7 @@
     </row>
     <row r="1018">
       <c r="A1018" t="str">
-        <v>gabrielsantosufc_</v>
+        <v>_matheustiberio</v>
       </c>
       <c r="B1018">
         <v>0</v>
@@ -14654,7 +14654,7 @@
     </row>
     <row r="1019">
       <c r="A1019" t="str">
-        <v>juugxmes</v>
+        <v>gabrielsantosufc_</v>
       </c>
       <c r="B1019">
         <v>0</v>
@@ -14668,7 +14668,7 @@
     </row>
     <row r="1020">
       <c r="A1020" t="str">
-        <v>gabriellb.andrade</v>
+        <v>juugxmes</v>
       </c>
       <c r="B1020">
         <v>0</v>
@@ -14682,7 +14682,7 @@
     </row>
     <row r="1021">
       <c r="A1021" t="str">
-        <v>romelluistro</v>
+        <v>gabriellb.andrade</v>
       </c>
       <c r="B1021">
         <v>0</v>
@@ -14696,7 +14696,7 @@
     </row>
     <row r="1022">
       <c r="A1022" t="str">
-        <v>yuricapelasso</v>
+        <v>romelluistro</v>
       </c>
       <c r="B1022">
         <v>0</v>
@@ -14710,7 +14710,7 @@
     </row>
     <row r="1023">
       <c r="A1023" t="str">
-        <v>lucasfenomeno_ufc</v>
+        <v>yuricapelasso</v>
       </c>
       <c r="B1023">
         <v>0</v>
@@ -14724,7 +14724,7 @@
     </row>
     <row r="1024">
       <c r="A1024" t="str">
-        <v>matheusdouradomma</v>
+        <v>lucasfenomeno_ufc</v>
       </c>
       <c r="B1024">
         <v>0</v>
@@ -14738,7 +14738,7 @@
     </row>
     <row r="1025">
       <c r="A1025" t="str">
-        <v>lazyboy.ufc</v>
+        <v>matheusdouradomma</v>
       </c>
       <c r="B1025">
         <v>0</v>
@@ -14752,7 +14752,7 @@
     </row>
     <row r="1026">
       <c r="A1026" t="str">
-        <v>gabriell_marcus</v>
+        <v>lazyboy.ufc</v>
       </c>
       <c r="B1026">
         <v>0</v>
@@ -14766,7 +14766,7 @@
     </row>
     <row r="1027">
       <c r="A1027" t="str">
-        <v>rafaelsouza7586</v>
+        <v>gabriell_marcus</v>
       </c>
       <c r="B1027">
         <v>0</v>
@@ -14780,7 +14780,7 @@
     </row>
     <row r="1028">
       <c r="A1028" t="str">
-        <v>dodge_big_johnson29</v>
+        <v>rafaelsouza7586</v>
       </c>
       <c r="B1028">
         <v>0</v>
@@ -14794,7 +14794,7 @@
     </row>
     <row r="1029">
       <c r="A1029" t="str">
-        <v>land_on_martelo_308</v>
+        <v>dodge_big_johnson29</v>
       </c>
       <c r="B1029">
         <v>0</v>
@@ -14808,7 +14808,7 @@
     </row>
     <row r="1030">
       <c r="A1030" t="str">
-        <v>dj__freckles</v>
+        <v>land_on_martelo_308</v>
       </c>
       <c r="B1030">
         <v>0</v>
@@ -14822,7 +14822,7 @@
     </row>
     <row r="1031">
       <c r="A1031" t="str">
-        <v>regis18vieira</v>
+        <v>dj__freckles</v>
       </c>
       <c r="B1031">
         <v>0</v>
@@ -14836,7 +14836,7 @@
     </row>
     <row r="1032">
       <c r="A1032" t="str">
-        <v>andy.techera.12</v>
+        <v>regis18vieira</v>
       </c>
       <c r="B1032">
         <v>0</v>
@@ -14850,7 +14850,7 @@
     </row>
     <row r="1033">
       <c r="A1033" t="str">
-        <v>celiogarcia6</v>
+        <v>andy.techera.12</v>
       </c>
       <c r="B1033">
         <v>0</v>
@@ -14864,7 +14864,7 @@
     </row>
     <row r="1034">
       <c r="A1034" t="str">
-        <v>luluakio</v>
+        <v>celiogarcia6</v>
       </c>
       <c r="B1034">
         <v>0</v>
@@ -14878,7 +14878,7 @@
     </row>
     <row r="1035">
       <c r="A1035" t="str">
-        <v>lusoaresjj</v>
+        <v>luluakio</v>
       </c>
       <c r="B1035">
         <v>0</v>
@@ -14892,7 +14892,7 @@
     </row>
     <row r="1036">
       <c r="A1036" t="str">
-        <v>barreto.boxe</v>
+        <v>lusoaresjj</v>
       </c>
       <c r="B1036">
         <v>0</v>
@@ -14906,7 +14906,7 @@
     </row>
     <row r="1037">
       <c r="A1037" t="str">
-        <v>sharingan_mma</v>
+        <v>barreto.boxe</v>
       </c>
       <c r="B1037">
         <v>0</v>
@@ -14920,7 +14920,7 @@
     </row>
     <row r="1038">
       <c r="A1038" t="str">
-        <v>thaisadantas</v>
+        <v>sharingan_mma</v>
       </c>
       <c r="B1038">
         <v>0</v>
@@ -14934,7 +14934,7 @@
     </row>
     <row r="1039">
       <c r="A1039" t="str">
-        <v>jp.mdc</v>
+        <v>thaisadantas</v>
       </c>
       <c r="B1039">
         <v>0</v>
@@ -14948,7 +14948,7 @@
     </row>
     <row r="1040">
       <c r="A1040" t="str">
-        <v>danielbzk_</v>
+        <v>jp.mdc</v>
       </c>
       <c r="B1040">
         <v>0</v>
@@ -14962,7 +14962,7 @@
     </row>
     <row r="1041">
       <c r="A1041" t="str">
-        <v>herbeth_indiomma</v>
+        <v>danielbzk_</v>
       </c>
       <c r="B1041">
         <v>0</v>
@@ -14976,7 +14976,7 @@
     </row>
     <row r="1042">
       <c r="A1042" t="str">
-        <v>pulsepro.nutrition</v>
+        <v>herbeth_indiomma</v>
       </c>
       <c r="B1042">
         <v>0</v>
@@ -14990,7 +14990,7 @@
     </row>
     <row r="1043">
       <c r="A1043" t="str">
-        <v>1210gi</v>
+        <v>pulsepro.nutrition</v>
       </c>
       <c r="B1043">
         <v>0</v>
@@ -15004,7 +15004,7 @@
     </row>
     <row r="1044">
       <c r="A1044" t="str">
-        <v>maicon_mamute_</v>
+        <v>1210gi</v>
       </c>
       <c r="B1044">
         <v>0</v>
@@ -15018,7 +15018,7 @@
     </row>
     <row r="1045">
       <c r="A1045" t="str">
-        <v>wildler_borriello</v>
+        <v>maicon_mamute_</v>
       </c>
       <c r="B1045">
         <v>0</v>
@@ -15032,7 +15032,7 @@
     </row>
     <row r="1046">
       <c r="A1046" t="str">
-        <v>esmeraldasales</v>
+        <v>wildler_borriello</v>
       </c>
       <c r="B1046">
         <v>0</v>
@@ -15046,7 +15046,7 @@
     </row>
     <row r="1047">
       <c r="A1047" t="str">
-        <v>raffaelcerqueira_ufc</v>
+        <v>esmeraldasales</v>
       </c>
       <c r="B1047">
         <v>0</v>
@@ -15060,7 +15060,7 @@
     </row>
     <row r="1048">
       <c r="A1048" t="str">
-        <v>jhonnydavid</v>
+        <v>raffaelcerqueira_ufc</v>
       </c>
       <c r="B1048">
         <v>0</v>
@@ -15074,7 +15074,7 @@
     </row>
     <row r="1049">
       <c r="A1049" t="str">
-        <v>dannielvieira</v>
+        <v>jhonnydavid</v>
       </c>
       <c r="B1049">
         <v>0</v>
@@ -15088,7 +15088,7 @@
     </row>
     <row r="1050">
       <c r="A1050" t="str">
-        <v>guilherme.leandromma</v>
+        <v>dannielvieira</v>
       </c>
       <c r="B1050">
         <v>0</v>
@@ -15102,7 +15102,7 @@
     </row>
     <row r="1051">
       <c r="A1051" t="str">
-        <v>siinho</v>
+        <v>guilherme.leandromma</v>
       </c>
       <c r="B1051">
         <v>0</v>
@@ -15116,7 +15116,7 @@
     </row>
     <row r="1052">
       <c r="A1052" t="str">
-        <v>rnn.neves</v>
+        <v>siinho</v>
       </c>
       <c r="B1052">
         <v>0</v>
@@ -15130,7 +15130,7 @@
     </row>
     <row r="1053">
       <c r="A1053" t="str">
-        <v>sulafotografia</v>
+        <v>rnn.neves</v>
       </c>
       <c r="B1053">
         <v>0</v>
@@ -15144,7 +15144,7 @@
     </row>
     <row r="1054">
       <c r="A1054" t="str">
-        <v>luisfendt</v>
+        <v>sulafotografia</v>
       </c>
       <c r="B1054">
         <v>0</v>
@@ -15158,7 +15158,7 @@
     </row>
     <row r="1055">
       <c r="A1055" t="str">
-        <v>cipobr</v>
+        <v>luisfendt</v>
       </c>
       <c r="B1055">
         <v>0</v>
@@ -15172,7 +15172,7 @@
     </row>
     <row r="1056">
       <c r="A1056" t="str">
-        <v>contadoraison</v>
+        <v>cipobr</v>
       </c>
       <c r="B1056">
         <v>0</v>
@@ -15186,7 +15186,7 @@
     </row>
     <row r="1057">
       <c r="A1057" t="str">
-        <v>guerreira.doasfalto</v>
+        <v>contadoraison</v>
       </c>
       <c r="B1057">
         <v>0</v>
@@ -15200,7 +15200,7 @@
     </row>
     <row r="1058">
       <c r="A1058" t="str">
-        <v>jlheitor</v>
+        <v>guerreira.doasfalto</v>
       </c>
       <c r="B1058">
         <v>0</v>
@@ -15214,7 +15214,7 @@
     </row>
     <row r="1059">
       <c r="A1059" t="str">
-        <v>nostalgia_npt</v>
+        <v>jlheitor</v>
       </c>
       <c r="B1059">
         <v>0</v>
@@ -15228,7 +15228,7 @@
     </row>
     <row r="1060">
       <c r="A1060" t="str">
-        <v>rapaduracapoeira</v>
+        <v>nostalgia_npt</v>
       </c>
       <c r="B1060">
         <v>0</v>
@@ -15242,7 +15242,7 @@
     </row>
     <row r="1061">
       <c r="A1061" t="str">
-        <v>cdmurilorossi</v>
+        <v>rapaduracapoeira</v>
       </c>
       <c r="B1061">
         <v>0</v>
@@ -15256,7 +15256,7 @@
     </row>
     <row r="1062">
       <c r="A1062" t="str">
-        <v>marciosil7</v>
+        <v>cdmurilorossi</v>
       </c>
       <c r="B1062">
         <v>0</v>
@@ -15270,7 +15270,7 @@
     </row>
     <row r="1063">
       <c r="A1063" t="str">
-        <v>s.rodrigobernardoda</v>
+        <v>marciosil7</v>
       </c>
       <c r="B1063">
         <v>0</v>
@@ -15284,7 +15284,7 @@
     </row>
     <row r="1064">
       <c r="A1064" t="str">
-        <v>fe.souza89</v>
+        <v>s.rodrigobernardoda</v>
       </c>
       <c r="B1064">
         <v>0</v>
@@ -15298,7 +15298,7 @@
     </row>
     <row r="1065">
       <c r="A1065" t="str">
-        <v>yuri.t.bechelli</v>
+        <v>fe.souza89</v>
       </c>
       <c r="B1065">
         <v>0</v>
@@ -15312,7 +15312,7 @@
     </row>
     <row r="1066">
       <c r="A1066" t="str">
-        <v>wellington_silva_1995</v>
+        <v>yuri.t.bechelli</v>
       </c>
       <c r="B1066">
         <v>0</v>
@@ -15326,7 +15326,7 @@
     </row>
     <row r="1067">
       <c r="A1067" t="str">
-        <v>ricardolopes4921</v>
+        <v>wellington_silva_1995</v>
       </c>
       <c r="B1067">
         <v>0</v>
@@ -15340,7 +15340,7 @@
     </row>
     <row r="1068">
       <c r="A1068" t="str">
-        <v>nicollebertolinie</v>
+        <v>ricardolopes4921</v>
       </c>
       <c r="B1068">
         <v>0</v>
@@ -15354,7 +15354,7 @@
     </row>
     <row r="1069">
       <c r="A1069" t="str">
-        <v>leticia_araujo447</v>
+        <v>nicollebertolinie</v>
       </c>
       <c r="B1069">
         <v>0</v>
@@ -15368,7 +15368,7 @@
     </row>
     <row r="1070">
       <c r="A1070" t="str">
-        <v>__paulaprada__</v>
+        <v>leticia_araujo447</v>
       </c>
       <c r="B1070">
         <v>0</v>
@@ -15382,7 +15382,7 @@
     </row>
     <row r="1071">
       <c r="A1071" t="str">
-        <v>alexandresagat.oficial</v>
+        <v>__paulaprada__</v>
       </c>
       <c r="B1071">
         <v>0</v>
@@ -15396,7 +15396,7 @@
     </row>
     <row r="1072">
       <c r="A1072" t="str">
-        <v>annamarya_silveira</v>
+        <v>alexandresagat.oficial</v>
       </c>
       <c r="B1072">
         <v>0</v>
@@ -15410,7 +15410,7 @@
     </row>
     <row r="1073">
       <c r="A1073" t="str">
-        <v>sousamaevia</v>
+        <v>annamarya_silveira</v>
       </c>
       <c r="B1073">
         <v>0</v>
@@ -15424,7 +15424,7 @@
     </row>
     <row r="1074">
       <c r="A1074" t="str">
-        <v>eneido_neto</v>
+        <v>sousamaevia</v>
       </c>
       <c r="B1074">
         <v>0</v>
@@ -15438,7 +15438,7 @@
     </row>
     <row r="1075">
       <c r="A1075" t="str">
-        <v>genillsson_177</v>
+        <v>eneido_neto</v>
       </c>
       <c r="B1075">
         <v>0</v>
@@ -15452,7 +15452,7 @@
     </row>
     <row r="1076">
       <c r="A1076" t="str">
-        <v>alesiqueira_personal</v>
+        <v>genillsson_177</v>
       </c>
       <c r="B1076">
         <v>0</v>
@@ -15466,7 +15466,7 @@
     </row>
     <row r="1077">
       <c r="A1077" t="str">
-        <v>anaclaudialc73</v>
+        <v>alesiqueira_personal</v>
       </c>
       <c r="B1077">
         <v>0</v>
@@ -15480,7 +15480,7 @@
     </row>
     <row r="1078">
       <c r="A1078" t="str">
-        <v>fernandohf32</v>
+        <v>anaclaudialc73</v>
       </c>
       <c r="B1078">
         <v>0</v>
@@ -15494,7 +15494,7 @@
     </row>
     <row r="1079">
       <c r="A1079" t="str">
-        <v>gleydeolyveeira</v>
+        <v>fernandohf32</v>
       </c>
       <c r="B1079">
         <v>0</v>
@@ -15508,7 +15508,7 @@
     </row>
     <row r="1080">
       <c r="A1080" t="str">
-        <v>rbueno81</v>
+        <v>gleydeolyveeira</v>
       </c>
       <c r="B1080">
         <v>0</v>
@@ -15522,7 +15522,7 @@
     </row>
     <row r="1081">
       <c r="A1081" t="str">
-        <v>rafamakita</v>
+        <v>rbueno81</v>
       </c>
       <c r="B1081">
         <v>0</v>
@@ -15536,7 +15536,7 @@
     </row>
     <row r="1082">
       <c r="A1082" t="str">
-        <v>biia_sousah</v>
+        <v>rafamakita</v>
       </c>
       <c r="B1082">
         <v>0</v>
@@ -15550,7 +15550,7 @@
     </row>
     <row r="1083">
       <c r="A1083" t="str">
-        <v>ronygoto</v>
+        <v>biia_sousah</v>
       </c>
       <c r="B1083">
         <v>0</v>
@@ -15564,7 +15564,7 @@
     </row>
     <row r="1084">
       <c r="A1084" t="str">
-        <v>igorpatrao</v>
+        <v>ronygoto</v>
       </c>
       <c r="B1084">
         <v>0</v>
@@ -15578,7 +15578,7 @@
     </row>
     <row r="1085">
       <c r="A1085" t="str">
-        <v>fideles8080</v>
+        <v>igorpatrao</v>
       </c>
       <c r="B1085">
         <v>0</v>
@@ -15592,28 +15592,42 @@
     </row>
     <row r="1086">
       <c r="A1086" t="str">
+        <v>fideles8080</v>
+      </c>
+      <c r="B1086">
+        <v>0</v>
+      </c>
+      <c r="C1086">
+        <v>1</v>
+      </c>
+      <c r="D1086">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="str">
         <v>nadiabarakkat</v>
       </c>
-      <c r="B1086">
-        <v>0</v>
-      </c>
-      <c r="C1086">
-        <v>1</v>
-      </c>
-      <c r="D1086">
+      <c r="B1087">
+        <v>0</v>
+      </c>
+      <c r="C1087">
+        <v>1</v>
+      </c>
+      <c r="D1087">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D1086"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1087"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D90"/>
+  <dimension ref="A1:D92"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -15648,13 +15662,13 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
+        <v>5</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>4</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -15883,30 +15897,30 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>mvp_lutas</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D20">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>kelly_ottoni</v>
+        <v>mvp_lutas</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22">
@@ -16387,41 +16401,41 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>johnmma9</v>
+        <v>pro_mmabetting</v>
       </c>
       <c r="B56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>blogfabiocosta</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B57">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D57">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>leo_sousa_cabeleleiro</v>
+        <v>aj_mma_</v>
       </c>
       <c r="B58">
         <v>0</v>
       </c>
       <c r="C58">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -16429,7 +16443,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>markiim_guerreiro</v>
+        <v>johnmma9</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -16443,7 +16457,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>god.motivacao</v>
+        <v>blogfabiocosta</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -16457,7 +16471,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>fe.souza89</v>
+        <v>leo_sousa_cabeleleiro</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -16466,12 +16480,12 @@
         <v>1</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>markiim_guerreiro</v>
       </c>
       <c r="B62">
         <v>0</v>
@@ -16480,12 +16494,12 @@
         <v>1</v>
       </c>
       <c r="D62">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>yuri.t.bechelli</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -16494,12 +16508,12 @@
         <v>1</v>
       </c>
       <c r="D63">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>wellington_silva_1995</v>
+        <v>fe.souza89</v>
       </c>
       <c r="B64">
         <v>0</v>
@@ -16513,7 +16527,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>ricardolopes4921</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -16527,7 +16541,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>nicollebertolinie</v>
+        <v>yuri.t.bechelli</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -16541,7 +16555,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>leticia_araujo447</v>
+        <v>wellington_silva_1995</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -16555,7 +16569,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>__paulaprada__</v>
+        <v>ricardolopes4921</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -16569,7 +16583,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>alexandresagat.oficial</v>
+        <v>nicollebertolinie</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -16583,7 +16597,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>annamarya_silveira</v>
+        <v>leticia_araujo447</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -16597,7 +16611,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>sousamaevia</v>
+        <v>__paulaprada__</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -16611,7 +16625,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>eneido_neto</v>
+        <v>alexandresagat.oficial</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -16625,7 +16639,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>genillsson_177</v>
+        <v>annamarya_silveira</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -16639,7 +16653,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>alesiqueira_personal</v>
+        <v>sousamaevia</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -16653,7 +16667,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>anaclaudialc73</v>
+        <v>eneido_neto</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -16667,7 +16681,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>fernandohf32</v>
+        <v>genillsson_177</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -16681,7 +16695,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>gleydeolyveeira</v>
+        <v>alesiqueira_personal</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -16695,7 +16709,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>rbueno81</v>
+        <v>anaclaudialc73</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -16709,7 +16723,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>rafamakita</v>
+        <v>fernandohf32</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -16723,7 +16737,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>biia_sousah</v>
+        <v>gleydeolyveeira</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -16737,7 +16751,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>ronygoto</v>
+        <v>rbueno81</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -16751,7 +16765,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>igorpatrao</v>
+        <v>rafamakita</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -16765,7 +16779,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>fideles8080</v>
+        <v>biia_sousah</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -16779,7 +16793,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>nadiabarakkat</v>
+        <v>ronygoto</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -16793,7 +16807,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>aj_mma_</v>
+        <v>igorpatrao</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -16807,7 +16821,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>washington_cassisno</v>
+        <v>fideles8080</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -16821,7 +16835,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>marcelogabrielmma</v>
+        <v>nadiabarakkat</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -16835,7 +16849,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>diegopaivajj</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -16849,7 +16863,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>aida_dos_sonhos</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -16863,21 +16877,49 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
+        <v>diegopaivajj</v>
+      </c>
+      <c r="B90">
+        <v>0</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="str">
+        <v>aida_dos_sonhos</v>
+      </c>
+      <c r="B91">
+        <v>0</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="str">
         <v>_oliveira09_</v>
       </c>
-      <c r="B90">
-        <v>0</v>
-      </c>
-      <c r="C90">
-        <v>1</v>
-      </c>
-      <c r="D90">
+      <c r="B92">
+        <v>0</v>
+      </c>
+      <c r="C92">
+        <v>1</v>
+      </c>
+      <c r="D92">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D90"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D92"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-08.xlsx
+++ b/Engagement Rankings 2026-08.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1087"/>
+  <dimension ref="A1:D1089"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -433,7 +433,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>3685</v>
+        <v>3687</v>
       </c>
       <c r="C3">
         <v>6</v>
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C6">
         <v>17</v>
       </c>
       <c r="D6">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="7">
@@ -1074,30 +1074,30 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>victus_torquatus00</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B49">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C49">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>kelly_ottoni</v>
+        <v>victus_torquatus00</v>
       </c>
       <c r="B50">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C50">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="D50">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="51">
@@ -4070,63 +4070,63 @@
     </row>
     <row r="263">
       <c r="A263" t="str">
-        <v>couragemma</v>
+        <v>_franklinxavier</v>
       </c>
       <c r="B263">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C263">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D263">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="str">
-        <v>kaua_limaofc</v>
+        <v>couragemma</v>
       </c>
       <c r="B264">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C264">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D264">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="str">
-        <v>ruangzk</v>
+        <v>kaua_limaofc</v>
       </c>
       <c r="B265">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C265">
         <v>0</v>
       </c>
       <c r="D265">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="str">
-        <v>emerson_lucaszx</v>
+        <v>ruangzk</v>
       </c>
       <c r="B266">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C266">
         <v>0</v>
       </c>
       <c r="D266">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>clouddhidden</v>
+        <v>emerson_lucaszx</v>
       </c>
       <c r="B267">
         <v>2</v>
@@ -4140,21 +4140,21 @@
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>_matheusifernandes</v>
+        <v>clouddhidden</v>
       </c>
       <c r="B268">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C268">
         <v>0</v>
       </c>
       <c r="D268">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>bryantank_</v>
+        <v>_matheusifernandes</v>
       </c>
       <c r="B269">
         <v>1</v>
@@ -4168,7 +4168,7 @@
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>ruan.arcanjo01</v>
+        <v>bryantank_</v>
       </c>
       <c r="B270">
         <v>1</v>
@@ -4182,7 +4182,7 @@
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>coyote_style_hair</v>
+        <v>ruan.arcanjo01</v>
       </c>
       <c r="B271">
         <v>1</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>edsoncostateixeirabjj</v>
+        <v>coyote_style_hair</v>
       </c>
       <c r="B272">
         <v>1</v>
@@ -4210,7 +4210,7 @@
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>og.mthx</v>
+        <v>edsoncostateixeirabjj</v>
       </c>
       <c r="B273">
         <v>1</v>
@@ -4224,83 +4224,83 @@
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>klein_hila</v>
+        <v>og.mthx</v>
       </c>
       <c r="B274">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C274">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D274">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>jhonatas_ricardo</v>
+        <v>klein_hila</v>
       </c>
       <c r="B275">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C275">
         <v>1</v>
       </c>
       <c r="D275">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>jhee_dias</v>
+        <v>jhonatas_ricardo</v>
       </c>
       <c r="B276">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C276">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D276">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>diegosilvabjjoficial</v>
+        <v>jhee_dias</v>
       </c>
       <c r="B277">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C277">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D277">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>vnciuss__df</v>
+        <v>diegosilvabjjoficial</v>
       </c>
       <c r="B278">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C278">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D278">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>tassiogiloficial</v>
+        <v>vnciuss__df</v>
       </c>
       <c r="B279">
         <v>2</v>
       </c>
       <c r="C279">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D279">
         <v>0</v>
@@ -4308,35 +4308,35 @@
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>nicolasmarretabjj</v>
+        <v>tassiogiloficial</v>
       </c>
       <c r="B280">
         <v>2</v>
       </c>
       <c r="C280">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D280">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>richards_brusen</v>
+        <v>nicolasmarretabjj</v>
       </c>
       <c r="B281">
         <v>2</v>
       </c>
       <c r="C281">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D281">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>natalan_wilgner</v>
+        <v>richards_brusen</v>
       </c>
       <c r="B282">
         <v>2</v>
@@ -4350,7 +4350,7 @@
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>leticiamartinspro</v>
+        <v>natalan_wilgner</v>
       </c>
       <c r="B283">
         <v>2</v>
@@ -4364,69 +4364,69 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>danilo_marquesc</v>
+        <v>leticiamartinspro</v>
       </c>
       <c r="B284">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C284">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D284">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>lucasspaulista</v>
+        <v>danilo_marquesc</v>
       </c>
       <c r="B285">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C285">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D285">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>eltonqueirozpereira</v>
+        <v>lucasspaulista</v>
       </c>
       <c r="B286">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C286">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D286">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>elderdiascaneladeaco</v>
+        <v>eltonqueirozpereira</v>
       </c>
       <c r="B287">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C287">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D287">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>select_from_joao</v>
+        <v>elderdiascaneladeaco</v>
       </c>
       <c r="B288">
         <v>2</v>
       </c>
       <c r="C288">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D288">
         <v>0</v>
@@ -4434,21 +4434,21 @@
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>claudio_marchese_7</v>
+        <v>select_from_joao</v>
       </c>
       <c r="B289">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C289">
         <v>1</v>
       </c>
       <c r="D289">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>fabaotipster</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B290">
         <v>1</v>
@@ -4462,13 +4462,13 @@
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>luanlacerda_ufc_61kg</v>
+        <v>fabaotipster</v>
       </c>
       <c r="B291">
         <v>1</v>
       </c>
       <c r="C291">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D291">
         <v>1</v>
@@ -4476,13 +4476,13 @@
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>helenaseveribjj</v>
+        <v>luanlacerda_ufc_61kg</v>
       </c>
       <c r="B292">
         <v>1</v>
       </c>
       <c r="C292">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D292">
         <v>1</v>
@@ -4490,41 +4490,41 @@
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>ommariotti</v>
+        <v>helenaseveribjj</v>
       </c>
       <c r="B293">
         <v>1</v>
       </c>
       <c r="C293">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D293">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>marciokeske</v>
+        <v>ommariotti</v>
       </c>
       <c r="B294">
         <v>1</v>
       </c>
       <c r="C294">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D294">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>felipebunesufc</v>
+        <v>marciokeske</v>
       </c>
       <c r="B295">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C295">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D295">
         <v>0</v>
@@ -4532,7 +4532,7 @@
     </row>
     <row r="296">
       <c r="A296" t="str">
-        <v>icarohilton</v>
+        <v>felipebunesufc</v>
       </c>
       <c r="B296">
         <v>2</v>
@@ -4546,35 +4546,35 @@
     </row>
     <row r="297">
       <c r="A297" t="str">
-        <v>jesabelmelo9</v>
+        <v>icarohilton</v>
       </c>
       <c r="B297">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C297">
         <v>1</v>
       </c>
       <c r="D297">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="str">
-        <v>iranbez</v>
+        <v>jesabelmelo9</v>
       </c>
       <c r="B298">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C298">
         <v>1</v>
       </c>
       <c r="D298">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="str">
-        <v>sthe._.araujo</v>
+        <v>iranbez</v>
       </c>
       <c r="B299">
         <v>2</v>
@@ -4588,13 +4588,13 @@
     </row>
     <row r="300">
       <c r="A300" t="str">
-        <v>clayton77silva</v>
+        <v>sthe._.araujo</v>
       </c>
       <c r="B300">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C300">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D300">
         <v>0</v>
@@ -4602,13 +4602,13 @@
     </row>
     <row r="301">
       <c r="A301" t="str">
-        <v>sarahfmaia</v>
+        <v>clayton77silva</v>
       </c>
       <c r="B301">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C301">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D301">
         <v>0</v>
@@ -4616,7 +4616,7 @@
     </row>
     <row r="302">
       <c r="A302" t="str">
-        <v>raycon_mma</v>
+        <v>sarahfmaia</v>
       </c>
       <c r="B302">
         <v>2</v>
@@ -4630,7 +4630,7 @@
     </row>
     <row r="303">
       <c r="A303" t="str">
-        <v>mmapalpitex</v>
+        <v>raycon_mma</v>
       </c>
       <c r="B303">
         <v>2</v>
@@ -4644,63 +4644,63 @@
     </row>
     <row r="304">
       <c r="A304" t="str">
-        <v>rosacostasousa36</v>
+        <v>mmapalpitex</v>
       </c>
       <c r="B304">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C304">
         <v>1</v>
       </c>
       <c r="D304">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
-        <v>luizferrer_br</v>
+        <v>rosacostasousa36</v>
       </c>
       <c r="B305">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C305">
         <v>1</v>
       </c>
       <c r="D305">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="str">
-        <v>fernando.nogueira.7792</v>
+        <v>luizferrer_br</v>
       </c>
       <c r="B306">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C306">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D306">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="str">
-        <v>erivan_sousa_tico</v>
+        <v>fernando.nogueira.7792</v>
       </c>
       <c r="B307">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C307">
         <v>0</v>
       </c>
       <c r="D307">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="str">
-        <v>aliferpaulo_</v>
+        <v>erivan_sousa_tico</v>
       </c>
       <c r="B308">
         <v>2</v>
@@ -4714,35 +4714,35 @@
     </row>
     <row r="309">
       <c r="A309" t="str">
-        <v>raelduraes</v>
+        <v>aliferpaulo_</v>
       </c>
       <c r="B309">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C309">
         <v>0</v>
       </c>
       <c r="D309">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="str">
-        <v>wesley_bjjvc</v>
+        <v>raelduraes</v>
       </c>
       <c r="B310">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C310">
         <v>0</v>
       </c>
       <c r="D310">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="str">
-        <v>_bety_marcal</v>
+        <v>wesley_bjjvc</v>
       </c>
       <c r="B311">
         <v>2</v>
@@ -4756,7 +4756,7 @@
     </row>
     <row r="312">
       <c r="A312" t="str">
-        <v>wlt_miguel</v>
+        <v>_bety_marcal</v>
       </c>
       <c r="B312">
         <v>2</v>
@@ -4770,7 +4770,7 @@
     </row>
     <row r="313">
       <c r="A313" t="str">
-        <v>martta.mariah</v>
+        <v>wlt_miguel</v>
       </c>
       <c r="B313">
         <v>2</v>
@@ -4784,7 +4784,7 @@
     </row>
     <row r="314">
       <c r="A314" t="str">
-        <v>guga.llisboa_bjj</v>
+        <v>martta.mariah</v>
       </c>
       <c r="B314">
         <v>2</v>
@@ -4798,21 +4798,21 @@
     </row>
     <row r="315">
       <c r="A315" t="str">
-        <v>gabriel.junior20bjj</v>
+        <v>guga.llisboa_bjj</v>
       </c>
       <c r="B315">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C315">
         <v>0</v>
       </c>
       <c r="D315">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="str">
-        <v>marcosmeireles_pqd_</v>
+        <v>gabriel.junior20bjj</v>
       </c>
       <c r="B316">
         <v>1</v>
@@ -4826,21 +4826,21 @@
     </row>
     <row r="317">
       <c r="A317" t="str">
-        <v>fabi.godooy</v>
+        <v>marcosmeireles_pqd_</v>
       </c>
       <c r="B317">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C317">
         <v>0</v>
       </c>
       <c r="D317">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="str">
-        <v>davicorbella</v>
+        <v>fabi.godooy</v>
       </c>
       <c r="B318">
         <v>2</v>
@@ -4854,7 +4854,7 @@
     </row>
     <row r="319">
       <c r="A319" t="str">
-        <v>joegam3r</v>
+        <v>davicorbella</v>
       </c>
       <c r="B319">
         <v>2</v>
@@ -4868,35 +4868,35 @@
     </row>
     <row r="320">
       <c r="A320" t="str">
-        <v>graalino</v>
+        <v>joegam3r</v>
       </c>
       <c r="B320">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C320">
         <v>0</v>
       </c>
       <c r="D320">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="str">
-        <v>ramanatoscanellibjj</v>
+        <v>graalino</v>
       </c>
       <c r="B321">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C321">
         <v>0</v>
       </c>
       <c r="D321">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="str">
-        <v>auriceliaribeiro_</v>
+        <v>ramanatoscanellibjj</v>
       </c>
       <c r="B322">
         <v>2</v>
@@ -4910,7 +4910,7 @@
     </row>
     <row r="323">
       <c r="A323" t="str">
-        <v>mariabeltapagani</v>
+        <v>auriceliaribeiro_</v>
       </c>
       <c r="B323">
         <v>2</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="324">
       <c r="A324" t="str">
-        <v>craig_cohen1</v>
+        <v>mariabeltapagani</v>
       </c>
       <c r="B324">
         <v>2</v>
@@ -4938,35 +4938,35 @@
     </row>
     <row r="325">
       <c r="A325" t="str">
-        <v>glessios_silva</v>
+        <v>craig_cohen1</v>
       </c>
       <c r="B325">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C325">
         <v>0</v>
       </c>
       <c r="D325">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="str">
-        <v>fabioincalado</v>
+        <v>glessios_silva</v>
       </c>
       <c r="B326">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C326">
         <v>0</v>
       </c>
       <c r="D326">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="str">
-        <v>vanderleiamellogois</v>
+        <v>fabioincalado</v>
       </c>
       <c r="B327">
         <v>2</v>
@@ -4980,91 +4980,91 @@
     </row>
     <row r="328">
       <c r="A328" t="str">
-        <v>pedrinhosbjj</v>
+        <v>vanderleiamellogois</v>
       </c>
       <c r="B328">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C328">
         <v>0</v>
       </c>
       <c r="D328">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="str">
-        <v>_jaquealms</v>
+        <v>pedrinhosbjj</v>
       </c>
       <c r="B329">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C329">
         <v>0</v>
       </c>
       <c r="D329">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="str">
-        <v>caio.fermianoo</v>
+        <v>_jaquealms</v>
       </c>
       <c r="B330">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C330">
         <v>0</v>
       </c>
       <c r="D330">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="str">
-        <v>corrozzzive</v>
+        <v>caio.fermianoo</v>
       </c>
       <c r="B331">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C331">
         <v>0</v>
       </c>
       <c r="D331">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="str">
-        <v>araujojonaspenhade</v>
+        <v>corrozzzive</v>
       </c>
       <c r="B332">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C332">
         <v>0</v>
       </c>
       <c r="D332">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="str">
-        <v>pvd_._dudis</v>
+        <v>araujojonaspenhade</v>
       </c>
       <c r="B333">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C333">
         <v>0</v>
       </c>
       <c r="D333">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="str">
-        <v>duuleitee</v>
+        <v>pvd_._dudis</v>
       </c>
       <c r="B334">
         <v>2</v>
@@ -5078,55 +5078,55 @@
     </row>
     <row r="335">
       <c r="A335" t="str">
-        <v>tatianeaguiarp</v>
+        <v>duuleitee</v>
       </c>
       <c r="B335">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C335">
         <v>0</v>
       </c>
       <c r="D335">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="str">
-        <v>boia_capoeira</v>
+        <v>tatianeaguiarp</v>
       </c>
       <c r="B336">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C336">
         <v>0</v>
       </c>
       <c r="D336">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="str">
-        <v>ismael.marreta_ufc</v>
+        <v>boia_capoeira</v>
       </c>
       <c r="B337">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C337">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D337">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="str">
-        <v>alcateiaartesmarciais</v>
+        <v>ismael.marreta_ufc</v>
       </c>
       <c r="B338">
         <v>1</v>
       </c>
       <c r="C338">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D338">
         <v>1</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="339">
       <c r="A339" t="str">
-        <v>ottonhona</v>
+        <v>alcateiaartesmarciais</v>
       </c>
       <c r="B339">
         <v>1</v>
@@ -5148,49 +5148,49 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>marcov__7</v>
+        <v>ottonhona</v>
       </c>
       <c r="B340">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C340">
         <v>0</v>
       </c>
       <c r="D340">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>anachierico_</v>
+        <v>marcov__7</v>
       </c>
       <c r="B341">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C341">
         <v>0</v>
       </c>
       <c r="D341">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>toraostreet</v>
+        <v>anachierico_</v>
       </c>
       <c r="B342">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C342">
         <v>0</v>
       </c>
       <c r="D342">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="str">
-        <v>bears635</v>
+        <v>toraostreet</v>
       </c>
       <c r="B343">
         <v>2</v>
@@ -5204,35 +5204,35 @@
     </row>
     <row r="344">
       <c r="A344" t="str">
-        <v>suel.f1270</v>
+        <v>bears635</v>
       </c>
       <c r="B344">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C344">
         <v>0</v>
       </c>
       <c r="D344">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="str">
-        <v>murilomuaythai</v>
+        <v>suel.f1270</v>
       </c>
       <c r="B345">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C345">
         <v>0</v>
       </c>
       <c r="D345">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="str">
-        <v>shockmonteiro</v>
+        <v>murilomuaythai</v>
       </c>
       <c r="B346">
         <v>2</v>
@@ -5246,7 +5246,7 @@
     </row>
     <row r="347">
       <c r="A347" t="str">
-        <v>vivi_fitnees</v>
+        <v>shockmonteiro</v>
       </c>
       <c r="B347">
         <v>2</v>
@@ -5260,7 +5260,7 @@
     </row>
     <row r="348">
       <c r="A348" t="str">
-        <v>thiagoxavier13</v>
+        <v>vivi_fitnees</v>
       </c>
       <c r="B348">
         <v>2</v>
@@ -5274,7 +5274,7 @@
     </row>
     <row r="349">
       <c r="A349" t="str">
-        <v>fatima_trindade_</v>
+        <v>thiagoxavier13</v>
       </c>
       <c r="B349">
         <v>2</v>
@@ -5288,21 +5288,21 @@
     </row>
     <row r="350">
       <c r="A350" t="str">
-        <v>gillesarquitetura</v>
+        <v>fatima_trindade_</v>
       </c>
       <c r="B350">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C350">
         <v>0</v>
       </c>
       <c r="D350">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="str">
-        <v>alvestank</v>
+        <v>gillesarquitetura</v>
       </c>
       <c r="B351">
         <v>1</v>
@@ -5316,7 +5316,7 @@
     </row>
     <row r="352">
       <c r="A352" t="str">
-        <v>adevaldojr_</v>
+        <v>alvestank</v>
       </c>
       <c r="B352">
         <v>1</v>
@@ -5330,35 +5330,35 @@
     </row>
     <row r="353">
       <c r="A353" t="str">
-        <v>marciooangelo</v>
+        <v>adevaldojr_</v>
       </c>
       <c r="B353">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C353">
         <v>0</v>
       </c>
       <c r="D353">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="str">
-        <v>manucanecorso.bjj</v>
+        <v>marciooangelo</v>
       </c>
       <c r="B354">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C354">
         <v>0</v>
       </c>
       <c r="D354">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="str">
-        <v>tavin.mendes</v>
+        <v>manucanecorso.bjj</v>
       </c>
       <c r="B355">
         <v>1</v>
@@ -5372,7 +5372,7 @@
     </row>
     <row r="356">
       <c r="A356" t="str">
-        <v>fabiieju</v>
+        <v>tavin.mendes</v>
       </c>
       <c r="B356">
         <v>1</v>
@@ -5386,35 +5386,35 @@
     </row>
     <row r="357">
       <c r="A357" t="str">
-        <v>_jullianadacruz</v>
+        <v>fabiieju</v>
       </c>
       <c r="B357">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C357">
         <v>0</v>
       </c>
       <c r="D357">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="str">
-        <v>joaogagoarta</v>
+        <v>_jullianadacruz</v>
       </c>
       <c r="B358">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C358">
         <v>0</v>
       </c>
       <c r="D358">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="str">
-        <v>adauto2505</v>
+        <v>joaogagoarta</v>
       </c>
       <c r="B359">
         <v>1</v>
@@ -5428,7 +5428,7 @@
     </row>
     <row r="360">
       <c r="A360" t="str">
-        <v>marqueswanderson</v>
+        <v>adauto2505</v>
       </c>
       <c r="B360">
         <v>1</v>
@@ -5442,7 +5442,7 @@
     </row>
     <row r="361">
       <c r="A361" t="str">
-        <v>brcks4breakfast</v>
+        <v>marqueswanderson</v>
       </c>
       <c r="B361">
         <v>1</v>
@@ -5456,7 +5456,7 @@
     </row>
     <row r="362">
       <c r="A362" t="str">
-        <v>murata_profight</v>
+        <v>brcks4breakfast</v>
       </c>
       <c r="B362">
         <v>1</v>
@@ -5470,7 +5470,7 @@
     </row>
     <row r="363">
       <c r="A363" t="str">
-        <v>roger_santosmma</v>
+        <v>murata_profight</v>
       </c>
       <c r="B363">
         <v>1</v>
@@ -5484,7 +5484,7 @@
     </row>
     <row r="364">
       <c r="A364" t="str">
-        <v>zackdos</v>
+        <v>roger_santosmma</v>
       </c>
       <c r="B364">
         <v>1</v>
@@ -5498,7 +5498,7 @@
     </row>
     <row r="365">
       <c r="A365" t="str">
-        <v>david_sfc19</v>
+        <v>zackdos</v>
       </c>
       <c r="B365">
         <v>1</v>
@@ -5512,7 +5512,7 @@
     </row>
     <row r="366">
       <c r="A366" t="str">
-        <v>claudineiscorrea</v>
+        <v>david_sfc19</v>
       </c>
       <c r="B366">
         <v>1</v>
@@ -5526,7 +5526,7 @@
     </row>
     <row r="367">
       <c r="A367" t="str">
-        <v>klebiofernando</v>
+        <v>claudineiscorrea</v>
       </c>
       <c r="B367">
         <v>1</v>
@@ -5540,7 +5540,7 @@
     </row>
     <row r="368">
       <c r="A368" t="str">
-        <v>b.scarvalhooo</v>
+        <v>klebiofernando</v>
       </c>
       <c r="B368">
         <v>1</v>
@@ -5554,35 +5554,35 @@
     </row>
     <row r="369">
       <c r="A369" t="str">
-        <v>biazon87</v>
+        <v>b.scarvalhooo</v>
       </c>
       <c r="B369">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C369">
         <v>0</v>
       </c>
       <c r="D369">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="str">
-        <v>gustavo_brasil09</v>
+        <v>biazon87</v>
       </c>
       <c r="B370">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C370">
         <v>0</v>
       </c>
       <c r="D370">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="str">
-        <v>fabiocesar_1997</v>
+        <v>gustavo_brasil09</v>
       </c>
       <c r="B371">
         <v>1</v>
@@ -5596,7 +5596,7 @@
     </row>
     <row r="372">
       <c r="A372" t="str">
-        <v>josuemoita1205</v>
+        <v>fabiocesar_1997</v>
       </c>
       <c r="B372">
         <v>1</v>
@@ -5610,7 +5610,7 @@
     </row>
     <row r="373">
       <c r="A373" t="str">
-        <v>milton_pitbull</v>
+        <v>josuemoita1205</v>
       </c>
       <c r="B373">
         <v>1</v>
@@ -5624,7 +5624,7 @@
     </row>
     <row r="374">
       <c r="A374" t="str">
-        <v>enzo.gsilva_</v>
+        <v>milton_pitbull</v>
       </c>
       <c r="B374">
         <v>1</v>
@@ -5638,7 +5638,7 @@
     </row>
     <row r="375">
       <c r="A375" t="str">
-        <v>raffaoito4</v>
+        <v>enzo.gsilva_</v>
       </c>
       <c r="B375">
         <v>1</v>
@@ -5652,7 +5652,7 @@
     </row>
     <row r="376">
       <c r="A376" t="str">
-        <v>rl_figo</v>
+        <v>raffaoito4</v>
       </c>
       <c r="B376">
         <v>1</v>
@@ -5666,7 +5666,7 @@
     </row>
     <row r="377">
       <c r="A377" t="str">
-        <v>ultraperegrinospelomundo</v>
+        <v>rl_figo</v>
       </c>
       <c r="B377">
         <v>1</v>
@@ -5680,105 +5680,105 @@
     </row>
     <row r="378">
       <c r="A378" t="str">
-        <v>dr.daniloduartefisio</v>
+        <v>ultraperegrinospelomundo</v>
       </c>
       <c r="B378">
         <v>1</v>
       </c>
       <c r="C378">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D378">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="str">
-        <v>pablo_bvg</v>
+        <v>dr.daniloduartefisio</v>
       </c>
       <c r="B379">
         <v>1</v>
       </c>
       <c r="C379">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D379">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="str">
-        <v>djsagatoficial</v>
+        <v>pablo_bvg</v>
       </c>
       <c r="B380">
         <v>1</v>
       </c>
       <c r="C380">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D380">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="str">
-        <v>marceloscorzato</v>
+        <v>djsagatoficial</v>
       </c>
       <c r="B381">
         <v>1</v>
       </c>
       <c r="C381">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D381">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="str">
-        <v>sergio_alves_bjj</v>
+        <v>marceloscorzato</v>
       </c>
       <c r="B382">
         <v>1</v>
       </c>
       <c r="C382">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D382">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="str">
-        <v>pedro_pavin_</v>
+        <v>sergio_alves_bjj</v>
       </c>
       <c r="B383">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C383">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D383">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="str">
-        <v>treinaadorrafael</v>
+        <v>pedro_pavin_</v>
       </c>
       <c r="B384">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C384">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D384">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="str">
-        <v>estevaotoledo</v>
+        <v>treinaadorrafael</v>
       </c>
       <c r="B385">
         <v>1</v>
@@ -5792,21 +5792,21 @@
     </row>
     <row r="386">
       <c r="A386" t="str">
-        <v>aida_dos_sonhos</v>
+        <v>estevaotoledo</v>
       </c>
       <c r="B386">
         <v>1</v>
       </c>
       <c r="C386">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D386">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="str">
-        <v>kael_lyto</v>
+        <v>aida_dos_sonhos</v>
       </c>
       <c r="B387">
         <v>1</v>
@@ -5815,18 +5815,18 @@
         <v>2</v>
       </c>
       <c r="D387">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="str">
-        <v>yurimartins1_</v>
+        <v>kael_lyto</v>
       </c>
       <c r="B388">
         <v>1</v>
       </c>
       <c r="C388">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D388">
         <v>0</v>
@@ -5834,7 +5834,7 @@
     </row>
     <row r="389">
       <c r="A389" t="str">
-        <v>maria.pereiradeoliveira.5283</v>
+        <v>yurimartins1_</v>
       </c>
       <c r="B389">
         <v>1</v>
@@ -5848,7 +5848,7 @@
     </row>
     <row r="390">
       <c r="A390" t="str">
-        <v>matheusteodoro_1</v>
+        <v>maria.pereiradeoliveira.5283</v>
       </c>
       <c r="B390">
         <v>1</v>
@@ -5862,7 +5862,7 @@
     </row>
     <row r="391">
       <c r="A391" t="str">
-        <v>kawannsenaboxe</v>
+        <v>matheusteodoro_1</v>
       </c>
       <c r="B391">
         <v>1</v>
@@ -5876,7 +5876,7 @@
     </row>
     <row r="392">
       <c r="A392" t="str">
-        <v>guiiviieira_</v>
+        <v>kawannsenaboxe</v>
       </c>
       <c r="B392">
         <v>1</v>
@@ -5890,7 +5890,7 @@
     </row>
     <row r="393">
       <c r="A393" t="str">
-        <v>cshigueo</v>
+        <v>guiiviieira_</v>
       </c>
       <c r="B393">
         <v>1</v>
@@ -5904,7 +5904,7 @@
     </row>
     <row r="394">
       <c r="A394" t="str">
-        <v>vitorhugo_vtr</v>
+        <v>cshigueo</v>
       </c>
       <c r="B394">
         <v>1</v>
@@ -5918,7 +5918,7 @@
     </row>
     <row r="395">
       <c r="A395" t="str">
-        <v>danni_goncalves12</v>
+        <v>vitorhugo_vtr</v>
       </c>
       <c r="B395">
         <v>1</v>
@@ -5932,7 +5932,7 @@
     </row>
     <row r="396">
       <c r="A396" t="str">
-        <v>mttsm._</v>
+        <v>danni_goncalves12</v>
       </c>
       <c r="B396">
         <v>1</v>
@@ -5946,7 +5946,7 @@
     </row>
     <row r="397">
       <c r="A397" t="str">
-        <v>andrealvess02</v>
+        <v>mttsm._</v>
       </c>
       <c r="B397">
         <v>1</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="398">
       <c r="A398" t="str">
-        <v>gildojiu</v>
+        <v>andrealvess02</v>
       </c>
       <c r="B398">
         <v>1</v>
@@ -5974,13 +5974,13 @@
     </row>
     <row r="399">
       <c r="A399" t="str">
-        <v>fagnerosensei</v>
+        <v>gildojiu</v>
       </c>
       <c r="B399">
         <v>1</v>
       </c>
       <c r="C399">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D399">
         <v>0</v>
@@ -5988,7 +5988,7 @@
     </row>
     <row r="400">
       <c r="A400" t="str">
-        <v>flavio.dequeiroz</v>
+        <v>fagnerosensei</v>
       </c>
       <c r="B400">
         <v>1</v>
@@ -6002,13 +6002,13 @@
     </row>
     <row r="401">
       <c r="A401" t="str">
-        <v>030sami</v>
+        <v>flavio.dequeiroz</v>
       </c>
       <c r="B401">
         <v>1</v>
       </c>
       <c r="C401">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D401">
         <v>0</v>
@@ -6016,35 +6016,35 @@
     </row>
     <row r="402">
       <c r="A402" t="str">
-        <v>giulia.fasolato</v>
+        <v>030sami</v>
       </c>
       <c r="B402">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C402">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D402">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="str">
-        <v>selipereirapereira</v>
+        <v>giulia.fasolato</v>
       </c>
       <c r="B403">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C403">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D403">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="str">
-        <v>d.silvamma</v>
+        <v>selipereirapereira</v>
       </c>
       <c r="B404">
         <v>1</v>
@@ -6058,7 +6058,7 @@
     </row>
     <row r="405">
       <c r="A405" t="str">
-        <v>kalindrafaria</v>
+        <v>d.silvamma</v>
       </c>
       <c r="B405">
         <v>1</v>
@@ -6072,35 +6072,35 @@
     </row>
     <row r="406">
       <c r="A406" t="str">
-        <v>igorsiqueiramma57</v>
+        <v>kalindrafaria</v>
       </c>
       <c r="B406">
         <v>1</v>
       </c>
       <c r="C406">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D406">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="str">
-        <v>oniszczuk_ko</v>
+        <v>igorsiqueiramma57</v>
       </c>
       <c r="B407">
         <v>1</v>
       </c>
       <c r="C407">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D407">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="str">
-        <v>andreibjj</v>
+        <v>oniszczuk_ko</v>
       </c>
       <c r="B408">
         <v>1</v>
@@ -6114,7 +6114,7 @@
     </row>
     <row r="409">
       <c r="A409" t="str">
-        <v>manoelwilliamdejesus</v>
+        <v>andreibjj</v>
       </c>
       <c r="B409">
         <v>1</v>
@@ -6128,7 +6128,7 @@
     </row>
     <row r="410">
       <c r="A410" t="str">
-        <v>killemquick</v>
+        <v>manoelwilliamdejesus</v>
       </c>
       <c r="B410">
         <v>1</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="411">
       <c r="A411" t="str">
-        <v>chuck_tlp</v>
+        <v>killemquick</v>
       </c>
       <c r="B411">
         <v>1</v>
@@ -6156,7 +6156,7 @@
     </row>
     <row r="412">
       <c r="A412" t="str">
-        <v>henriquemmunhoz</v>
+        <v>chuck_tlp</v>
       </c>
       <c r="B412">
         <v>1</v>
@@ -6170,7 +6170,7 @@
     </row>
     <row r="413">
       <c r="A413" t="str">
-        <v>flavio_tuba8</v>
+        <v>henriquemmunhoz</v>
       </c>
       <c r="B413">
         <v>1</v>
@@ -6184,13 +6184,13 @@
     </row>
     <row r="414">
       <c r="A414" t="str">
-        <v>koliseu.br</v>
+        <v>flavio_tuba8</v>
       </c>
       <c r="B414">
         <v>1</v>
       </c>
       <c r="C414">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D414">
         <v>0</v>
@@ -6198,13 +6198,13 @@
     </row>
     <row r="415">
       <c r="A415" t="str">
-        <v>marianappedro</v>
+        <v>koliseu.br</v>
       </c>
       <c r="B415">
         <v>1</v>
       </c>
       <c r="C415">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D415">
         <v>0</v>
@@ -6212,13 +6212,13 @@
     </row>
     <row r="416">
       <c r="A416" t="str">
-        <v>cathya_ferreira</v>
+        <v>marianappedro</v>
       </c>
       <c r="B416">
         <v>1</v>
       </c>
       <c r="C416">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D416">
         <v>0</v>
@@ -6226,13 +6226,13 @@
     </row>
     <row r="417">
       <c r="A417" t="str">
-        <v>plmoreiraz</v>
+        <v>cathya_ferreira</v>
       </c>
       <c r="B417">
         <v>1</v>
       </c>
       <c r="C417">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D417">
         <v>0</v>
@@ -6240,7 +6240,7 @@
     </row>
     <row r="418">
       <c r="A418" t="str">
-        <v>morena_ramos</v>
+        <v>plmoreiraz</v>
       </c>
       <c r="B418">
         <v>1</v>
@@ -6254,21 +6254,21 @@
     </row>
     <row r="419">
       <c r="A419" t="str">
-        <v>_pedro0h</v>
+        <v>morena_ramos</v>
       </c>
       <c r="B419">
         <v>1</v>
       </c>
       <c r="C419">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D419">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="str">
-        <v>percepcar</v>
+        <v>_pedro0h</v>
       </c>
       <c r="B420">
         <v>1</v>
@@ -6277,12 +6277,12 @@
         <v>1</v>
       </c>
       <c r="D420">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="str">
-        <v>ojaimerocha</v>
+        <v>percepcar</v>
       </c>
       <c r="B421">
         <v>1</v>
@@ -6296,7 +6296,7 @@
     </row>
     <row r="422">
       <c r="A422" t="str">
-        <v>yeslifeacademia</v>
+        <v>ojaimerocha</v>
       </c>
       <c r="B422">
         <v>1</v>
@@ -6310,7 +6310,7 @@
     </row>
     <row r="423">
       <c r="A423" t="str">
-        <v>edergama.mma</v>
+        <v>yeslifeacademia</v>
       </c>
       <c r="B423">
         <v>1</v>
@@ -6324,7 +6324,7 @@
     </row>
     <row r="424">
       <c r="A424" t="str">
-        <v>eliandropires</v>
+        <v>edergama.mma</v>
       </c>
       <c r="B424">
         <v>1</v>
@@ -6338,7 +6338,7 @@
     </row>
     <row r="425">
       <c r="A425" t="str">
-        <v>_gabrielpego</v>
+        <v>eliandropires</v>
       </c>
       <c r="B425">
         <v>1</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="426">
       <c r="A426" t="str">
-        <v>eusoufernandosaito</v>
+        <v>_gabrielpego</v>
       </c>
       <c r="B426">
         <v>1</v>
@@ -6366,7 +6366,7 @@
     </row>
     <row r="427">
       <c r="A427" t="str">
-        <v>motumbo_team</v>
+        <v>eusoufernandosaito</v>
       </c>
       <c r="B427">
         <v>1</v>
@@ -6380,7 +6380,7 @@
     </row>
     <row r="428">
       <c r="A428" t="str">
-        <v>beabmendes_</v>
+        <v>motumbo_team</v>
       </c>
       <c r="B428">
         <v>1</v>
@@ -6394,7 +6394,7 @@
     </row>
     <row r="429">
       <c r="A429" t="str">
-        <v>jenifer.ciborg</v>
+        <v>beabmendes_</v>
       </c>
       <c r="B429">
         <v>1</v>
@@ -6408,7 +6408,7 @@
     </row>
     <row r="430">
       <c r="A430" t="str">
-        <v>felipefrancoufc</v>
+        <v>jenifer.ciborg</v>
       </c>
       <c r="B430">
         <v>1</v>
@@ -6422,7 +6422,7 @@
     </row>
     <row r="431">
       <c r="A431" t="str">
-        <v>leonardoo_paixao</v>
+        <v>felipefrancoufc</v>
       </c>
       <c r="B431">
         <v>1</v>
@@ -6436,35 +6436,35 @@
     </row>
     <row r="432">
       <c r="A432" t="str">
-        <v>antonioemanuel.13</v>
+        <v>leonardoo_paixao</v>
       </c>
       <c r="B432">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C432">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D432">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="str">
-        <v>gasparjr1983</v>
+        <v>antonioemanuel.13</v>
       </c>
       <c r="B433">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C433">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D433">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="str">
-        <v>magnoddias</v>
+        <v>gasparjr1983</v>
       </c>
       <c r="B434">
         <v>1</v>
@@ -6478,7 +6478,7 @@
     </row>
     <row r="435">
       <c r="A435" t="str">
-        <v>ballestarbosa</v>
+        <v>magnoddias</v>
       </c>
       <c r="B435">
         <v>1</v>
@@ -6492,7 +6492,7 @@
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>marcioticotobarbosa</v>
+        <v>ballestarbosa</v>
       </c>
       <c r="B436">
         <v>1</v>
@@ -6506,7 +6506,7 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>renan.dniz</v>
+        <v>marcioticotobarbosa</v>
       </c>
       <c r="B437">
         <v>1</v>
@@ -6520,7 +6520,7 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>nunesjanjacomo</v>
+        <v>renan.dniz</v>
       </c>
       <c r="B438">
         <v>1</v>
@@ -6534,7 +6534,7 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>eumarianojr</v>
+        <v>nunesjanjacomo</v>
       </c>
       <c r="B439">
         <v>1</v>
@@ -6548,7 +6548,7 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>chillyfit007</v>
+        <v>eumarianojr</v>
       </c>
       <c r="B440">
         <v>1</v>
@@ -6562,7 +6562,7 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>george.laroque</v>
+        <v>chillyfit007</v>
       </c>
       <c r="B441">
         <v>1</v>
@@ -6576,41 +6576,41 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>dudaadantass</v>
+        <v>george.laroque</v>
       </c>
       <c r="B442">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C442">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D442">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>cassiosants__</v>
+        <v>dudaadantass</v>
       </c>
       <c r="B443">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C443">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D443">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>mth_fernandes031</v>
+        <v>cassiosants__</v>
       </c>
       <c r="B444">
         <v>1</v>
       </c>
       <c r="C444">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D444">
         <v>0</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>jhoninhaoficial031</v>
+        <v>mth_fernandes031</v>
       </c>
       <c r="B445">
         <v>1</v>
@@ -6632,7 +6632,7 @@
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>bigjota.music</v>
+        <v>jhoninhaoficial031</v>
       </c>
       <c r="B446">
         <v>1</v>
@@ -6646,7 +6646,7 @@
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>lay_roqs</v>
+        <v>bigjota.music</v>
       </c>
       <c r="B447">
         <v>1</v>
@@ -6660,7 +6660,7 @@
     </row>
     <row r="448">
       <c r="A448" t="str">
-        <v>gabrielsilva_mma</v>
+        <v>lay_roqs</v>
       </c>
       <c r="B448">
         <v>1</v>
@@ -6674,7 +6674,7 @@
     </row>
     <row r="449">
       <c r="A449" t="str">
-        <v>igorfso_</v>
+        <v>gabrielsilva_mma</v>
       </c>
       <c r="B449">
         <v>1</v>
@@ -6688,7 +6688,7 @@
     </row>
     <row r="450">
       <c r="A450" t="str">
-        <v>gutocriativo</v>
+        <v>igorfso_</v>
       </c>
       <c r="B450">
         <v>1</v>
@@ -6702,7 +6702,7 @@
     </row>
     <row r="451">
       <c r="A451" t="str">
-        <v>leosacraa</v>
+        <v>gutocriativo</v>
       </c>
       <c r="B451">
         <v>1</v>
@@ -6716,7 +6716,7 @@
     </row>
     <row r="452">
       <c r="A452" t="str">
-        <v>vinyrodriguesoficial</v>
+        <v>leosacraa</v>
       </c>
       <c r="B452">
         <v>1</v>
@@ -6730,7 +6730,7 @@
     </row>
     <row r="453">
       <c r="A453" t="str">
-        <v>olga.oliveira013</v>
+        <v>vinyrodriguesoficial</v>
       </c>
       <c r="B453">
         <v>1</v>
@@ -6744,7 +6744,7 @@
     </row>
     <row r="454">
       <c r="A454" t="str">
-        <v>leandro_motiv4</v>
+        <v>olga.oliveira013</v>
       </c>
       <c r="B454">
         <v>1</v>
@@ -6758,7 +6758,7 @@
     </row>
     <row r="455">
       <c r="A455" t="str">
-        <v>andrejetx</v>
+        <v>leandro_motiv4</v>
       </c>
       <c r="B455">
         <v>1</v>
@@ -6772,7 +6772,7 @@
     </row>
     <row r="456">
       <c r="A456" t="str">
-        <v>phillipe.harry</v>
+        <v>andrejetx</v>
       </c>
       <c r="B456">
         <v>1</v>
@@ -6786,7 +6786,7 @@
     </row>
     <row r="457">
       <c r="A457" t="str">
-        <v>andre.legendre.10</v>
+        <v>phillipe.harry</v>
       </c>
       <c r="B457">
         <v>1</v>
@@ -6800,7 +6800,7 @@
     </row>
     <row r="458">
       <c r="A458" t="str">
-        <v>wagner_alexandre_w_a</v>
+        <v>andre.legendre.10</v>
       </c>
       <c r="B458">
         <v>1</v>
@@ -6814,13 +6814,13 @@
     </row>
     <row r="459">
       <c r="A459" t="str">
-        <v>rafaela_duaartee</v>
+        <v>wagner_alexandre_w_a</v>
       </c>
       <c r="B459">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C459">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D459">
         <v>0</v>
@@ -6828,13 +6828,13 @@
     </row>
     <row r="460">
       <c r="A460" t="str">
-        <v>cezary_oleksiejczuk</v>
+        <v>rafaela_duaartee</v>
       </c>
       <c r="B460">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C460">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D460">
         <v>0</v>
@@ -6842,7 +6842,7 @@
     </row>
     <row r="461">
       <c r="A461" t="str">
-        <v>_alcantara.bru</v>
+        <v>cezary_oleksiejczuk</v>
       </c>
       <c r="B461">
         <v>1</v>
@@ -6856,7 +6856,7 @@
     </row>
     <row r="462">
       <c r="A462" t="str">
-        <v>arthurhenrique.sx</v>
+        <v>_alcantara.bru</v>
       </c>
       <c r="B462">
         <v>1</v>
@@ -6870,7 +6870,7 @@
     </row>
     <row r="463">
       <c r="A463" t="str">
-        <v>fran.ruys</v>
+        <v>arthurhenrique.sx</v>
       </c>
       <c r="B463">
         <v>1</v>
@@ -6884,7 +6884,7 @@
     </row>
     <row r="464">
       <c r="A464" t="str">
-        <v>vitor_buck</v>
+        <v>fran.ruys</v>
       </c>
       <c r="B464">
         <v>1</v>
@@ -6898,7 +6898,7 @@
     </row>
     <row r="465">
       <c r="A465" t="str">
-        <v>mr__rlk01</v>
+        <v>vitor_buck</v>
       </c>
       <c r="B465">
         <v>1</v>
@@ -6912,7 +6912,7 @@
     </row>
     <row r="466">
       <c r="A466" t="str">
-        <v>_lsanchess_</v>
+        <v>mr__rlk01</v>
       </c>
       <c r="B466">
         <v>1</v>
@@ -6926,7 +6926,7 @@
     </row>
     <row r="467">
       <c r="A467" t="str">
-        <v>gabriel_trevelin</v>
+        <v>_lsanchess_</v>
       </c>
       <c r="B467">
         <v>1</v>
@@ -6940,7 +6940,7 @@
     </row>
     <row r="468">
       <c r="A468" t="str">
-        <v>danlouiz.jj</v>
+        <v>gabriel_trevelin</v>
       </c>
       <c r="B468">
         <v>1</v>
@@ -6954,7 +6954,7 @@
     </row>
     <row r="469">
       <c r="A469" t="str">
-        <v>camii_bonfim</v>
+        <v>danlouiz.jj</v>
       </c>
       <c r="B469">
         <v>1</v>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="470">
       <c r="A470" t="str">
-        <v>flazuera14</v>
+        <v>camii_bonfim</v>
       </c>
       <c r="B470">
         <v>1</v>
@@ -6982,7 +6982,7 @@
     </row>
     <row r="471">
       <c r="A471" t="str">
-        <v>gilberto_7606</v>
+        <v>flazuera14</v>
       </c>
       <c r="B471">
         <v>1</v>
@@ -6996,7 +6996,7 @@
     </row>
     <row r="472">
       <c r="A472" t="str">
-        <v>aloirmarcal</v>
+        <v>gilberto_7606</v>
       </c>
       <c r="B472">
         <v>1</v>
@@ -7010,7 +7010,7 @@
     </row>
     <row r="473">
       <c r="A473" t="str">
-        <v>_fernunes</v>
+        <v>aloirmarcal</v>
       </c>
       <c r="B473">
         <v>1</v>
@@ -7024,7 +7024,7 @@
     </row>
     <row r="474">
       <c r="A474" t="str">
-        <v>andre_alcausa</v>
+        <v>_fernunes</v>
       </c>
       <c r="B474">
         <v>1</v>
@@ -7038,7 +7038,7 @@
     </row>
     <row r="475">
       <c r="A475" t="str">
-        <v>judadany</v>
+        <v>andre_alcausa</v>
       </c>
       <c r="B475">
         <v>1</v>
@@ -7052,7 +7052,7 @@
     </row>
     <row r="476">
       <c r="A476" t="str">
-        <v>pativinisf</v>
+        <v>judadany</v>
       </c>
       <c r="B476">
         <v>1</v>
@@ -7066,7 +7066,7 @@
     </row>
     <row r="477">
       <c r="A477" t="str">
-        <v>guilhermeefelix__</v>
+        <v>pativinisf</v>
       </c>
       <c r="B477">
         <v>1</v>
@@ -7080,7 +7080,7 @@
     </row>
     <row r="478">
       <c r="A478" t="str">
-        <v>___neller</v>
+        <v>guilhermeefelix__</v>
       </c>
       <c r="B478">
         <v>1</v>
@@ -7094,7 +7094,7 @@
     </row>
     <row r="479">
       <c r="A479" t="str">
-        <v>pietroshz</v>
+        <v>___neller</v>
       </c>
       <c r="B479">
         <v>1</v>
@@ -7108,7 +7108,7 @@
     </row>
     <row r="480">
       <c r="A480" t="str">
-        <v>gabicardoson</v>
+        <v>pietroshz</v>
       </c>
       <c r="B480">
         <v>1</v>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="481">
       <c r="A481" t="str">
-        <v>cami.terra_</v>
+        <v>gabicardoson</v>
       </c>
       <c r="B481">
         <v>1</v>
@@ -7136,7 +7136,7 @@
     </row>
     <row r="482">
       <c r="A482" t="str">
-        <v>_rayysp</v>
+        <v>cami.terra_</v>
       </c>
       <c r="B482">
         <v>1</v>
@@ -7150,7 +7150,7 @@
     </row>
     <row r="483">
       <c r="A483" t="str">
-        <v>_puroosso88</v>
+        <v>_rayysp</v>
       </c>
       <c r="B483">
         <v>1</v>
@@ -7164,7 +7164,7 @@
     </row>
     <row r="484">
       <c r="A484" t="str">
-        <v>navarro_9430</v>
+        <v>_puroosso88</v>
       </c>
       <c r="B484">
         <v>1</v>
@@ -7178,7 +7178,7 @@
     </row>
     <row r="485">
       <c r="A485" t="str">
-        <v>miguelrodriguesbjj</v>
+        <v>navarro_9430</v>
       </c>
       <c r="B485">
         <v>1</v>
@@ -7192,7 +7192,7 @@
     </row>
     <row r="486">
       <c r="A486" t="str">
-        <v>benivalentinn</v>
+        <v>miguelrodriguesbjj</v>
       </c>
       <c r="B486">
         <v>1</v>
@@ -7206,7 +7206,7 @@
     </row>
     <row r="487">
       <c r="A487" t="str">
-        <v>alternativaremocoes</v>
+        <v>benivalentinn</v>
       </c>
       <c r="B487">
         <v>1</v>
@@ -7220,7 +7220,7 @@
     </row>
     <row r="488">
       <c r="A488" t="str">
-        <v>saj_photo_miami</v>
+        <v>alternativaremocoes</v>
       </c>
       <c r="B488">
         <v>1</v>
@@ -7234,7 +7234,7 @@
     </row>
     <row r="489">
       <c r="A489" t="str">
-        <v>draanapaulaponceano</v>
+        <v>saj_photo_miami</v>
       </c>
       <c r="B489">
         <v>1</v>
@@ -7248,7 +7248,7 @@
     </row>
     <row r="490">
       <c r="A490" t="str">
-        <v>charlesanthony2466</v>
+        <v>draanapaulaponceano</v>
       </c>
       <c r="B490">
         <v>1</v>
@@ -7262,7 +7262,7 @@
     </row>
     <row r="491">
       <c r="A491" t="str">
-        <v>maryanagandra</v>
+        <v>charlesanthony2466</v>
       </c>
       <c r="B491">
         <v>1</v>
@@ -7276,7 +7276,7 @@
     </row>
     <row r="492">
       <c r="A492" t="str">
-        <v>xavyeroficial</v>
+        <v>maryanagandra</v>
       </c>
       <c r="B492">
         <v>1</v>
@@ -7290,7 +7290,7 @@
     </row>
     <row r="493">
       <c r="A493" t="str">
-        <v>geraldocnetomma</v>
+        <v>xavyeroficial</v>
       </c>
       <c r="B493">
         <v>1</v>
@@ -7304,7 +7304,7 @@
     </row>
     <row r="494">
       <c r="A494" t="str">
-        <v>katiaecarreraf</v>
+        <v>geraldocnetomma</v>
       </c>
       <c r="B494">
         <v>1</v>
@@ -7318,13 +7318,13 @@
     </row>
     <row r="495">
       <c r="A495" t="str">
-        <v>marinealcausa</v>
+        <v>katiaecarreraf</v>
       </c>
       <c r="B495">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C495">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D495">
         <v>0</v>
@@ -7332,13 +7332,13 @@
     </row>
     <row r="496">
       <c r="A496" t="str">
-        <v>artemio_bjj</v>
+        <v>marinealcausa</v>
       </c>
       <c r="B496">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C496">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D496">
         <v>0</v>
@@ -7346,7 +7346,7 @@
     </row>
     <row r="497">
       <c r="A497" t="str">
-        <v>isaac.bah_starinazzo</v>
+        <v>artemio_bjj</v>
       </c>
       <c r="B497">
         <v>1</v>
@@ -7360,7 +7360,7 @@
     </row>
     <row r="498">
       <c r="A498" t="str">
-        <v>carolinne.xwp</v>
+        <v>isaac.bah_starinazzo</v>
       </c>
       <c r="B498">
         <v>1</v>
@@ -7374,7 +7374,7 @@
     </row>
     <row r="499">
       <c r="A499" t="str">
-        <v>yan_touro_.7766</v>
+        <v>carolinne.xwp</v>
       </c>
       <c r="B499">
         <v>1</v>
@@ -7388,7 +7388,7 @@
     </row>
     <row r="500">
       <c r="A500" t="str">
-        <v>codasqueves</v>
+        <v>yan_touro_.7766</v>
       </c>
       <c r="B500">
         <v>1</v>
@@ -7402,7 +7402,7 @@
     </row>
     <row r="501">
       <c r="A501" t="str">
-        <v>lara.rpr</v>
+        <v>codasqueves</v>
       </c>
       <c r="B501">
         <v>1</v>
@@ -7416,7 +7416,7 @@
     </row>
     <row r="502">
       <c r="A502" t="str">
-        <v>brothers_of_life</v>
+        <v>lara.rpr</v>
       </c>
       <c r="B502">
         <v>1</v>
@@ -7430,7 +7430,7 @@
     </row>
     <row r="503">
       <c r="A503" t="str">
-        <v>minotaurinho</v>
+        <v>brothers_of_life</v>
       </c>
       <c r="B503">
         <v>1</v>
@@ -7444,7 +7444,7 @@
     </row>
     <row r="504">
       <c r="A504" t="str">
-        <v>teacherthalesyouplus</v>
+        <v>minotaurinho</v>
       </c>
       <c r="B504">
         <v>1</v>
@@ -7458,7 +7458,7 @@
     </row>
     <row r="505">
       <c r="A505" t="str">
-        <v>anahangelica</v>
+        <v>teacherthalesyouplus</v>
       </c>
       <c r="B505">
         <v>1</v>
@@ -7472,7 +7472,7 @@
     </row>
     <row r="506">
       <c r="A506" t="str">
-        <v>frankikolimabjj</v>
+        <v>anahangelica</v>
       </c>
       <c r="B506">
         <v>1</v>
@@ -7486,7 +7486,7 @@
     </row>
     <row r="507">
       <c r="A507" t="str">
-        <v>euvitormirandaa</v>
+        <v>frankikolimabjj</v>
       </c>
       <c r="B507">
         <v>1</v>
@@ -7500,7 +7500,7 @@
     </row>
     <row r="508">
       <c r="A508" t="str">
-        <v>gabesantos.13</v>
+        <v>euvitormirandaa</v>
       </c>
       <c r="B508">
         <v>1</v>
@@ -7514,7 +7514,7 @@
     </row>
     <row r="509">
       <c r="A509" t="str">
-        <v>mariaraimundad940</v>
+        <v>gabesantos.13</v>
       </c>
       <c r="B509">
         <v>1</v>
@@ -7528,7 +7528,7 @@
     </row>
     <row r="510">
       <c r="A510" t="str">
-        <v>pdfiv</v>
+        <v>mariaraimundad940</v>
       </c>
       <c r="B510">
         <v>1</v>
@@ -7542,7 +7542,7 @@
     </row>
     <row r="511">
       <c r="A511" t="str">
-        <v>_eliasffx</v>
+        <v>pdfiv</v>
       </c>
       <c r="B511">
         <v>1</v>
@@ -7556,7 +7556,7 @@
     </row>
     <row r="512">
       <c r="A512" t="str">
-        <v>tonketjudes</v>
+        <v>_eliasffx</v>
       </c>
       <c r="B512">
         <v>1</v>
@@ -7570,7 +7570,7 @@
     </row>
     <row r="513">
       <c r="A513" t="str">
-        <v>gandra.julya</v>
+        <v>tonketjudes</v>
       </c>
       <c r="B513">
         <v>1</v>
@@ -7584,7 +7584,7 @@
     </row>
     <row r="514">
       <c r="A514" t="str">
-        <v>azulcapoeirabjj</v>
+        <v>gandra.julya</v>
       </c>
       <c r="B514">
         <v>1</v>
@@ -7598,7 +7598,7 @@
     </row>
     <row r="515">
       <c r="A515" t="str">
-        <v>espacomarcialino</v>
+        <v>azulcapoeirabjj</v>
       </c>
       <c r="B515">
         <v>1</v>
@@ -7612,7 +7612,7 @@
     </row>
     <row r="516">
       <c r="A516" t="str">
-        <v>andreiaatleta</v>
+        <v>espacomarcialino</v>
       </c>
       <c r="B516">
         <v>1</v>
@@ -7626,7 +7626,7 @@
     </row>
     <row r="517">
       <c r="A517" t="str">
-        <v>turmanmma</v>
+        <v>andreiaatleta</v>
       </c>
       <c r="B517">
         <v>1</v>
@@ -7640,7 +7640,7 @@
     </row>
     <row r="518">
       <c r="A518" t="str">
-        <v>drfelipeoliveira_adv</v>
+        <v>turmanmma</v>
       </c>
       <c r="B518">
         <v>1</v>
@@ -7654,7 +7654,7 @@
     </row>
     <row r="519">
       <c r="A519" t="str">
-        <v>muriloo__ferreira</v>
+        <v>drfelipeoliveira_adv</v>
       </c>
       <c r="B519">
         <v>1</v>
@@ -7668,7 +7668,7 @@
     </row>
     <row r="520">
       <c r="A520" t="str">
-        <v>sidneibabu</v>
+        <v>muriloo__ferreira</v>
       </c>
       <c r="B520">
         <v>1</v>
@@ -7682,7 +7682,7 @@
     </row>
     <row r="521">
       <c r="A521" t="str">
-        <v>allisonestuchi_fisioterapeuta</v>
+        <v>sidneibabu</v>
       </c>
       <c r="B521">
         <v>1</v>
@@ -7696,7 +7696,7 @@
     </row>
     <row r="522">
       <c r="A522" t="str">
-        <v>nutrivan.alves</v>
+        <v>allisonestuchi_fisioterapeuta</v>
       </c>
       <c r="B522">
         <v>1</v>
@@ -7710,7 +7710,7 @@
     </row>
     <row r="523">
       <c r="A523" t="str">
-        <v>valqsm</v>
+        <v>nutrivan.alves</v>
       </c>
       <c r="B523">
         <v>1</v>
@@ -7724,7 +7724,7 @@
     </row>
     <row r="524">
       <c r="A524" t="str">
-        <v>selma.ribeirotr</v>
+        <v>valqsm</v>
       </c>
       <c r="B524">
         <v>1</v>
@@ -7738,7 +7738,7 @@
     </row>
     <row r="525">
       <c r="A525" t="str">
-        <v>eu_felipe_leite</v>
+        <v>selma.ribeirotr</v>
       </c>
       <c r="B525">
         <v>1</v>
@@ -7752,7 +7752,7 @@
     </row>
     <row r="526">
       <c r="A526" t="str">
-        <v>do_caex_wandel</v>
+        <v>eu_felipe_leite</v>
       </c>
       <c r="B526">
         <v>1</v>
@@ -7766,7 +7766,7 @@
     </row>
     <row r="527">
       <c r="A527" t="str">
-        <v>jack_hashimoto</v>
+        <v>do_caex_wandel</v>
       </c>
       <c r="B527">
         <v>1</v>
@@ -7780,7 +7780,7 @@
     </row>
     <row r="528">
       <c r="A528" t="str">
-        <v>luhluhm</v>
+        <v>jack_hashimoto</v>
       </c>
       <c r="B528">
         <v>1</v>
@@ -7794,7 +7794,7 @@
     </row>
     <row r="529">
       <c r="A529" t="str">
-        <v>donrey_42</v>
+        <v>luhluhm</v>
       </c>
       <c r="B529">
         <v>1</v>
@@ -7808,7 +7808,7 @@
     </row>
     <row r="530">
       <c r="A530" t="str">
-        <v>lumarasantosjj</v>
+        <v>donrey_42</v>
       </c>
       <c r="B530">
         <v>1</v>
@@ -7822,7 +7822,7 @@
     </row>
     <row r="531">
       <c r="A531" t="str">
-        <v>andre_luizdj</v>
+        <v>lumarasantosjj</v>
       </c>
       <c r="B531">
         <v>1</v>
@@ -7836,7 +7836,7 @@
     </row>
     <row r="532">
       <c r="A532" t="str">
-        <v>itsmayraregina</v>
+        <v>andre_luizdj</v>
       </c>
       <c r="B532">
         <v>1</v>
@@ -7850,7 +7850,7 @@
     </row>
     <row r="533">
       <c r="A533" t="str">
-        <v>personalmaju</v>
+        <v>itsmayraregina</v>
       </c>
       <c r="B533">
         <v>1</v>
@@ -7864,7 +7864,7 @@
     </row>
     <row r="534">
       <c r="A534" t="str">
-        <v>fototatico</v>
+        <v>personalmaju</v>
       </c>
       <c r="B534">
         <v>1</v>
@@ -7878,7 +7878,7 @@
     </row>
     <row r="535">
       <c r="A535" t="str">
-        <v>michel.juliano.barbershop</v>
+        <v>fototatico</v>
       </c>
       <c r="B535">
         <v>1</v>
@@ -7892,7 +7892,7 @@
     </row>
     <row r="536">
       <c r="A536" t="str">
-        <v>diegomoisesribeiro</v>
+        <v>michel.juliano.barbershop</v>
       </c>
       <c r="B536">
         <v>1</v>
@@ -7906,7 +7906,7 @@
     </row>
     <row r="537">
       <c r="A537" t="str">
-        <v>ruperto_696</v>
+        <v>diegomoisesribeiro</v>
       </c>
       <c r="B537">
         <v>1</v>
@@ -7920,7 +7920,7 @@
     </row>
     <row r="538">
       <c r="A538" t="str">
-        <v>brunito_bernardo</v>
+        <v>ruperto_696</v>
       </c>
       <c r="B538">
         <v>1</v>
@@ -7934,7 +7934,7 @@
     </row>
     <row r="539">
       <c r="A539" t="str">
-        <v>calebe1000grau</v>
+        <v>brunito_bernardo</v>
       </c>
       <c r="B539">
         <v>1</v>
@@ -7948,7 +7948,7 @@
     </row>
     <row r="540">
       <c r="A540" t="str">
-        <v>lucca_bjj_01</v>
+        <v>calebe1000grau</v>
       </c>
       <c r="B540">
         <v>1</v>
@@ -7962,7 +7962,7 @@
     </row>
     <row r="541">
       <c r="A541" t="str">
-        <v>clarianavillasboasoficial</v>
+        <v>lucca_bjj_01</v>
       </c>
       <c r="B541">
         <v>1</v>
@@ -7976,7 +7976,7 @@
     </row>
     <row r="542">
       <c r="A542" t="str">
-        <v>williamjanser</v>
+        <v>clarianavillasboasoficial</v>
       </c>
       <c r="B542">
         <v>1</v>
@@ -7990,7 +7990,7 @@
     </row>
     <row r="543">
       <c r="A543" t="str">
-        <v>aureooficial</v>
+        <v>williamjanser</v>
       </c>
       <c r="B543">
         <v>1</v>
@@ -8004,7 +8004,7 @@
     </row>
     <row r="544">
       <c r="A544" t="str">
-        <v>gladyador_do_asa</v>
+        <v>aureooficial</v>
       </c>
       <c r="B544">
         <v>1</v>
@@ -8018,7 +8018,7 @@
     </row>
     <row r="545">
       <c r="A545" t="str">
-        <v>chicinvancity</v>
+        <v>gladyador_do_asa</v>
       </c>
       <c r="B545">
         <v>1</v>
@@ -8032,7 +8032,7 @@
     </row>
     <row r="546">
       <c r="A546" t="str">
-        <v>jeremyericjacobs</v>
+        <v>chicinvancity</v>
       </c>
       <c r="B546">
         <v>1</v>
@@ -8046,7 +8046,7 @@
     </row>
     <row r="547">
       <c r="A547" t="str">
-        <v>gallupistrengthconditioning</v>
+        <v>jeremyericjacobs</v>
       </c>
       <c r="B547">
         <v>1</v>
@@ -8060,7 +8060,7 @@
     </row>
     <row r="548">
       <c r="A548" t="str">
-        <v>satsangbjj</v>
+        <v>gallupistrengthconditioning</v>
       </c>
       <c r="B548">
         <v>1</v>
@@ -8074,7 +8074,7 @@
     </row>
     <row r="549">
       <c r="A549" t="str">
-        <v>susiemelchionda</v>
+        <v>satsangbjj</v>
       </c>
       <c r="B549">
         <v>1</v>
@@ -8088,7 +8088,7 @@
     </row>
     <row r="550">
       <c r="A550" t="str">
-        <v>alehh_novaes</v>
+        <v>susiemelchionda</v>
       </c>
       <c r="B550">
         <v>1</v>
@@ -8102,7 +8102,7 @@
     </row>
     <row r="551">
       <c r="A551" t="str">
-        <v>andreaapurinaoficial</v>
+        <v>alehh_novaes</v>
       </c>
       <c r="B551">
         <v>1</v>
@@ -8116,7 +8116,7 @@
     </row>
     <row r="552">
       <c r="A552" t="str">
-        <v>gilcilenecristina</v>
+        <v>andreaapurinaoficial</v>
       </c>
       <c r="B552">
         <v>1</v>
@@ -8130,7 +8130,7 @@
     </row>
     <row r="553">
       <c r="A553" t="str">
-        <v>danibastiaan</v>
+        <v>gilcilenecristina</v>
       </c>
       <c r="B553">
         <v>1</v>
@@ -8144,7 +8144,7 @@
     </row>
     <row r="554">
       <c r="A554" t="str">
-        <v>valbersonsantoss</v>
+        <v>danibastiaan</v>
       </c>
       <c r="B554">
         <v>1</v>
@@ -8158,7 +8158,7 @@
     </row>
     <row r="555">
       <c r="A555" t="str">
-        <v>franklinamaral</v>
+        <v>valbersonsantoss</v>
       </c>
       <c r="B555">
         <v>1</v>
@@ -8172,7 +8172,7 @@
     </row>
     <row r="556">
       <c r="A556" t="str">
-        <v>j.borgespz</v>
+        <v>franklinamaral</v>
       </c>
       <c r="B556">
         <v>1</v>
@@ -8186,7 +8186,7 @@
     </row>
     <row r="557">
       <c r="A557" t="str">
-        <v>lucaswallaceftt</v>
+        <v>j.borgespz</v>
       </c>
       <c r="B557">
         <v>1</v>
@@ -8200,7 +8200,7 @@
     </row>
     <row r="558">
       <c r="A558" t="str">
-        <v>renancarlini</v>
+        <v>lucaswallaceftt</v>
       </c>
       <c r="B558">
         <v>1</v>
@@ -8214,7 +8214,7 @@
     </row>
     <row r="559">
       <c r="A559" t="str">
-        <v>almir_gdf</v>
+        <v>renancarlini</v>
       </c>
       <c r="B559">
         <v>1</v>
@@ -8228,7 +8228,7 @@
     </row>
     <row r="560">
       <c r="A560" t="str">
-        <v>gpedroza1</v>
+        <v>almir_gdf</v>
       </c>
       <c r="B560">
         <v>1</v>
@@ -8242,7 +8242,7 @@
     </row>
     <row r="561">
       <c r="A561" t="str">
-        <v>lilianvillaca_</v>
+        <v>gpedroza1</v>
       </c>
       <c r="B561">
         <v>1</v>
@@ -8256,7 +8256,7 @@
     </row>
     <row r="562">
       <c r="A562" t="str">
-        <v>alinedoprojeto</v>
+        <v>lilianvillaca_</v>
       </c>
       <c r="B562">
         <v>1</v>
@@ -8270,7 +8270,7 @@
     </row>
     <row r="563">
       <c r="A563" t="str">
-        <v>sabe_de_uma_coisa2026</v>
+        <v>alinedoprojeto</v>
       </c>
       <c r="B563">
         <v>1</v>
@@ -8284,7 +8284,7 @@
     </row>
     <row r="564">
       <c r="A564" t="str">
-        <v>gratidao_jesus2026</v>
+        <v>sabe_de_uma_coisa2026</v>
       </c>
       <c r="B564">
         <v>1</v>
@@ -8298,7 +8298,7 @@
     </row>
     <row r="565">
       <c r="A565" t="str">
-        <v>projeto_amigos_de_ouro</v>
+        <v>gratidao_jesus2026</v>
       </c>
       <c r="B565">
         <v>1</v>
@@ -8312,7 +8312,7 @@
     </row>
     <row r="566">
       <c r="A566" t="str">
-        <v>jose_carlos_baixote</v>
+        <v>projeto_amigos_de_ouro</v>
       </c>
       <c r="B566">
         <v>1</v>
@@ -8326,7 +8326,7 @@
     </row>
     <row r="567">
       <c r="A567" t="str">
-        <v>dani120690</v>
+        <v>jose_carlos_baixote</v>
       </c>
       <c r="B567">
         <v>1</v>
@@ -8340,7 +8340,7 @@
     </row>
     <row r="568">
       <c r="A568" t="str">
-        <v>raonasthai</v>
+        <v>dani120690</v>
       </c>
       <c r="B568">
         <v>1</v>
@@ -8354,7 +8354,7 @@
     </row>
     <row r="569">
       <c r="A569" t="str">
-        <v>adonaibjj_grip</v>
+        <v>raonasthai</v>
       </c>
       <c r="B569">
         <v>1</v>
@@ -8368,7 +8368,7 @@
     </row>
     <row r="570">
       <c r="A570" t="str">
-        <v>arturbambam</v>
+        <v>adonaibjj_grip</v>
       </c>
       <c r="B570">
         <v>1</v>
@@ -8382,7 +8382,7 @@
     </row>
     <row r="571">
       <c r="A571" t="str">
-        <v>cebolajj167</v>
+        <v>arturbambam</v>
       </c>
       <c r="B571">
         <v>1</v>
@@ -8396,7 +8396,7 @@
     </row>
     <row r="572">
       <c r="A572" t="str">
-        <v>danieljsantoss_</v>
+        <v>cebolajj167</v>
       </c>
       <c r="B572">
         <v>1</v>
@@ -8410,7 +8410,7 @@
     </row>
     <row r="573">
       <c r="A573" t="str">
-        <v>hermaan10_</v>
+        <v>danieljsantoss_</v>
       </c>
       <c r="B573">
         <v>1</v>
@@ -8424,7 +8424,7 @@
     </row>
     <row r="574">
       <c r="A574" t="str">
-        <v>hunter.mccrary</v>
+        <v>hermaan10_</v>
       </c>
       <c r="B574">
         <v>1</v>
@@ -8438,7 +8438,7 @@
     </row>
     <row r="575">
       <c r="A575" t="str">
-        <v>markakasocks</v>
+        <v>hunter.mccrary</v>
       </c>
       <c r="B575">
         <v>1</v>
@@ -8452,7 +8452,7 @@
     </row>
     <row r="576">
       <c r="A576" t="str">
-        <v>rodrigojansen_</v>
+        <v>markakasocks</v>
       </c>
       <c r="B576">
         <v>1</v>
@@ -8466,7 +8466,7 @@
     </row>
     <row r="577">
       <c r="A577" t="str">
-        <v>odivaldo_lobo</v>
+        <v>rodrigojansen_</v>
       </c>
       <c r="B577">
         <v>1</v>
@@ -8480,7 +8480,7 @@
     </row>
     <row r="578">
       <c r="A578" t="str">
-        <v>davidpina_047</v>
+        <v>odivaldo_lobo</v>
       </c>
       <c r="B578">
         <v>1</v>
@@ -8494,7 +8494,7 @@
     </row>
     <row r="579">
       <c r="A579" t="str">
-        <v>selma.oscar12</v>
+        <v>davidpina_047</v>
       </c>
       <c r="B579">
         <v>1</v>
@@ -8508,7 +8508,7 @@
     </row>
     <row r="580">
       <c r="A580" t="str">
-        <v>flahvinhotreinador</v>
+        <v>selma.oscar12</v>
       </c>
       <c r="B580">
         <v>1</v>
@@ -8522,7 +8522,7 @@
     </row>
     <row r="581">
       <c r="A581" t="str">
-        <v>ariel_alvees</v>
+        <v>flahvinhotreinador</v>
       </c>
       <c r="B581">
         <v>1</v>
@@ -8536,7 +8536,7 @@
     </row>
     <row r="582">
       <c r="A582" t="str">
-        <v>cristiane.c.santana</v>
+        <v>ariel_alvees</v>
       </c>
       <c r="B582">
         <v>1</v>
@@ -8550,7 +8550,7 @@
     </row>
     <row r="583">
       <c r="A583" t="str">
-        <v>marciocatenacci</v>
+        <v>cristiane.c.santana</v>
       </c>
       <c r="B583">
         <v>1</v>
@@ -8564,7 +8564,7 @@
     </row>
     <row r="584">
       <c r="A584" t="str">
-        <v>claudioribeiro_ufc</v>
+        <v>marciocatenacci</v>
       </c>
       <c r="B584">
         <v>1</v>
@@ -8578,7 +8578,7 @@
     </row>
     <row r="585">
       <c r="A585" t="str">
-        <v>rodrigolidiosales</v>
+        <v>claudioribeiro_ufc</v>
       </c>
       <c r="B585">
         <v>1</v>
@@ -8592,7 +8592,7 @@
     </row>
     <row r="586">
       <c r="A586" t="str">
-        <v>moisespira</v>
+        <v>rodrigolidiosales</v>
       </c>
       <c r="B586">
         <v>1</v>
@@ -8606,7 +8606,7 @@
     </row>
     <row r="587">
       <c r="A587" t="str">
-        <v>ctt.casaestopteam</v>
+        <v>moisespira</v>
       </c>
       <c r="B587">
         <v>1</v>
@@ -8620,7 +8620,7 @@
     </row>
     <row r="588">
       <c r="A588" t="str">
-        <v>cassius.paula</v>
+        <v>ctt.casaestopteam</v>
       </c>
       <c r="B588">
         <v>1</v>
@@ -8634,7 +8634,7 @@
     </row>
     <row r="589">
       <c r="A589" t="str">
-        <v>renatoevangelistaa</v>
+        <v>cassius.paula</v>
       </c>
       <c r="B589">
         <v>1</v>
@@ -8648,7 +8648,7 @@
     </row>
     <row r="590">
       <c r="A590" t="str">
-        <v>manmoska</v>
+        <v>renatoevangelistaa</v>
       </c>
       <c r="B590">
         <v>1</v>
@@ -8662,7 +8662,7 @@
     </row>
     <row r="591">
       <c r="A591" t="str">
-        <v>lucasampaio</v>
+        <v>manmoska</v>
       </c>
       <c r="B591">
         <v>1</v>
@@ -8676,7 +8676,7 @@
     </row>
     <row r="592">
       <c r="A592" t="str">
-        <v>ricieritonan</v>
+        <v>lucasampaio</v>
       </c>
       <c r="B592">
         <v>1</v>
@@ -8690,7 +8690,7 @@
     </row>
     <row r="593">
       <c r="A593" t="str">
-        <v>alphavillesup</v>
+        <v>ricieritonan</v>
       </c>
       <c r="B593">
         <v>1</v>
@@ -8704,7 +8704,7 @@
     </row>
     <row r="594">
       <c r="A594" t="str">
-        <v>omarcotomaz</v>
+        <v>alphavillesup</v>
       </c>
       <c r="B594">
         <v>1</v>
@@ -8718,7 +8718,7 @@
     </row>
     <row r="595">
       <c r="A595" t="str">
-        <v>joao_lins_muaythai</v>
+        <v>omarcotomaz</v>
       </c>
       <c r="B595">
         <v>1</v>
@@ -8732,7 +8732,7 @@
     </row>
     <row r="596">
       <c r="A596" t="str">
-        <v>pelevermelha.uniformes</v>
+        <v>joao_lins_muaythai</v>
       </c>
       <c r="B596">
         <v>1</v>
@@ -8746,7 +8746,7 @@
     </row>
     <row r="597">
       <c r="A597" t="str">
-        <v>flavia_gomes_29</v>
+        <v>pelevermelha.uniformes</v>
       </c>
       <c r="B597">
         <v>1</v>
@@ -8760,7 +8760,7 @@
     </row>
     <row r="598">
       <c r="A598" t="str">
-        <v>romulobelarmino</v>
+        <v>flavia_gomes_29</v>
       </c>
       <c r="B598">
         <v>1</v>
@@ -8774,7 +8774,7 @@
     </row>
     <row r="599">
       <c r="A599" t="str">
-        <v>israelbahiensebraz</v>
+        <v>romulobelarmino</v>
       </c>
       <c r="B599">
         <v>1</v>
@@ -8788,7 +8788,7 @@
     </row>
     <row r="600">
       <c r="A600" t="str">
-        <v>leitefelippez</v>
+        <v>israelbahiensebraz</v>
       </c>
       <c r="B600">
         <v>1</v>
@@ -8802,7 +8802,7 @@
     </row>
     <row r="601">
       <c r="A601" t="str">
-        <v>gabrielsoaresbjj</v>
+        <v>leitefelippez</v>
       </c>
       <c r="B601">
         <v>1</v>
@@ -8816,7 +8816,7 @@
     </row>
     <row r="602">
       <c r="A602" t="str">
-        <v>larissamartinsbjj</v>
+        <v>gabrielsoaresbjj</v>
       </c>
       <c r="B602">
         <v>1</v>
@@ -8830,7 +8830,7 @@
     </row>
     <row r="603">
       <c r="A603" t="str">
-        <v>fernandamourabjj</v>
+        <v>larissamartinsbjj</v>
       </c>
       <c r="B603">
         <v>1</v>
@@ -8844,7 +8844,7 @@
     </row>
     <row r="604">
       <c r="A604" t="str">
-        <v>isasantos1404</v>
+        <v>fernandamourabjj</v>
       </c>
       <c r="B604">
         <v>1</v>
@@ -8858,7 +8858,7 @@
     </row>
     <row r="605">
       <c r="A605" t="str">
-        <v>alberto_garcia_queiroz_junior</v>
+        <v>isasantos1404</v>
       </c>
       <c r="B605">
         <v>1</v>
@@ -8872,7 +8872,7 @@
     </row>
     <row r="606">
       <c r="A606" t="str">
-        <v>titosbjj</v>
+        <v>alberto_garcia_queiroz_junior</v>
       </c>
       <c r="B606">
         <v>1</v>
@@ -8886,7 +8886,7 @@
     </row>
     <row r="607">
       <c r="A607" t="str">
-        <v>johnnydesinfluencer</v>
+        <v>titosbjj</v>
       </c>
       <c r="B607">
         <v>1</v>
@@ -8900,7 +8900,7 @@
     </row>
     <row r="608">
       <c r="A608" t="str">
-        <v>keep.itpushinnn</v>
+        <v>johnnydesinfluencer</v>
       </c>
       <c r="B608">
         <v>1</v>
@@ -8914,7 +8914,7 @@
     </row>
     <row r="609">
       <c r="A609" t="str">
-        <v>x_xpatto</v>
+        <v>keep.itpushinnn</v>
       </c>
       <c r="B609">
         <v>1</v>
@@ -8928,7 +8928,7 @@
     </row>
     <row r="610">
       <c r="A610" t="str">
-        <v>aldomanuel1994</v>
+        <v>x_xpatto</v>
       </c>
       <c r="B610">
         <v>1</v>
@@ -8942,7 +8942,7 @@
     </row>
     <row r="611">
       <c r="A611" t="str">
-        <v>joselia_1980</v>
+        <v>aldomanuel1994</v>
       </c>
       <c r="B611">
         <v>1</v>
@@ -8956,7 +8956,7 @@
     </row>
     <row r="612">
       <c r="A612" t="str">
-        <v>geovannaalc_</v>
+        <v>joselia_1980</v>
       </c>
       <c r="B612">
         <v>1</v>
@@ -8970,7 +8970,7 @@
     </row>
     <row r="613">
       <c r="A613" t="str">
-        <v>biabezerra88</v>
+        <v>geovannaalc_</v>
       </c>
       <c r="B613">
         <v>1</v>
@@ -8984,7 +8984,7 @@
     </row>
     <row r="614">
       <c r="A614" t="str">
-        <v>_murilo_06</v>
+        <v>biabezerra88</v>
       </c>
       <c r="B614">
         <v>1</v>
@@ -8998,7 +8998,7 @@
     </row>
     <row r="615">
       <c r="A615" t="str">
-        <v>gi.liimaa_</v>
+        <v>_murilo_06</v>
       </c>
       <c r="B615">
         <v>1</v>
@@ -9012,7 +9012,7 @@
     </row>
     <row r="616">
       <c r="A616" t="str">
-        <v>generaldantas</v>
+        <v>gi.liimaa_</v>
       </c>
       <c r="B616">
         <v>1</v>
@@ -9026,7 +9026,7 @@
     </row>
     <row r="617">
       <c r="A617" t="str">
-        <v>paulokami.mma</v>
+        <v>generaldantas</v>
       </c>
       <c r="B617">
         <v>1</v>
@@ -9040,7 +9040,7 @@
     </row>
     <row r="618">
       <c r="A618" t="str">
-        <v>ph_castroh</v>
+        <v>paulokami.mma</v>
       </c>
       <c r="B618">
         <v>1</v>
@@ -9054,7 +9054,7 @@
     </row>
     <row r="619">
       <c r="A619" t="str">
-        <v>jhonny.2302_aritamma</v>
+        <v>ph_castroh</v>
       </c>
       <c r="B619">
         <v>1</v>
@@ -9068,7 +9068,7 @@
     </row>
     <row r="620">
       <c r="A620" t="str">
-        <v>pettys2298</v>
+        <v>jhonny.2302_aritamma</v>
       </c>
       <c r="B620">
         <v>1</v>
@@ -9082,7 +9082,7 @@
     </row>
     <row r="621">
       <c r="A621" t="str">
-        <v>jeffersonliu2022</v>
+        <v>pettys2298</v>
       </c>
       <c r="B621">
         <v>1</v>
@@ -9096,7 +9096,7 @@
     </row>
     <row r="622">
       <c r="A622" t="str">
-        <v>guihs_cardoso</v>
+        <v>jeffersonliu2022</v>
       </c>
       <c r="B622">
         <v>1</v>
@@ -9110,7 +9110,7 @@
     </row>
     <row r="623">
       <c r="A623" t="str">
-        <v>sp__theus</v>
+        <v>guihs_cardoso</v>
       </c>
       <c r="B623">
         <v>1</v>
@@ -9124,7 +9124,7 @@
     </row>
     <row r="624">
       <c r="A624" t="str">
-        <v>eriikdossantoos</v>
+        <v>sp__theus</v>
       </c>
       <c r="B624">
         <v>1</v>
@@ -9138,7 +9138,7 @@
     </row>
     <row r="625">
       <c r="A625" t="str">
-        <v>rick.santosz</v>
+        <v>eriikdossantoos</v>
       </c>
       <c r="B625">
         <v>1</v>
@@ -9152,7 +9152,7 @@
     </row>
     <row r="626">
       <c r="A626" t="str">
-        <v>pbmoments_</v>
+        <v>rick.santosz</v>
       </c>
       <c r="B626">
         <v>1</v>
@@ -9166,7 +9166,7 @@
     </row>
     <row r="627">
       <c r="A627" t="str">
-        <v>ana.cristina.uno</v>
+        <v>pbmoments_</v>
       </c>
       <c r="B627">
         <v>1</v>
@@ -9180,7 +9180,7 @@
     </row>
     <row r="628">
       <c r="A628" t="str">
-        <v>silva_junior1979</v>
+        <v>ana.cristina.uno</v>
       </c>
       <c r="B628">
         <v>1</v>
@@ -9194,7 +9194,7 @@
     </row>
     <row r="629">
       <c r="A629" t="str">
-        <v>santos39roger</v>
+        <v>silva_junior1979</v>
       </c>
       <c r="B629">
         <v>1</v>
@@ -9208,7 +9208,7 @@
     </row>
     <row r="630">
       <c r="A630" t="str">
-        <v>terapeuta_moniquedias</v>
+        <v>santos39roger</v>
       </c>
       <c r="B630">
         <v>1</v>
@@ -9222,7 +9222,7 @@
     </row>
     <row r="631">
       <c r="A631" t="str">
-        <v>bernardocavalcanti1</v>
+        <v>terapeuta_moniquedias</v>
       </c>
       <c r="B631">
         <v>1</v>
@@ -9236,7 +9236,7 @@
     </row>
     <row r="632">
       <c r="A632" t="str">
-        <v>mestrevascobento</v>
+        <v>bernardocavalcanti1</v>
       </c>
       <c r="B632">
         <v>1</v>
@@ -9250,7 +9250,7 @@
     </row>
     <row r="633">
       <c r="A633" t="str">
-        <v>ever.soulson</v>
+        <v>mestrevascobento</v>
       </c>
       <c r="B633">
         <v>1</v>
@@ -9264,7 +9264,7 @@
     </row>
     <row r="634">
       <c r="A634" t="str">
-        <v>martins.rauanee</v>
+        <v>ever.soulson</v>
       </c>
       <c r="B634">
         <v>1</v>
@@ -9278,7 +9278,7 @@
     </row>
     <row r="635">
       <c r="A635" t="str">
-        <v>camillinhamma</v>
+        <v>martins.rauanee</v>
       </c>
       <c r="B635">
         <v>1</v>
@@ -9292,7 +9292,7 @@
     </row>
     <row r="636">
       <c r="A636" t="str">
-        <v>leandro_pedro7</v>
+        <v>camillinhamma</v>
       </c>
       <c r="B636">
         <v>1</v>
@@ -9306,7 +9306,7 @@
     </row>
     <row r="637">
       <c r="A637" t="str">
-        <v>soniarochaco</v>
+        <v>leandro_pedro7</v>
       </c>
       <c r="B637">
         <v>1</v>
@@ -9320,7 +9320,7 @@
     </row>
     <row r="638">
       <c r="A638" t="str">
-        <v>andreloliva12</v>
+        <v>soniarochaco</v>
       </c>
       <c r="B638">
         <v>1</v>
@@ -9334,7 +9334,7 @@
     </row>
     <row r="639">
       <c r="A639" t="str">
-        <v>dcoops2</v>
+        <v>andreloliva12</v>
       </c>
       <c r="B639">
         <v>1</v>
@@ -9348,7 +9348,7 @@
     </row>
     <row r="640">
       <c r="A640" t="str">
-        <v>homemdeita</v>
+        <v>dcoops2</v>
       </c>
       <c r="B640">
         <v>1</v>
@@ -9362,7 +9362,7 @@
     </row>
     <row r="641">
       <c r="A641" t="str">
-        <v>ludelmaraujo</v>
+        <v>homemdeita</v>
       </c>
       <c r="B641">
         <v>1</v>
@@ -9376,7 +9376,7 @@
     </row>
     <row r="642">
       <c r="A642" t="str">
-        <v>ricardosousa811</v>
+        <v>ludelmaraujo</v>
       </c>
       <c r="B642">
         <v>1</v>
@@ -9390,7 +9390,7 @@
     </row>
     <row r="643">
       <c r="A643" t="str">
-        <v>axiaaly</v>
+        <v>ricardosousa811</v>
       </c>
       <c r="B643">
         <v>1</v>
@@ -9404,7 +9404,7 @@
     </row>
     <row r="644">
       <c r="A644" t="str">
-        <v>oficialrichardsilva_ice_men</v>
+        <v>axiaaly</v>
       </c>
       <c r="B644">
         <v>1</v>
@@ -9418,7 +9418,7 @@
     </row>
     <row r="645">
       <c r="A645" t="str">
-        <v>eimysalazar</v>
+        <v>oficialrichardsilva_ice_men</v>
       </c>
       <c r="B645">
         <v>1</v>
@@ -9432,7 +9432,7 @@
     </row>
     <row r="646">
       <c r="A646" t="str">
-        <v>victorxferreira</v>
+        <v>eimysalazar</v>
       </c>
       <c r="B646">
         <v>1</v>
@@ -9446,7 +9446,7 @@
     </row>
     <row r="647">
       <c r="A647" t="str">
-        <v>renatogomes769</v>
+        <v>victorxferreira</v>
       </c>
       <c r="B647">
         <v>1</v>
@@ -9460,7 +9460,7 @@
     </row>
     <row r="648">
       <c r="A648" t="str">
-        <v>thiagomoisesmma</v>
+        <v>renatogomes769</v>
       </c>
       <c r="B648">
         <v>1</v>
@@ -9474,7 +9474,7 @@
     </row>
     <row r="649">
       <c r="A649" t="str">
-        <v>pazzini__</v>
+        <v>thiagomoisesmma</v>
       </c>
       <c r="B649">
         <v>1</v>
@@ -9488,7 +9488,7 @@
     </row>
     <row r="650">
       <c r="A650" t="str">
-        <v>sr.dpaula10</v>
+        <v>pazzini__</v>
       </c>
       <c r="B650">
         <v>1</v>
@@ -9502,7 +9502,7 @@
     </row>
     <row r="651">
       <c r="A651" t="str">
-        <v>santosriveiros18737383</v>
+        <v>sr.dpaula10</v>
       </c>
       <c r="B651">
         <v>1</v>
@@ -9516,7 +9516,7 @@
     </row>
     <row r="652">
       <c r="A652" t="str">
-        <v>dinhomoraisoficial</v>
+        <v>santosriveiros18737383</v>
       </c>
       <c r="B652">
         <v>1</v>
@@ -9530,7 +9530,7 @@
     </row>
     <row r="653">
       <c r="A653" t="str">
-        <v>adrianoblessed89</v>
+        <v>dinhomoraisoficial</v>
       </c>
       <c r="B653">
         <v>1</v>
@@ -9544,7 +9544,7 @@
     </row>
     <row r="654">
       <c r="A654" t="str">
-        <v>dobby_1968</v>
+        <v>adrianoblessed89</v>
       </c>
       <c r="B654">
         <v>1</v>
@@ -9558,7 +9558,7 @@
     </row>
     <row r="655">
       <c r="A655" t="str">
-        <v>ricardogabriel.sr</v>
+        <v>dobby_1968</v>
       </c>
       <c r="B655">
         <v>1</v>
@@ -9572,7 +9572,7 @@
     </row>
     <row r="656">
       <c r="A656" t="str">
-        <v>ottoniisrael</v>
+        <v>ricardogabriel.sr</v>
       </c>
       <c r="B656">
         <v>1</v>
@@ -9586,7 +9586,7 @@
     </row>
     <row r="657">
       <c r="A657" t="str">
-        <v>allves___46</v>
+        <v>ottoniisrael</v>
       </c>
       <c r="B657">
         <v>1</v>
@@ -9600,7 +9600,7 @@
     </row>
     <row r="658">
       <c r="A658" t="str">
-        <v>fe_.faggi</v>
+        <v>allves___46</v>
       </c>
       <c r="B658">
         <v>1</v>
@@ -9614,7 +9614,7 @@
     </row>
     <row r="659">
       <c r="A659" t="str">
-        <v>lucianatpiccelli</v>
+        <v>fe_.faggi</v>
       </c>
       <c r="B659">
         <v>1</v>
@@ -9628,7 +9628,7 @@
     </row>
     <row r="660">
       <c r="A660" t="str">
-        <v>dyrodriguesohplano</v>
+        <v>lucianatpiccelli</v>
       </c>
       <c r="B660">
         <v>1</v>
@@ -9642,7 +9642,7 @@
     </row>
     <row r="661">
       <c r="A661" t="str">
-        <v>almeida_.e7</v>
+        <v>dyrodriguesohplano</v>
       </c>
       <c r="B661">
         <v>1</v>
@@ -9656,7 +9656,7 @@
     </row>
     <row r="662">
       <c r="A662" t="str">
-        <v>rxdi_mns</v>
+        <v>almeida_.e7</v>
       </c>
       <c r="B662">
         <v>1</v>
@@ -9670,7 +9670,7 @@
     </row>
     <row r="663">
       <c r="A663" t="str">
-        <v>grupoohplanooficial</v>
+        <v>rxdi_mns</v>
       </c>
       <c r="B663">
         <v>1</v>
@@ -9684,7 +9684,7 @@
     </row>
     <row r="664">
       <c r="A664" t="str">
-        <v>maribrittos22</v>
+        <v>grupoohplanooficial</v>
       </c>
       <c r="B664">
         <v>1</v>
@@ -9698,7 +9698,7 @@
     </row>
     <row r="665">
       <c r="A665" t="str">
-        <v>yago_08k</v>
+        <v>maribrittos22</v>
       </c>
       <c r="B665">
         <v>1</v>
@@ -9712,7 +9712,7 @@
     </row>
     <row r="666">
       <c r="A666" t="str">
-        <v>blesed578</v>
+        <v>yago_08k</v>
       </c>
       <c r="B666">
         <v>1</v>
@@ -9726,7 +9726,7 @@
     </row>
     <row r="667">
       <c r="A667" t="str">
-        <v>remarchina</v>
+        <v>blesed578</v>
       </c>
       <c r="B667">
         <v>1</v>
@@ -9740,7 +9740,7 @@
     </row>
     <row r="668">
       <c r="A668" t="str">
-        <v>odennismagalhaes</v>
+        <v>remarchina</v>
       </c>
       <c r="B668">
         <v>1</v>
@@ -9754,7 +9754,7 @@
     </row>
     <row r="669">
       <c r="A669" t="str">
-        <v>1felipe.bjj</v>
+        <v>odennismagalhaes</v>
       </c>
       <c r="B669">
         <v>1</v>
@@ -9768,7 +9768,7 @@
     </row>
     <row r="670">
       <c r="A670" t="str">
-        <v>_samu35</v>
+        <v>1felipe.bjj</v>
       </c>
       <c r="B670">
         <v>1</v>
@@ -9782,7 +9782,7 @@
     </row>
     <row r="671">
       <c r="A671" t="str">
-        <v>indiopersonalfight</v>
+        <v>_samu35</v>
       </c>
       <c r="B671">
         <v>1</v>
@@ -9796,7 +9796,7 @@
     </row>
     <row r="672">
       <c r="A672" t="str">
-        <v>davi.cb</v>
+        <v>indiopersonalfight</v>
       </c>
       <c r="B672">
         <v>1</v>
@@ -9810,7 +9810,7 @@
     </row>
     <row r="673">
       <c r="A673" t="str">
-        <v>guilherme.duartesilva</v>
+        <v>davi.cb</v>
       </c>
       <c r="B673">
         <v>1</v>
@@ -9824,7 +9824,7 @@
     </row>
     <row r="674">
       <c r="A674" t="str">
-        <v>_.carlos.2x._</v>
+        <v>guilherme.duartesilva</v>
       </c>
       <c r="B674">
         <v>1</v>
@@ -9838,7 +9838,7 @@
     </row>
     <row r="675">
       <c r="A675" t="str">
-        <v>thizzlenik</v>
+        <v>_.carlos.2x._</v>
       </c>
       <c r="B675">
         <v>1</v>
@@ -9852,7 +9852,7 @@
     </row>
     <row r="676">
       <c r="A676" t="str">
-        <v>yon0sab0</v>
+        <v>thizzlenik</v>
       </c>
       <c r="B676">
         <v>1</v>
@@ -9866,7 +9866,7 @@
     </row>
     <row r="677">
       <c r="A677" t="str">
-        <v>bammer2026</v>
+        <v>yon0sab0</v>
       </c>
       <c r="B677">
         <v>1</v>
@@ -9880,7 +9880,7 @@
     </row>
     <row r="678">
       <c r="A678" t="str">
-        <v>elnaggar_85</v>
+        <v>bammer2026</v>
       </c>
       <c r="B678">
         <v>1</v>
@@ -9894,7 +9894,7 @@
     </row>
     <row r="679">
       <c r="A679" t="str">
-        <v>nulife2day</v>
+        <v>elnaggar_85</v>
       </c>
       <c r="B679">
         <v>1</v>
@@ -9908,7 +9908,7 @@
     </row>
     <row r="680">
       <c r="A680" t="str">
-        <v>abbasrizvi2204</v>
+        <v>nulife2day</v>
       </c>
       <c r="B680">
         <v>1</v>
@@ -9922,7 +9922,7 @@
     </row>
     <row r="681">
       <c r="A681" t="str">
-        <v>dogodoy</v>
+        <v>abbasrizvi2204</v>
       </c>
       <c r="B681">
         <v>1</v>
@@ -9936,7 +9936,7 @@
     </row>
     <row r="682">
       <c r="A682" t="str">
-        <v>cabreuvamma</v>
+        <v>dogodoy</v>
       </c>
       <c r="B682">
         <v>1</v>
@@ -9950,7 +9950,7 @@
     </row>
     <row r="683">
       <c r="A683" t="str">
-        <v>clinicaikiro</v>
+        <v>cabreuvamma</v>
       </c>
       <c r="B683">
         <v>1</v>
@@ -9964,7 +9964,7 @@
     </row>
     <row r="684">
       <c r="A684" t="str">
-        <v>jefte_jizreel</v>
+        <v>clinicaikiro</v>
       </c>
       <c r="B684">
         <v>1</v>
@@ -9978,7 +9978,7 @@
     </row>
     <row r="685">
       <c r="A685" t="str">
-        <v>klaiver.027xx</v>
+        <v>jefte_jizreel</v>
       </c>
       <c r="B685">
         <v>1</v>
@@ -9992,7 +9992,7 @@
     </row>
     <row r="686">
       <c r="A686" t="str">
-        <v>bmarinhorogerio</v>
+        <v>klaiver.027xx</v>
       </c>
       <c r="B686">
         <v>1</v>
@@ -10006,7 +10006,7 @@
     </row>
     <row r="687">
       <c r="A687" t="str">
-        <v>lucaspaes047</v>
+        <v>bmarinhorogerio</v>
       </c>
       <c r="B687">
         <v>1</v>
@@ -10020,7 +10020,7 @@
     </row>
     <row r="688">
       <c r="A688" t="str">
-        <v>nautinhor7</v>
+        <v>lucaspaes047</v>
       </c>
       <c r="B688">
         <v>1</v>
@@ -10034,7 +10034,7 @@
     </row>
     <row r="689">
       <c r="A689" t="str">
-        <v>1tiagomonteiro</v>
+        <v>nautinhor7</v>
       </c>
       <c r="B689">
         <v>1</v>
@@ -10048,7 +10048,7 @@
     </row>
     <row r="690">
       <c r="A690" t="str">
-        <v>s_giofe</v>
+        <v>1tiagomonteiro</v>
       </c>
       <c r="B690">
         <v>1</v>
@@ -10062,7 +10062,7 @@
     </row>
     <row r="691">
       <c r="A691" t="str">
-        <v>mauricio_dutra_m</v>
+        <v>s_giofe</v>
       </c>
       <c r="B691">
         <v>1</v>
@@ -10076,7 +10076,7 @@
     </row>
     <row r="692">
       <c r="A692" t="str">
-        <v>claudio_tikar</v>
+        <v>mauricio_dutra_m</v>
       </c>
       <c r="B692">
         <v>1</v>
@@ -10090,7 +10090,7 @@
     </row>
     <row r="693">
       <c r="A693" t="str">
-        <v>boeno_rafael</v>
+        <v>claudio_tikar</v>
       </c>
       <c r="B693">
         <v>1</v>
@@ -10104,7 +10104,7 @@
     </row>
     <row r="694">
       <c r="A694" t="str">
-        <v>nati.monteiro</v>
+        <v>boeno_rafael</v>
       </c>
       <c r="B694">
         <v>1</v>
@@ -10118,7 +10118,7 @@
     </row>
     <row r="695">
       <c r="A695" t="str">
-        <v>cinemarianophoto</v>
+        <v>nati.monteiro</v>
       </c>
       <c r="B695">
         <v>1</v>
@@ -10132,7 +10132,7 @@
     </row>
     <row r="696">
       <c r="A696" t="str">
-        <v>patriciarichteroficial</v>
+        <v>cinemarianophoto</v>
       </c>
       <c r="B696">
         <v>1</v>
@@ -10146,7 +10146,7 @@
     </row>
     <row r="697">
       <c r="A697" t="str">
-        <v>use.ellasfit</v>
+        <v>patriciarichteroficial</v>
       </c>
       <c r="B697">
         <v>1</v>
@@ -10160,7 +10160,7 @@
     </row>
     <row r="698">
       <c r="A698" t="str">
-        <v>kauan_mantas</v>
+        <v>use.ellasfit</v>
       </c>
       <c r="B698">
         <v>1</v>
@@ -10174,7 +10174,7 @@
     </row>
     <row r="699">
       <c r="A699" t="str">
-        <v>emersonapache</v>
+        <v>kauan_mantas</v>
       </c>
       <c r="B699">
         <v>1</v>
@@ -10188,7 +10188,7 @@
     </row>
     <row r="700">
       <c r="A700" t="str">
-        <v>nataliavidal965</v>
+        <v>emersonapache</v>
       </c>
       <c r="B700">
         <v>1</v>
@@ -10202,7 +10202,7 @@
     </row>
     <row r="701">
       <c r="A701" t="str">
-        <v>ruanpantojanutricionista</v>
+        <v>nataliavidal965</v>
       </c>
       <c r="B701">
         <v>1</v>
@@ -10216,7 +10216,7 @@
     </row>
     <row r="702">
       <c r="A702" t="str">
-        <v>luizpaulomma</v>
+        <v>ruanpantojanutricionista</v>
       </c>
       <c r="B702">
         <v>1</v>
@@ -10230,7 +10230,7 @@
     </row>
     <row r="703">
       <c r="A703" t="str">
-        <v>tvlinsoficial</v>
+        <v>luizpaulomma</v>
       </c>
       <c r="B703">
         <v>1</v>
@@ -10244,7 +10244,7 @@
     </row>
     <row r="704">
       <c r="A704" t="str">
-        <v>epicjoel2022</v>
+        <v>tvlinsoficial</v>
       </c>
       <c r="B704">
         <v>1</v>
@@ -10258,7 +10258,7 @@
     </row>
     <row r="705">
       <c r="A705" t="str">
-        <v>paulo_rafa_personal</v>
+        <v>epicjoel2022</v>
       </c>
       <c r="B705">
         <v>1</v>
@@ -10272,35 +10272,35 @@
     </row>
     <row r="706">
       <c r="A706" t="str">
-        <v>lucasbaddoure</v>
+        <v>paulo_rafa_personal</v>
       </c>
       <c r="B706">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C706">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D706">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="str">
-        <v>desativado_no_off33</v>
+        <v>lucasbaddoure</v>
       </c>
       <c r="B707">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C707">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D707">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="708">
       <c r="A708" t="str">
-        <v>mg._silvaa_</v>
+        <v>desativado_no_off33</v>
       </c>
       <c r="B708">
         <v>1</v>
@@ -10314,7 +10314,7 @@
     </row>
     <row r="709">
       <c r="A709" t="str">
-        <v>_itamar_maximo</v>
+        <v>mg._silvaa_</v>
       </c>
       <c r="B709">
         <v>1</v>
@@ -10328,7 +10328,7 @@
     </row>
     <row r="710">
       <c r="A710" t="str">
-        <v>lopes.felipe13</v>
+        <v>_itamar_maximo</v>
       </c>
       <c r="B710">
         <v>1</v>
@@ -10342,7 +10342,7 @@
     </row>
     <row r="711">
       <c r="A711" t="str">
-        <v>instrutorindiovs</v>
+        <v>lopes.felipe13</v>
       </c>
       <c r="B711">
         <v>1</v>
@@ -10356,7 +10356,7 @@
     </row>
     <row r="712">
       <c r="A712" t="str">
-        <v>cadupereirss</v>
+        <v>instrutorindiovs</v>
       </c>
       <c r="B712">
         <v>1</v>
@@ -10370,7 +10370,7 @@
     </row>
     <row r="713">
       <c r="A713" t="str">
-        <v>endurance_guia</v>
+        <v>cadupereirss</v>
       </c>
       <c r="B713">
         <v>1</v>
@@ -10384,7 +10384,7 @@
     </row>
     <row r="714">
       <c r="A714" t="str">
-        <v>m1guelmolina</v>
+        <v>endurance_guia</v>
       </c>
       <c r="B714">
         <v>1</v>
@@ -10398,7 +10398,7 @@
     </row>
     <row r="715">
       <c r="A715" t="str">
-        <v>rafa_speda</v>
+        <v>m1guelmolina</v>
       </c>
       <c r="B715">
         <v>1</v>
@@ -10412,7 +10412,7 @@
     </row>
     <row r="716">
       <c r="A716" t="str">
-        <v>marchi_vinicius</v>
+        <v>rafa_speda</v>
       </c>
       <c r="B716">
         <v>1</v>
@@ -10426,7 +10426,7 @@
     </row>
     <row r="717">
       <c r="A717" t="str">
-        <v>perninhakickboxing</v>
+        <v>marchi_vinicius</v>
       </c>
       <c r="B717">
         <v>1</v>
@@ -10440,7 +10440,7 @@
     </row>
     <row r="718">
       <c r="A718" t="str">
-        <v>alissonlayza</v>
+        <v>perninhakickboxing</v>
       </c>
       <c r="B718">
         <v>1</v>
@@ -10454,7 +10454,7 @@
     </row>
     <row r="719">
       <c r="A719" t="str">
-        <v>cotty_bigmonster</v>
+        <v>alissonlayza</v>
       </c>
       <c r="B719">
         <v>1</v>
@@ -10468,7 +10468,7 @@
     </row>
     <row r="720">
       <c r="A720" t="str">
-        <v>programaparadois</v>
+        <v>cotty_bigmonster</v>
       </c>
       <c r="B720">
         <v>1</v>
@@ -10482,7 +10482,7 @@
     </row>
     <row r="721">
       <c r="A721" t="str">
-        <v>alinefurlann</v>
+        <v>programaparadois</v>
       </c>
       <c r="B721">
         <v>1</v>
@@ -10496,7 +10496,7 @@
     </row>
     <row r="722">
       <c r="A722" t="str">
-        <v>cassiolee013</v>
+        <v>alinefurlann</v>
       </c>
       <c r="B722">
         <v>1</v>
@@ -10510,7 +10510,7 @@
     </row>
     <row r="723">
       <c r="A723" t="str">
-        <v>caiogoularts</v>
+        <v>cassiolee013</v>
       </c>
       <c r="B723">
         <v>1</v>
@@ -10524,7 +10524,7 @@
     </row>
     <row r="724">
       <c r="A724" t="str">
-        <v>rosantos83</v>
+        <v>caiogoularts</v>
       </c>
       <c r="B724">
         <v>1</v>
@@ -10538,7 +10538,7 @@
     </row>
     <row r="725">
       <c r="A725" t="str">
-        <v>rodrigo.nsx</v>
+        <v>rosantos83</v>
       </c>
       <c r="B725">
         <v>1</v>
@@ -10552,7 +10552,7 @@
     </row>
     <row r="726">
       <c r="A726" t="str">
-        <v>lorenzojjts</v>
+        <v>rodrigo.nsx</v>
       </c>
       <c r="B726">
         <v>1</v>
@@ -10566,7 +10566,7 @@
     </row>
     <row r="727">
       <c r="A727" t="str">
-        <v>enzorkbjj</v>
+        <v>lorenzojjts</v>
       </c>
       <c r="B727">
         <v>1</v>
@@ -10580,7 +10580,7 @@
     </row>
     <row r="728">
       <c r="A728" t="str">
-        <v>_hygor.soares</v>
+        <v>enzorkbjj</v>
       </c>
       <c r="B728">
         <v>1</v>
@@ -10594,7 +10594,7 @@
     </row>
     <row r="729">
       <c r="A729" t="str">
-        <v>k_costa68</v>
+        <v>_hygor.soares</v>
       </c>
       <c r="B729">
         <v>1</v>
@@ -10608,7 +10608,7 @@
     </row>
     <row r="730">
       <c r="A730" t="str">
-        <v>808.chaz</v>
+        <v>k_costa68</v>
       </c>
       <c r="B730">
         <v>1</v>
@@ -10622,7 +10622,7 @@
     </row>
     <row r="731">
       <c r="A731" t="str">
-        <v>i_am_mauispunjahchick</v>
+        <v>808.chaz</v>
       </c>
       <c r="B731">
         <v>1</v>
@@ -10636,7 +10636,7 @@
     </row>
     <row r="732">
       <c r="A732" t="str">
-        <v>leomvgomes</v>
+        <v>i_am_mauispunjahchick</v>
       </c>
       <c r="B732">
         <v>1</v>
@@ -10650,7 +10650,7 @@
     </row>
     <row r="733">
       <c r="A733" t="str">
-        <v>luizguilhermepaiva_</v>
+        <v>leomvgomes</v>
       </c>
       <c r="B733">
         <v>1</v>
@@ -10664,7 +10664,7 @@
     </row>
     <row r="734">
       <c r="A734" t="str">
-        <v>wagnermeneguelll</v>
+        <v>luizguilhermepaiva_</v>
       </c>
       <c r="B734">
         <v>1</v>
@@ -10678,7 +10678,7 @@
     </row>
     <row r="735">
       <c r="A735" t="str">
-        <v>marcos_indio._</v>
+        <v>wagnermeneguelll</v>
       </c>
       <c r="B735">
         <v>1</v>
@@ -10692,7 +10692,7 @@
     </row>
     <row r="736">
       <c r="A736" t="str">
-        <v>corullapedro</v>
+        <v>marcos_indio._</v>
       </c>
       <c r="B736">
         <v>1</v>
@@ -10706,7 +10706,7 @@
     </row>
     <row r="737">
       <c r="A737" t="str">
-        <v>wanderley_silva081</v>
+        <v>corullapedro</v>
       </c>
       <c r="B737">
         <v>1</v>
@@ -10720,7 +10720,7 @@
     </row>
     <row r="738">
       <c r="A738" t="str">
-        <v>kakaa_ranch</v>
+        <v>wanderley_silva081</v>
       </c>
       <c r="B738">
         <v>1</v>
@@ -10734,7 +10734,7 @@
     </row>
     <row r="739">
       <c r="A739" t="str">
-        <v>lorenzo.klippel</v>
+        <v>kakaa_ranch</v>
       </c>
       <c r="B739">
         <v>1</v>
@@ -10748,7 +10748,7 @@
     </row>
     <row r="740">
       <c r="A740" t="str">
-        <v>luana8324</v>
+        <v>lorenzo.klippel</v>
       </c>
       <c r="B740">
         <v>1</v>
@@ -10762,7 +10762,7 @@
     </row>
     <row r="741">
       <c r="A741" t="str">
-        <v>paidepef</v>
+        <v>luana8324</v>
       </c>
       <c r="B741">
         <v>1</v>
@@ -10776,7 +10776,7 @@
     </row>
     <row r="742">
       <c r="A742" t="str">
-        <v>malhadinho_ufc</v>
+        <v>paidepef</v>
       </c>
       <c r="B742">
         <v>1</v>
@@ -10790,7 +10790,7 @@
     </row>
     <row r="743">
       <c r="A743" t="str">
-        <v>juan.lboxe_</v>
+        <v>malhadinho_ufc</v>
       </c>
       <c r="B743">
         <v>1</v>
@@ -10804,35 +10804,35 @@
     </row>
     <row r="744">
       <c r="A744" t="str">
-        <v>pedroriela</v>
+        <v>juan.lboxe_</v>
       </c>
       <c r="B744">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C744">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D744">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="745">
       <c r="A745" t="str">
-        <v>andradeoficiaal</v>
+        <v>pedroriela</v>
       </c>
       <c r="B745">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C745">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D745">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="746">
       <c r="A746" t="str">
-        <v>netinho_souzas</v>
+        <v>andradeoficiaal</v>
       </c>
       <c r="B746">
         <v>1</v>
@@ -10846,7 +10846,7 @@
     </row>
     <row r="747">
       <c r="A747" t="str">
-        <v>katharinelopes</v>
+        <v>netinho_souzas</v>
       </c>
       <c r="B747">
         <v>1</v>
@@ -10860,7 +10860,7 @@
     </row>
     <row r="748">
       <c r="A748" t="str">
-        <v>__dias_07_</v>
+        <v>katharinelopes</v>
       </c>
       <c r="B748">
         <v>1</v>
@@ -10874,7 +10874,7 @@
     </row>
     <row r="749">
       <c r="A749" t="str">
-        <v>igorsbessa</v>
+        <v>__dias_07_</v>
       </c>
       <c r="B749">
         <v>1</v>
@@ -10888,7 +10888,7 @@
     </row>
     <row r="750">
       <c r="A750" t="str">
-        <v>themarcosalves</v>
+        <v>igorsbessa</v>
       </c>
       <c r="B750">
         <v>1</v>
@@ -10902,7 +10902,7 @@
     </row>
     <row r="751">
       <c r="A751" t="str">
-        <v>deni_jesus_shalom</v>
+        <v>themarcosalves</v>
       </c>
       <c r="B751">
         <v>1</v>
@@ -10916,7 +10916,7 @@
     </row>
     <row r="752">
       <c r="A752" t="str">
-        <v>george.bjj_</v>
+        <v>deni_jesus_shalom</v>
       </c>
       <c r="B752">
         <v>1</v>
@@ -10930,7 +10930,7 @@
     </row>
     <row r="753">
       <c r="A753" t="str">
-        <v>carlosshenn</v>
+        <v>george.bjj_</v>
       </c>
       <c r="B753">
         <v>1</v>
@@ -10944,7 +10944,7 @@
     </row>
     <row r="754">
       <c r="A754" t="str">
-        <v>almeida.nyara</v>
+        <v>carlosshenn</v>
       </c>
       <c r="B754">
         <v>1</v>
@@ -10958,7 +10958,7 @@
     </row>
     <row r="755">
       <c r="A755" t="str">
-        <v>dubernardo37</v>
+        <v>almeida.nyara</v>
       </c>
       <c r="B755">
         <v>1</v>
@@ -10972,7 +10972,7 @@
     </row>
     <row r="756">
       <c r="A756" t="str">
-        <v>sadraquesantana</v>
+        <v>dubernardo37</v>
       </c>
       <c r="B756">
         <v>1</v>
@@ -10986,7 +10986,7 @@
     </row>
     <row r="757">
       <c r="A757" t="str">
-        <v>rogerio.maga</v>
+        <v>sadraquesantana</v>
       </c>
       <c r="B757">
         <v>1</v>
@@ -11000,7 +11000,7 @@
     </row>
     <row r="758">
       <c r="A758" t="str">
-        <v>roblesbastosalfredo</v>
+        <v>rogerio.maga</v>
       </c>
       <c r="B758">
         <v>1</v>
@@ -11014,7 +11014,7 @@
     </row>
     <row r="759">
       <c r="A759" t="str">
-        <v>alexandroscorreia</v>
+        <v>roblesbastosalfredo</v>
       </c>
       <c r="B759">
         <v>1</v>
@@ -11028,7 +11028,7 @@
     </row>
     <row r="760">
       <c r="A760" t="str">
-        <v>lucifit50</v>
+        <v>alexandroscorreia</v>
       </c>
       <c r="B760">
         <v>1</v>
@@ -11042,7 +11042,7 @@
     </row>
     <row r="761">
       <c r="A761" t="str">
-        <v>martinscdione</v>
+        <v>lucifit50</v>
       </c>
       <c r="B761">
         <v>1</v>
@@ -11056,7 +11056,7 @@
     </row>
     <row r="762">
       <c r="A762" t="str">
-        <v>gustavotoi</v>
+        <v>martinscdione</v>
       </c>
       <c r="B762">
         <v>1</v>
@@ -11070,7 +11070,7 @@
     </row>
     <row r="763">
       <c r="A763" t="str">
-        <v>erivaldosilva3333</v>
+        <v>gustavotoi</v>
       </c>
       <c r="B763">
         <v>1</v>
@@ -11084,7 +11084,7 @@
     </row>
     <row r="764">
       <c r="A764" t="str">
-        <v>marcos_r_s_</v>
+        <v>erivaldosilva3333</v>
       </c>
       <c r="B764">
         <v>1</v>
@@ -11098,7 +11098,7 @@
     </row>
     <row r="765">
       <c r="A765" t="str">
-        <v>moys158</v>
+        <v>marcos_r_s_</v>
       </c>
       <c r="B765">
         <v>1</v>
@@ -11112,7 +11112,7 @@
     </row>
     <row r="766">
       <c r="A766" t="str">
-        <v>viviane_moota</v>
+        <v>moys158</v>
       </c>
       <c r="B766">
         <v>1</v>
@@ -11126,7 +11126,7 @@
     </row>
     <row r="767">
       <c r="A767" t="str">
-        <v>ra.imundo8575</v>
+        <v>viviane_moota</v>
       </c>
       <c r="B767">
         <v>1</v>
@@ -11140,7 +11140,7 @@
     </row>
     <row r="768">
       <c r="A768" t="str">
-        <v>caio.lazzuri</v>
+        <v>ra.imundo8575</v>
       </c>
       <c r="B768">
         <v>1</v>
@@ -11154,7 +11154,7 @@
     </row>
     <row r="769">
       <c r="A769" t="str">
-        <v>rafaella_olliveira08</v>
+        <v>caio.lazzuri</v>
       </c>
       <c r="B769">
         <v>1</v>
@@ -11168,7 +11168,7 @@
     </row>
     <row r="770">
       <c r="A770" t="str">
-        <v>antoniomarcos84</v>
+        <v>rafaella_olliveira08</v>
       </c>
       <c r="B770">
         <v>1</v>
@@ -11182,7 +11182,7 @@
     </row>
     <row r="771">
       <c r="A771" t="str">
-        <v>hipolito.netoo</v>
+        <v>antoniomarcos84</v>
       </c>
       <c r="B771">
         <v>1</v>
@@ -11196,7 +11196,7 @@
     </row>
     <row r="772">
       <c r="A772" t="str">
-        <v>febcm</v>
+        <v>hipolito.netoo</v>
       </c>
       <c r="B772">
         <v>1</v>
@@ -11210,7 +11210,7 @@
     </row>
     <row r="773">
       <c r="A773" t="str">
-        <v>gabriel_angello_</v>
+        <v>febcm</v>
       </c>
       <c r="B773">
         <v>1</v>
@@ -11224,7 +11224,7 @@
     </row>
     <row r="774">
       <c r="A774" t="str">
-        <v>dronearcariri</v>
+        <v>gabriel_angello_</v>
       </c>
       <c r="B774">
         <v>1</v>
@@ -11238,7 +11238,7 @@
     </row>
     <row r="775">
       <c r="A775" t="str">
-        <v>roncy_068</v>
+        <v>dronearcariri</v>
       </c>
       <c r="B775">
         <v>1</v>
@@ -11252,7 +11252,7 @@
     </row>
     <row r="776">
       <c r="A776" t="str">
-        <v>gustavo_vivancos</v>
+        <v>roncy_068</v>
       </c>
       <c r="B776">
         <v>1</v>
@@ -11266,7 +11266,7 @@
     </row>
     <row r="777">
       <c r="A777" t="str">
-        <v>jo.aopedro748</v>
+        <v>gustavo_vivancos</v>
       </c>
       <c r="B777">
         <v>1</v>
@@ -11280,7 +11280,7 @@
     </row>
     <row r="778">
       <c r="A778" t="str">
-        <v>marcoscesarbodo</v>
+        <v>jo.aopedro748</v>
       </c>
       <c r="B778">
         <v>1</v>
@@ -11294,7 +11294,7 @@
     </row>
     <row r="779">
       <c r="A779" t="str">
-        <v>mardonio9549</v>
+        <v>marcoscesarbodo</v>
       </c>
       <c r="B779">
         <v>1</v>
@@ -11308,7 +11308,7 @@
     </row>
     <row r="780">
       <c r="A780" t="str">
-        <v>driigallinucci</v>
+        <v>mardonio9549</v>
       </c>
       <c r="B780">
         <v>1</v>
@@ -11322,7 +11322,7 @@
     </row>
     <row r="781">
       <c r="A781" t="str">
-        <v>araujodiana1231</v>
+        <v>driigallinucci</v>
       </c>
       <c r="B781">
         <v>1</v>
@@ -11336,7 +11336,7 @@
     </row>
     <row r="782">
       <c r="A782" t="str">
-        <v>mr.disciplina</v>
+        <v>araujodiana1231</v>
       </c>
       <c r="B782">
         <v>1</v>
@@ -11350,7 +11350,7 @@
     </row>
     <row r="783">
       <c r="A783" t="str">
-        <v>_franklinxavier</v>
+        <v>mr.disciplina</v>
       </c>
       <c r="B783">
         <v>1</v>
@@ -15618,16 +15618,44 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1088">
+      <c r="A1088" t="str">
+        <v>nofight.nohistory</v>
+      </c>
+      <c r="B1088">
+        <v>0</v>
+      </c>
+      <c r="C1088">
+        <v>1</v>
+      </c>
+      <c r="D1088">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="str">
+        <v>andredida</v>
+      </c>
+      <c r="B1089">
+        <v>0</v>
+      </c>
+      <c r="C1089">
+        <v>1</v>
+      </c>
+      <c r="D1089">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D1087"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1089"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D94"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -15648,13 +15676,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -15662,7 +15690,7 @@
         <v>pedr00jj</v>
       </c>
       <c r="B3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -15701,35 +15729,35 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>luizferrer_br</v>
+        <v>_franklinxavier</v>
       </c>
       <c r="B6">
         <v>2</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>combintel</v>
+        <v>luizferrer_br</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>masonharper_mma</v>
+        <v>combintel</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -15743,7 +15771,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>tiwifenixmma</v>
+        <v>masonharper_mma</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -15757,7 +15785,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>gustavo_brasil09</v>
+        <v>tiwifenixmma</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -15771,7 +15799,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>fabiocesar_1997</v>
+        <v>gustavo_brasil09</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -15785,7 +15813,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>josuemoita1205</v>
+        <v>fabiocesar_1997</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -15799,7 +15827,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>milton_pitbull</v>
+        <v>josuemoita1205</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -15813,7 +15841,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>enzo.gsilva_</v>
+        <v>milton_pitbull</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -15827,7 +15855,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>raffaoito4</v>
+        <v>enzo.gsilva_</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -15841,7 +15869,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>rl_figo</v>
+        <v>raffaoito4</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -15855,7 +15883,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>ultraperegrinospelomundo</v>
+        <v>rl_figo</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -15869,7 +15897,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>claudio_marchese_7</v>
+        <v>ultraperegrinospelomundo</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -15883,27 +15911,27 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>eolucasrosa</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>kelly_ottoni</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B20">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C20">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -15911,35 +15939,35 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>mvp_lutas</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
       <c r="C21">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>alexandroscorreia</v>
+        <v>mvp_lutas</v>
       </c>
       <c r="B22">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>lucifit50</v>
+        <v>alexandroscorreia</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -15953,7 +15981,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>martinscdione</v>
+        <v>lucifit50</v>
       </c>
       <c r="B24">
         <v>1</v>
@@ -15967,7 +15995,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>gustavotoi</v>
+        <v>martinscdione</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -15981,7 +16009,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>erivaldosilva3333</v>
+        <v>gustavotoi</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -15995,7 +16023,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>marcos_r_s_</v>
+        <v>erivaldosilva3333</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -16009,7 +16037,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>biazon87</v>
+        <v>marcos_r_s_</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -16023,7 +16051,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>moys158</v>
+        <v>biazon87</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -16037,7 +16065,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>viviane_moota</v>
+        <v>moys158</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -16051,7 +16079,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>ra.imundo8575</v>
+        <v>viviane_moota</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -16065,7 +16093,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>caio.lazzuri</v>
+        <v>ra.imundo8575</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -16079,7 +16107,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>sambagabrieloficial</v>
+        <v>caio.lazzuri</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -16093,7 +16121,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>rafaella_olliveira08</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -16107,7 +16135,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>antoniomarcos84</v>
+        <v>rafaella_olliveira08</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -16121,7 +16149,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>hipolito.netoo</v>
+        <v>antoniomarcos84</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -16135,7 +16163,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>febcm</v>
+        <v>hipolito.netoo</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -16149,7 +16177,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>gabriel_angello_</v>
+        <v>febcm</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -16163,7 +16191,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>dronearcariri</v>
+        <v>gabriel_angello_</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -16177,7 +16205,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>roncy_068</v>
+        <v>dronearcariri</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -16191,7 +16219,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>mmapalpitex</v>
+        <v>roncy_068</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -16205,7 +16233,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>gustavo_vivancos</v>
+        <v>mmapalpitex</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -16219,7 +16247,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>jo.aopedro748</v>
+        <v>gustavo_vivancos</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -16233,7 +16261,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>marcoscesarbodo</v>
+        <v>jo.aopedro748</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -16247,7 +16275,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>mardonio9549</v>
+        <v>marcoscesarbodo</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -16261,7 +16289,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>driigallinucci</v>
+        <v>mardonio9549</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -16275,7 +16303,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>araujodiana1231</v>
+        <v>driigallinucci</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -16289,7 +16317,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>mr.disciplina</v>
+        <v>araujodiana1231</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -16303,7 +16331,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>jvxz______</v>
+        <v>mr.disciplina</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -16317,7 +16345,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>carlos_hm_iglesias</v>
+        <v>jvxz______</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -16331,7 +16359,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>_franklinxavier</v>
+        <v>carlos_hm_iglesias</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -16917,9 +16945,37 @@
         <v>0</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="str">
+        <v>nofight.nohistory</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+      <c r="C93">
+        <v>1</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="str">
+        <v>andredida</v>
+      </c>
+      <c r="B94">
+        <v>0</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D92"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D94"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-08.xlsx
+++ b/Engagement Rankings 2026-08.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1089"/>
+  <dimension ref="A1:D1095"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -464,7 +464,7 @@
         <v>2194</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D5">
         <v>997</v>
@@ -475,10 +475,10 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>774</v>
@@ -590,7 +590,7 @@
         <v>187</v>
       </c>
       <c r="C14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14">
         <v>60</v>
@@ -615,13 +615,13 @@
         <v>johnmma9</v>
       </c>
       <c r="B16">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
       <c r="D16">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
@@ -657,13 +657,13 @@
         <v>masonharper_mma</v>
       </c>
       <c r="B19">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20">
@@ -674,7 +674,7 @@
         <v>120</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D20">
         <v>61</v>
@@ -685,13 +685,13 @@
         <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B21">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C21">
         <v>54</v>
       </c>
       <c r="D21">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22">
@@ -2012,30 +2012,30 @@
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>npb.enterprise</v>
+        <v>aj_mma_</v>
       </c>
       <c r="B116">
         <v>5</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D116">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>aj_mma_</v>
+        <v>npb.enterprise</v>
       </c>
       <c r="B117">
         <v>5</v>
       </c>
       <c r="C117">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D117">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="118">
@@ -2544,21 +2544,21 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>dagestan0920</v>
+        <v>mvp_lutas</v>
       </c>
       <c r="B154">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C154">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D154">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>cesar.boanerges</v>
+        <v>dagestan0920</v>
       </c>
       <c r="B155">
         <v>5</v>
@@ -2572,35 +2572,35 @@
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>tatibscardoso</v>
+        <v>cesar.boanerges</v>
       </c>
       <c r="B156">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C156">
         <v>0</v>
       </c>
       <c r="D156">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>olifrankiw</v>
+        <v>tatibscardoso</v>
       </c>
       <c r="B157">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C157">
         <v>0</v>
       </c>
       <c r="D157">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>mayarinhafreestyle</v>
+        <v>olifrankiw</v>
       </c>
       <c r="B158">
         <v>6</v>
@@ -2614,30 +2614,30 @@
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>carlos_hm_iglesias</v>
+        <v>mayarinhafreestyle</v>
       </c>
       <c r="B159">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C159">
         <v>0</v>
       </c>
       <c r="D159">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>mvp_lutas</v>
+        <v>carlos_hm_iglesias</v>
       </c>
       <c r="B160">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C160">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D160">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161">
@@ -2866,63 +2866,63 @@
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>salost.ofc</v>
+        <v>peacegrappler_podcast</v>
       </c>
       <c r="B177">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C177">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D177">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>gabrielsouzamma</v>
+        <v>salost.ofc</v>
       </c>
       <c r="B178">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C178">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D178">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>wilson_n_janjacomo</v>
+        <v>gabrielsouzamma</v>
       </c>
       <c r="B179">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C179">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D179">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>helenmacielmma</v>
+        <v>wilson_n_janjacomo</v>
       </c>
       <c r="B180">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C180">
         <v>0</v>
       </c>
       <c r="D180">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>peacegrappler_podcast</v>
+        <v>helenmacielmma</v>
       </c>
       <c r="B181">
         <v>3</v>
@@ -11378,63 +11378,63 @@
     </row>
     <row r="785">
       <c r="A785" t="str">
-        <v>luizcosta_mma</v>
+        <v>marcelonascimentojiujitsu</v>
       </c>
       <c r="B785">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C785">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D785">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="786">
       <c r="A786" t="str">
-        <v>taylor_71kg</v>
+        <v>jairinhovibedeejay</v>
       </c>
       <c r="B786">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C786">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D786">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="str">
-        <v>_vpft</v>
+        <v>vanessa25harreson</v>
       </c>
       <c r="B787">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C787">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D787">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="788">
       <c r="A788" t="str">
-        <v>viniciustbf</v>
+        <v>eu_isasantana1</v>
       </c>
       <c r="B788">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C788">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D788">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="str">
-        <v>dayanaa1511</v>
+        <v>luizcosta_mma</v>
       </c>
       <c r="B789">
         <v>0</v>
@@ -11443,12 +11443,12 @@
         <v>2</v>
       </c>
       <c r="D789">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="790">
       <c r="A790" t="str">
-        <v>danielfranzesilva</v>
+        <v>taylor_71kg</v>
       </c>
       <c r="B790">
         <v>0</v>
@@ -11457,18 +11457,18 @@
         <v>3</v>
       </c>
       <c r="D790">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="791">
       <c r="A791" t="str">
-        <v>ednilsonkaicai</v>
+        <v>_vpft</v>
       </c>
       <c r="B791">
         <v>0</v>
       </c>
       <c r="C791">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D791">
         <v>1</v>
@@ -11476,7 +11476,7 @@
     </row>
     <row r="792">
       <c r="A792" t="str">
-        <v>vanessamelomma</v>
+        <v>viniciustbf</v>
       </c>
       <c r="B792">
         <v>0</v>
@@ -11485,26 +11485,26 @@
         <v>2</v>
       </c>
       <c r="D792">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="793">
       <c r="A793" t="str">
-        <v>michelle_mirele</v>
+        <v>dayanaa1511</v>
       </c>
       <c r="B793">
         <v>0</v>
       </c>
       <c r="C793">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D793">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="794">
       <c r="A794" t="str">
-        <v>geyziellsouza</v>
+        <v>danielfranzesilva</v>
       </c>
       <c r="B794">
         <v>0</v>
@@ -11518,7 +11518,7 @@
     </row>
     <row r="795">
       <c r="A795" t="str">
-        <v>guerreirammaofc</v>
+        <v>ednilsonkaicai</v>
       </c>
       <c r="B795">
         <v>0</v>
@@ -11532,7 +11532,7 @@
     </row>
     <row r="796">
       <c r="A796" t="str">
-        <v>kalaga_vito</v>
+        <v>vanessamelomma</v>
       </c>
       <c r="B796">
         <v>0</v>
@@ -11546,35 +11546,35 @@
     </row>
     <row r="797">
       <c r="A797" t="str">
-        <v>bryandazuera</v>
+        <v>michelle_mirele</v>
       </c>
       <c r="B797">
         <v>0</v>
       </c>
       <c r="C797">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D797">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="798">
       <c r="A798" t="str">
-        <v>danilofernandescf</v>
+        <v>geyziellsouza</v>
       </c>
       <c r="B798">
         <v>0</v>
       </c>
       <c r="C798">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D798">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="799">
       <c r="A799" t="str">
-        <v>4lissson</v>
+        <v>guerreirammaofc</v>
       </c>
       <c r="B799">
         <v>0</v>
@@ -11583,12 +11583,12 @@
         <v>2</v>
       </c>
       <c r="D799">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="800">
       <c r="A800" t="str">
-        <v>vitorshowman</v>
+        <v>kalaga_vito</v>
       </c>
       <c r="B800">
         <v>0</v>
@@ -11597,40 +11597,40 @@
         <v>2</v>
       </c>
       <c r="D800">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="801">
       <c r="A801" t="str">
-        <v>orlando_alfa09</v>
+        <v>bryandazuera</v>
       </c>
       <c r="B801">
         <v>0</v>
       </c>
       <c r="C801">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D801">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="802">
       <c r="A802" t="str">
-        <v>jhonnatanboxe_</v>
+        <v>danilofernandescf</v>
       </c>
       <c r="B802">
         <v>0</v>
       </c>
       <c r="C802">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D802">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="803">
       <c r="A803" t="str">
-        <v>manumito.oficial</v>
+        <v>4lissson</v>
       </c>
       <c r="B803">
         <v>0</v>
@@ -11644,21 +11644,21 @@
     </row>
     <row r="804">
       <c r="A804" t="str">
-        <v>coutz11</v>
+        <v>vitorshowman</v>
       </c>
       <c r="B804">
         <v>0</v>
       </c>
       <c r="C804">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D804">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="805">
       <c r="A805" t="str">
-        <v>eglaudiomma</v>
+        <v>orlando_alfa09</v>
       </c>
       <c r="B805">
         <v>0</v>
@@ -11672,21 +11672,21 @@
     </row>
     <row r="806">
       <c r="A806" t="str">
-        <v>lokomemo_protetores</v>
+        <v>jhonnatanboxe_</v>
       </c>
       <c r="B806">
         <v>0</v>
       </c>
       <c r="C806">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D806">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="807">
       <c r="A807" t="str">
-        <v>carlosnoelblack</v>
+        <v>manumito.oficial</v>
       </c>
       <c r="B807">
         <v>0</v>
@@ -11700,35 +11700,35 @@
     </row>
     <row r="808">
       <c r="A808" t="str">
-        <v>rafaelcmjj</v>
+        <v>coutz11</v>
       </c>
       <c r="B808">
         <v>0</v>
       </c>
       <c r="C808">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D808">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="809">
       <c r="A809" t="str">
-        <v>rahikikhalid</v>
+        <v>eglaudiomma</v>
       </c>
       <c r="B809">
         <v>0</v>
       </c>
       <c r="C809">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D809">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="810">
       <c r="A810" t="str">
-        <v>leonardopateira</v>
+        <v>lokomemo_protetores</v>
       </c>
       <c r="B810">
         <v>0</v>
@@ -11742,7 +11742,7 @@
     </row>
     <row r="811">
       <c r="A811" t="str">
-        <v>tpapereira</v>
+        <v>carlosnoelblack</v>
       </c>
       <c r="B811">
         <v>0</v>
@@ -11756,7 +11756,7 @@
     </row>
     <row r="812">
       <c r="A812" t="str">
-        <v>thalytabjj</v>
+        <v>rafaelcmjj</v>
       </c>
       <c r="B812">
         <v>0</v>
@@ -11770,21 +11770,21 @@
     </row>
     <row r="813">
       <c r="A813" t="str">
-        <v>rafaelantonio.rj</v>
+        <v>rahikikhalid</v>
       </c>
       <c r="B813">
         <v>0</v>
       </c>
       <c r="C813">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D813">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="814">
       <c r="A814" t="str">
-        <v>yasminreis_oficiall</v>
+        <v>leonardopateira</v>
       </c>
       <c r="B814">
         <v>0</v>
@@ -11798,7 +11798,7 @@
     </row>
     <row r="815">
       <c r="A815" t="str">
-        <v>armysenju</v>
+        <v>tpapereira</v>
       </c>
       <c r="B815">
         <v>0</v>
@@ -11812,7 +11812,7 @@
     </row>
     <row r="816">
       <c r="A816" t="str">
-        <v>dnoxsport</v>
+        <v>thalytabjj</v>
       </c>
       <c r="B816">
         <v>0</v>
@@ -11826,7 +11826,7 @@
     </row>
     <row r="817">
       <c r="A817" t="str">
-        <v>kamtalksmma</v>
+        <v>rafaelantonio.rj</v>
       </c>
       <c r="B817">
         <v>0</v>
@@ -11840,7 +11840,7 @@
     </row>
     <row r="818">
       <c r="A818" t="str">
-        <v>arleyleboss</v>
+        <v>yasminreis_oficiall</v>
       </c>
       <c r="B818">
         <v>0</v>
@@ -11854,35 +11854,35 @@
     </row>
     <row r="819">
       <c r="A819" t="str">
-        <v>janjaovix</v>
+        <v>armysenju</v>
       </c>
       <c r="B819">
         <v>0</v>
       </c>
       <c r="C819">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D819">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="820">
       <c r="A820" t="str">
-        <v>dra.izabeldelfino_</v>
+        <v>dnoxsport</v>
       </c>
       <c r="B820">
         <v>0</v>
       </c>
       <c r="C820">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D820">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="821">
       <c r="A821" t="str">
-        <v>jj_miguel05</v>
+        <v>kamtalksmma</v>
       </c>
       <c r="B821">
         <v>0</v>
@@ -11896,7 +11896,7 @@
     </row>
     <row r="822">
       <c r="A822" t="str">
-        <v>joaolucasmma.rocha</v>
+        <v>arleyleboss</v>
       </c>
       <c r="B822">
         <v>0</v>
@@ -11910,7 +11910,7 @@
     </row>
     <row r="823">
       <c r="A823" t="str">
-        <v>edsonbahienseb</v>
+        <v>janjaovix</v>
       </c>
       <c r="B823">
         <v>0</v>
@@ -11924,7 +11924,7 @@
     </row>
     <row r="824">
       <c r="A824" t="str">
-        <v>paulomartins.mma</v>
+        <v>dra.izabeldelfino_</v>
       </c>
       <c r="B824">
         <v>0</v>
@@ -11938,7 +11938,7 @@
     </row>
     <row r="825">
       <c r="A825" t="str">
-        <v>daniel_natel</v>
+        <v>jj_miguel05</v>
       </c>
       <c r="B825">
         <v>0</v>
@@ -11952,7 +11952,7 @@
     </row>
     <row r="826">
       <c r="A826" t="str">
-        <v>dhuks11</v>
+        <v>joaolucasmma.rocha</v>
       </c>
       <c r="B826">
         <v>0</v>
@@ -11961,12 +11961,12 @@
         <v>1</v>
       </c>
       <c r="D826">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="str">
-        <v>macksomlee</v>
+        <v>edsonbahienseb</v>
       </c>
       <c r="B827">
         <v>0</v>
@@ -11980,35 +11980,35 @@
     </row>
     <row r="828">
       <c r="A828" t="str">
-        <v>y_nichimura</v>
+        <v>paulomartins.mma</v>
       </c>
       <c r="B828">
         <v>0</v>
       </c>
       <c r="C828">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D828">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="str">
-        <v>patascubo</v>
+        <v>daniel_natel</v>
       </c>
       <c r="B829">
         <v>0</v>
       </c>
       <c r="C829">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D829">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="str">
-        <v>mayconzilli</v>
+        <v>dhuks11</v>
       </c>
       <c r="B830">
         <v>0</v>
@@ -12017,12 +12017,12 @@
         <v>1</v>
       </c>
       <c r="D830">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="str">
-        <v>jeffesonmeirelles</v>
+        <v>macksomlee</v>
       </c>
       <c r="B831">
         <v>0</v>
@@ -12036,21 +12036,21 @@
     </row>
     <row r="832">
       <c r="A832" t="str">
-        <v>denilson.unit</v>
+        <v>y_nichimura</v>
       </c>
       <c r="B832">
         <v>0</v>
       </c>
       <c r="C832">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D832">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="str">
-        <v>vieirabjj____</v>
+        <v>patascubo</v>
       </c>
       <c r="B833">
         <v>0</v>
@@ -12064,7 +12064,7 @@
     </row>
     <row r="834">
       <c r="A834" t="str">
-        <v>bruno_pontes1992</v>
+        <v>mayconzilli</v>
       </c>
       <c r="B834">
         <v>0</v>
@@ -12078,7 +12078,7 @@
     </row>
     <row r="835">
       <c r="A835" t="str">
-        <v>leandro__parpinelli</v>
+        <v>jeffesonmeirelles</v>
       </c>
       <c r="B835">
         <v>0</v>
@@ -12092,7 +12092,7 @@
     </row>
     <row r="836">
       <c r="A836" t="str">
-        <v>allan10adm</v>
+        <v>denilson.unit</v>
       </c>
       <c r="B836">
         <v>0</v>
@@ -12106,7 +12106,7 @@
     </row>
     <row r="837">
       <c r="A837" t="str">
-        <v>gaby_alves07</v>
+        <v>vieirabjj____</v>
       </c>
       <c r="B837">
         <v>0</v>
@@ -12120,7 +12120,7 @@
     </row>
     <row r="838">
       <c r="A838" t="str">
-        <v>blogfabiocosta</v>
+        <v>bruno_pontes1992</v>
       </c>
       <c r="B838">
         <v>0</v>
@@ -12134,7 +12134,7 @@
     </row>
     <row r="839">
       <c r="A839" t="str">
-        <v>leo_sousa_cabeleleiro</v>
+        <v>leandro__parpinelli</v>
       </c>
       <c r="B839">
         <v>0</v>
@@ -12148,7 +12148,7 @@
     </row>
     <row r="840">
       <c r="A840" t="str">
-        <v>markiim_guerreiro</v>
+        <v>allan10adm</v>
       </c>
       <c r="B840">
         <v>0</v>
@@ -12162,7 +12162,7 @@
     </row>
     <row r="841">
       <c r="A841" t="str">
-        <v>roginbrito</v>
+        <v>gaby_alves07</v>
       </c>
       <c r="B841">
         <v>0</v>
@@ -12171,12 +12171,12 @@
         <v>1</v>
       </c>
       <c r="D841">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="842">
       <c r="A842" t="str">
-        <v>raulcarvalho1010</v>
+        <v>blogfabiocosta</v>
       </c>
       <c r="B842">
         <v>0</v>
@@ -12185,12 +12185,12 @@
         <v>1</v>
       </c>
       <c r="D842">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="843">
       <c r="A843" t="str">
-        <v>gemeaslauraebrenda</v>
+        <v>leo_sousa_cabeleleiro</v>
       </c>
       <c r="B843">
         <v>0</v>
@@ -12199,12 +12199,12 @@
         <v>1</v>
       </c>
       <c r="D843">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="844">
       <c r="A844" t="str">
-        <v>douglas_vitor8</v>
+        <v>markiim_guerreiro</v>
       </c>
       <c r="B844">
         <v>0</v>
@@ -12213,12 +12213,12 @@
         <v>1</v>
       </c>
       <c r="D844">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="845">
       <c r="A845" t="str">
-        <v>kevin.mota95</v>
+        <v>roginbrito</v>
       </c>
       <c r="B845">
         <v>0</v>
@@ -12232,7 +12232,7 @@
     </row>
     <row r="846">
       <c r="A846" t="str">
-        <v>guilhermews1994</v>
+        <v>raulcarvalho1010</v>
       </c>
       <c r="B846">
         <v>0</v>
@@ -12246,7 +12246,7 @@
     </row>
     <row r="847">
       <c r="A847" t="str">
-        <v>tamysregina</v>
+        <v>gemeaslauraebrenda</v>
       </c>
       <c r="B847">
         <v>0</v>
@@ -12260,7 +12260,7 @@
     </row>
     <row r="848">
       <c r="A848" t="str">
-        <v>aline.amaral21</v>
+        <v>douglas_vitor8</v>
       </c>
       <c r="B848">
         <v>0</v>
@@ -12274,7 +12274,7 @@
     </row>
     <row r="849">
       <c r="A849" t="str">
-        <v>katlembrenda</v>
+        <v>kevin.mota95</v>
       </c>
       <c r="B849">
         <v>0</v>
@@ -12288,7 +12288,7 @@
     </row>
     <row r="850">
       <c r="A850" t="str">
-        <v>dudu.acabamentos</v>
+        <v>guilhermews1994</v>
       </c>
       <c r="B850">
         <v>0</v>
@@ -12302,7 +12302,7 @@
     </row>
     <row r="851">
       <c r="A851" t="str">
-        <v>isadoragolimpio</v>
+        <v>tamysregina</v>
       </c>
       <c r="B851">
         <v>0</v>
@@ -12316,7 +12316,7 @@
     </row>
     <row r="852">
       <c r="A852" t="str">
-        <v>audizioandrade</v>
+        <v>aline.amaral21</v>
       </c>
       <c r="B852">
         <v>0</v>
@@ -12330,7 +12330,7 @@
     </row>
     <row r="853">
       <c r="A853" t="str">
-        <v>boradepodcastoficial</v>
+        <v>katlembrenda</v>
       </c>
       <c r="B853">
         <v>0</v>
@@ -12344,7 +12344,7 @@
     </row>
     <row r="854">
       <c r="A854" t="str">
-        <v>marlon_bodybuilding</v>
+        <v>dudu.acabamentos</v>
       </c>
       <c r="B854">
         <v>0</v>
@@ -12358,7 +12358,7 @@
     </row>
     <row r="855">
       <c r="A855" t="str">
-        <v>natalves5</v>
+        <v>isadoragolimpio</v>
       </c>
       <c r="B855">
         <v>0</v>
@@ -12372,7 +12372,7 @@
     </row>
     <row r="856">
       <c r="A856" t="str">
-        <v>barbaracontadora</v>
+        <v>audizioandrade</v>
       </c>
       <c r="B856">
         <v>0</v>
@@ -12386,7 +12386,7 @@
     </row>
     <row r="857">
       <c r="A857" t="str">
-        <v>vidaldanin</v>
+        <v>boradepodcastoficial</v>
       </c>
       <c r="B857">
         <v>0</v>
@@ -12400,7 +12400,7 @@
     </row>
     <row r="858">
       <c r="A858" t="str">
-        <v>andrey_m_s_</v>
+        <v>marlon_bodybuilding</v>
       </c>
       <c r="B858">
         <v>0</v>
@@ -12414,7 +12414,7 @@
     </row>
     <row r="859">
       <c r="A859" t="str">
-        <v>deivssonmanin</v>
+        <v>natalves5</v>
       </c>
       <c r="B859">
         <v>0</v>
@@ -12428,7 +12428,7 @@
     </row>
     <row r="860">
       <c r="A860" t="str">
-        <v>rejr_mma</v>
+        <v>barbaracontadora</v>
       </c>
       <c r="B860">
         <v>0</v>
@@ -12442,7 +12442,7 @@
     </row>
     <row r="861">
       <c r="A861" t="str">
-        <v>felipeocalmon</v>
+        <v>vidaldanin</v>
       </c>
       <c r="B861">
         <v>0</v>
@@ -12456,7 +12456,7 @@
     </row>
     <row r="862">
       <c r="A862" t="str">
-        <v>igorbrasileiro01</v>
+        <v>andrey_m_s_</v>
       </c>
       <c r="B862">
         <v>0</v>
@@ -12470,7 +12470,7 @@
     </row>
     <row r="863">
       <c r="A863" t="str">
-        <v>joaolauar_</v>
+        <v>deivssonmanin</v>
       </c>
       <c r="B863">
         <v>0</v>
@@ -12484,7 +12484,7 @@
     </row>
     <row r="864">
       <c r="A864" t="str">
-        <v>michele_mixa</v>
+        <v>rejr_mma</v>
       </c>
       <c r="B864">
         <v>0</v>
@@ -12498,7 +12498,7 @@
     </row>
     <row r="865">
       <c r="A865" t="str">
-        <v>nataliaemanuela.personal</v>
+        <v>felipeocalmon</v>
       </c>
       <c r="B865">
         <v>0</v>
@@ -12512,7 +12512,7 @@
     </row>
     <row r="866">
       <c r="A866" t="str">
-        <v>benicius_edu</v>
+        <v>igorbrasileiro01</v>
       </c>
       <c r="B866">
         <v>0</v>
@@ -12526,7 +12526,7 @@
     </row>
     <row r="867">
       <c r="A867" t="str">
-        <v>andreza.thais.1</v>
+        <v>joaolauar_</v>
       </c>
       <c r="B867">
         <v>0</v>
@@ -12540,7 +12540,7 @@
     </row>
     <row r="868">
       <c r="A868" t="str">
-        <v>julckreis</v>
+        <v>michele_mixa</v>
       </c>
       <c r="B868">
         <v>0</v>
@@ -12554,7 +12554,7 @@
     </row>
     <row r="869">
       <c r="A869" t="str">
-        <v>alineanne_</v>
+        <v>nataliaemanuela.personal</v>
       </c>
       <c r="B869">
         <v>0</v>
@@ -12568,7 +12568,7 @@
     </row>
     <row r="870">
       <c r="A870" t="str">
-        <v>romulerasilva</v>
+        <v>benicius_edu</v>
       </c>
       <c r="B870">
         <v>0</v>
@@ -12582,7 +12582,7 @@
     </row>
     <row r="871">
       <c r="A871" t="str">
-        <v>higorsaantana</v>
+        <v>andreza.thais.1</v>
       </c>
       <c r="B871">
         <v>0</v>
@@ -12596,7 +12596,7 @@
     </row>
     <row r="872">
       <c r="A872" t="str">
-        <v>vitorcosta_mma</v>
+        <v>julckreis</v>
       </c>
       <c r="B872">
         <v>0</v>
@@ -12610,7 +12610,7 @@
     </row>
     <row r="873">
       <c r="A873" t="str">
-        <v>paulo.titoo</v>
+        <v>alineanne_</v>
       </c>
       <c r="B873">
         <v>0</v>
@@ -12624,7 +12624,7 @@
     </row>
     <row r="874">
       <c r="A874" t="str">
-        <v>1000ton_n</v>
+        <v>romulerasilva</v>
       </c>
       <c r="B874">
         <v>0</v>
@@ -12638,7 +12638,7 @@
     </row>
     <row r="875">
       <c r="A875" t="str">
-        <v>anamatias.m</v>
+        <v>higorsaantana</v>
       </c>
       <c r="B875">
         <v>0</v>
@@ -12652,7 +12652,7 @@
     </row>
     <row r="876">
       <c r="A876" t="str">
-        <v>taporondebruno</v>
+        <v>vitorcosta_mma</v>
       </c>
       <c r="B876">
         <v>0</v>
@@ -12666,7 +12666,7 @@
     </row>
     <row r="877">
       <c r="A877" t="str">
-        <v>ricardotofanello</v>
+        <v>paulo.titoo</v>
       </c>
       <c r="B877">
         <v>0</v>
@@ -12680,7 +12680,7 @@
     </row>
     <row r="878">
       <c r="A878" t="str">
-        <v>strong_stg_oficial</v>
+        <v>1000ton_n</v>
       </c>
       <c r="B878">
         <v>0</v>
@@ -12694,7 +12694,7 @@
     </row>
     <row r="879">
       <c r="A879" t="str">
-        <v>nuncadesistir.nd</v>
+        <v>anamatias.m</v>
       </c>
       <c r="B879">
         <v>0</v>
@@ -12708,7 +12708,7 @@
     </row>
     <row r="880">
       <c r="A880" t="str">
-        <v>sabrinaalsilva</v>
+        <v>taporondebruno</v>
       </c>
       <c r="B880">
         <v>0</v>
@@ -12722,7 +12722,7 @@
     </row>
     <row r="881">
       <c r="A881" t="str">
-        <v>caioparangole</v>
+        <v>ricardotofanello</v>
       </c>
       <c r="B881">
         <v>0</v>
@@ -12736,7 +12736,7 @@
     </row>
     <row r="882">
       <c r="A882" t="str">
-        <v>leaoanaalice</v>
+        <v>strong_stg_oficial</v>
       </c>
       <c r="B882">
         <v>0</v>
@@ -12750,7 +12750,7 @@
     </row>
     <row r="883">
       <c r="A883" t="str">
-        <v>pe.mirandas</v>
+        <v>nuncadesistir.nd</v>
       </c>
       <c r="B883">
         <v>0</v>
@@ -12764,7 +12764,7 @@
     </row>
     <row r="884">
       <c r="A884" t="str">
-        <v>doraasivla</v>
+        <v>sabrinaalsilva</v>
       </c>
       <c r="B884">
         <v>0</v>
@@ -12778,7 +12778,7 @@
     </row>
     <row r="885">
       <c r="A885" t="str">
-        <v>marcilio.silva.71404</v>
+        <v>caioparangole</v>
       </c>
       <c r="B885">
         <v>0</v>
@@ -12792,7 +12792,7 @@
     </row>
     <row r="886">
       <c r="A886" t="str">
-        <v>cristianomarcello</v>
+        <v>leaoanaalice</v>
       </c>
       <c r="B886">
         <v>0</v>
@@ -12806,7 +12806,7 @@
     </row>
     <row r="887">
       <c r="A887" t="str">
-        <v>herrickmarinho</v>
+        <v>pe.mirandas</v>
       </c>
       <c r="B887">
         <v>0</v>
@@ -12820,7 +12820,7 @@
     </row>
     <row r="888">
       <c r="A888" t="str">
-        <v>kfcampeoes</v>
+        <v>doraasivla</v>
       </c>
       <c r="B888">
         <v>0</v>
@@ -12834,7 +12834,7 @@
     </row>
     <row r="889">
       <c r="A889" t="str">
-        <v>sejamotivadorofc</v>
+        <v>marcilio.silva.71404</v>
       </c>
       <c r="B889">
         <v>0</v>
@@ -12848,7 +12848,7 @@
     </row>
     <row r="890">
       <c r="A890" t="str">
-        <v>oliveiraandiarabjj</v>
+        <v>cristianomarcello</v>
       </c>
       <c r="B890">
         <v>0</v>
@@ -12862,7 +12862,7 @@
     </row>
     <row r="891">
       <c r="A891" t="str">
-        <v>dandraco_</v>
+        <v>herrickmarinho</v>
       </c>
       <c r="B891">
         <v>0</v>
@@ -12876,7 +12876,7 @@
     </row>
     <row r="892">
       <c r="A892" t="str">
-        <v>chubotaru_lilu</v>
+        <v>kfcampeoes</v>
       </c>
       <c r="B892">
         <v>0</v>
@@ -12890,7 +12890,7 @@
     </row>
     <row r="893">
       <c r="A893" t="str">
-        <v>esteticaluharruda</v>
+        <v>sejamotivadorofc</v>
       </c>
       <c r="B893">
         <v>0</v>
@@ -12904,7 +12904,7 @@
     </row>
     <row r="894">
       <c r="A894" t="str">
-        <v>dadwillians</v>
+        <v>oliveiraandiarabjj</v>
       </c>
       <c r="B894">
         <v>0</v>
@@ -12918,7 +12918,7 @@
     </row>
     <row r="895">
       <c r="A895" t="str">
-        <v>vanemessina</v>
+        <v>dandraco_</v>
       </c>
       <c r="B895">
         <v>0</v>
@@ -12932,7 +12932,7 @@
     </row>
     <row r="896">
       <c r="A896" t="str">
-        <v>geanne_franca_</v>
+        <v>chubotaru_lilu</v>
       </c>
       <c r="B896">
         <v>0</v>
@@ -12946,7 +12946,7 @@
     </row>
     <row r="897">
       <c r="A897" t="str">
-        <v>victor_brunopersonal</v>
+        <v>esteticaluharruda</v>
       </c>
       <c r="B897">
         <v>0</v>
@@ -12960,7 +12960,7 @@
     </row>
     <row r="898">
       <c r="A898" t="str">
-        <v>omar_alneaimi</v>
+        <v>dadwillians</v>
       </c>
       <c r="B898">
         <v>0</v>
@@ -12974,7 +12974,7 @@
     </row>
     <row r="899">
       <c r="A899" t="str">
-        <v>jimmy_indioap</v>
+        <v>vanemessina</v>
       </c>
       <c r="B899">
         <v>0</v>
@@ -12988,7 +12988,7 @@
     </row>
     <row r="900">
       <c r="A900" t="str">
-        <v>_kainanlima</v>
+        <v>geanne_franca_</v>
       </c>
       <c r="B900">
         <v>0</v>
@@ -13002,7 +13002,7 @@
     </row>
     <row r="901">
       <c r="A901" t="str">
-        <v>mariacleusa.lopes</v>
+        <v>victor_brunopersonal</v>
       </c>
       <c r="B901">
         <v>0</v>
@@ -13016,7 +13016,7 @@
     </row>
     <row r="902">
       <c r="A902" t="str">
-        <v>leziamorbeck50</v>
+        <v>omar_alneaimi</v>
       </c>
       <c r="B902">
         <v>0</v>
@@ -13030,7 +13030,7 @@
     </row>
     <row r="903">
       <c r="A903" t="str">
-        <v>andrearschack</v>
+        <v>jimmy_indioap</v>
       </c>
       <c r="B903">
         <v>0</v>
@@ -13044,7 +13044,7 @@
     </row>
     <row r="904">
       <c r="A904" t="str">
-        <v>martinpakciarz</v>
+        <v>_kainanlima</v>
       </c>
       <c r="B904">
         <v>0</v>
@@ -13058,7 +13058,7 @@
     </row>
     <row r="905">
       <c r="A905" t="str">
-        <v>rafaelbipolarufc</v>
+        <v>mariacleusa.lopes</v>
       </c>
       <c r="B905">
         <v>0</v>
@@ -13072,7 +13072,7 @@
     </row>
     <row r="906">
       <c r="A906" t="str">
-        <v>meirelesmma</v>
+        <v>leziamorbeck50</v>
       </c>
       <c r="B906">
         <v>0</v>
@@ -13086,7 +13086,7 @@
     </row>
     <row r="907">
       <c r="A907" t="str">
-        <v>teamsilverio</v>
+        <v>andrearschack</v>
       </c>
       <c r="B907">
         <v>0</v>
@@ -13100,7 +13100,7 @@
     </row>
     <row r="908">
       <c r="A908" t="str">
-        <v>tatiaradias</v>
+        <v>martinpakciarz</v>
       </c>
       <c r="B908">
         <v>0</v>
@@ -13114,7 +13114,7 @@
     </row>
     <row r="909">
       <c r="A909" t="str">
-        <v>miltoncjr28</v>
+        <v>rafaelbipolarufc</v>
       </c>
       <c r="B909">
         <v>0</v>
@@ -13128,7 +13128,7 @@
     </row>
     <row r="910">
       <c r="A910" t="str">
-        <v>leafarlemos</v>
+        <v>meirelesmma</v>
       </c>
       <c r="B910">
         <v>0</v>
@@ -13142,7 +13142,7 @@
     </row>
     <row r="911">
       <c r="A911" t="str">
-        <v>thiagopssantos</v>
+        <v>teamsilverio</v>
       </c>
       <c r="B911">
         <v>0</v>
@@ -13156,7 +13156,7 @@
     </row>
     <row r="912">
       <c r="A912" t="str">
-        <v>daniloacordeon_oficial</v>
+        <v>tatiaradias</v>
       </c>
       <c r="B912">
         <v>0</v>
@@ -13170,7 +13170,7 @@
     </row>
     <row r="913">
       <c r="A913" t="str">
-        <v>dorgivan13_bjj</v>
+        <v>miltoncjr28</v>
       </c>
       <c r="B913">
         <v>0</v>
@@ -13184,7 +13184,7 @@
     </row>
     <row r="914">
       <c r="A914" t="str">
-        <v>ryu_artes_marciais</v>
+        <v>leafarlemos</v>
       </c>
       <c r="B914">
         <v>0</v>
@@ -13198,7 +13198,7 @@
     </row>
     <row r="915">
       <c r="A915" t="str">
-        <v>marques.__bjj</v>
+        <v>thiagopssantos</v>
       </c>
       <c r="B915">
         <v>0</v>
@@ -13212,7 +13212,7 @@
     </row>
     <row r="916">
       <c r="A916" t="str">
-        <v>foryousaudeespecializada</v>
+        <v>daniloacordeon_oficial</v>
       </c>
       <c r="B916">
         <v>0</v>
@@ -13226,7 +13226,7 @@
     </row>
     <row r="917">
       <c r="A917" t="str">
-        <v>soniarmurata</v>
+        <v>dorgivan13_bjj</v>
       </c>
       <c r="B917">
         <v>0</v>
@@ -13240,7 +13240,7 @@
     </row>
     <row r="918">
       <c r="A918" t="str">
-        <v>almeidajjwk</v>
+        <v>ryu_artes_marciais</v>
       </c>
       <c r="B918">
         <v>0</v>
@@ -13254,7 +13254,7 @@
     </row>
     <row r="919">
       <c r="A919" t="str">
-        <v>dvlucc2k26_</v>
+        <v>marques.__bjj</v>
       </c>
       <c r="B919">
         <v>0</v>
@@ -13268,7 +13268,7 @@
     </row>
     <row r="920">
       <c r="A920" t="str">
-        <v>otaviocarneiromma</v>
+        <v>foryousaudeespecializada</v>
       </c>
       <c r="B920">
         <v>0</v>
@@ -13282,7 +13282,7 @@
     </row>
     <row r="921">
       <c r="A921" t="str">
-        <v>ayman__falil_06</v>
+        <v>soniarmurata</v>
       </c>
       <c r="B921">
         <v>0</v>
@@ -13296,7 +13296,7 @@
     </row>
     <row r="922">
       <c r="A922" t="str">
-        <v>lurochachef</v>
+        <v>almeidajjwk</v>
       </c>
       <c r="B922">
         <v>0</v>
@@ -13310,7 +13310,7 @@
     </row>
     <row r="923">
       <c r="A923" t="str">
-        <v>thayanne_rodrigues_bjj</v>
+        <v>dvlucc2k26_</v>
       </c>
       <c r="B923">
         <v>0</v>
@@ -13324,7 +13324,7 @@
     </row>
     <row r="924">
       <c r="A924" t="str">
-        <v>galindofrontado</v>
+        <v>otaviocarneiromma</v>
       </c>
       <c r="B924">
         <v>0</v>
@@ -13338,7 +13338,7 @@
     </row>
     <row r="925">
       <c r="A925" t="str">
-        <v>laureanucalvo</v>
+        <v>ayman__falil_06</v>
       </c>
       <c r="B925">
         <v>0</v>
@@ -13352,7 +13352,7 @@
     </row>
     <row r="926">
       <c r="A926" t="str">
-        <v>gisbedejose</v>
+        <v>lurochachef</v>
       </c>
       <c r="B926">
         <v>0</v>
@@ -13366,7 +13366,7 @@
     </row>
     <row r="927">
       <c r="A927" t="str">
-        <v>mauriciogeorge</v>
+        <v>thayanne_rodrigues_bjj</v>
       </c>
       <c r="B927">
         <v>0</v>
@@ -13380,7 +13380,7 @@
     </row>
     <row r="928">
       <c r="A928" t="str">
-        <v>viniciusmorais.bjj</v>
+        <v>galindofrontado</v>
       </c>
       <c r="B928">
         <v>0</v>
@@ -13394,7 +13394,7 @@
     </row>
     <row r="929">
       <c r="A929" t="str">
-        <v>gandrapaulino</v>
+        <v>laureanucalvo</v>
       </c>
       <c r="B929">
         <v>0</v>
@@ -13408,7 +13408,7 @@
     </row>
     <row r="930">
       <c r="A930" t="str">
-        <v>chalakakavinda</v>
+        <v>gisbedejose</v>
       </c>
       <c r="B930">
         <v>0</v>
@@ -13422,7 +13422,7 @@
     </row>
     <row r="931">
       <c r="A931" t="str">
-        <v>pgmarquesantos</v>
+        <v>mauriciogeorge</v>
       </c>
       <c r="B931">
         <v>0</v>
@@ -13436,7 +13436,7 @@
     </row>
     <row r="932">
       <c r="A932" t="str">
-        <v>uluukyrgyz_tima</v>
+        <v>viniciusmorais.bjj</v>
       </c>
       <c r="B932">
         <v>0</v>
@@ -13450,7 +13450,7 @@
     </row>
     <row r="933">
       <c r="A933" t="str">
-        <v>kells2vallone</v>
+        <v>gandrapaulino</v>
       </c>
       <c r="B933">
         <v>0</v>
@@ -13464,7 +13464,7 @@
     </row>
     <row r="934">
       <c r="A934" t="str">
-        <v>personaljakeline</v>
+        <v>chalakakavinda</v>
       </c>
       <c r="B934">
         <v>0</v>
@@ -13478,7 +13478,7 @@
     </row>
     <row r="935">
       <c r="A935" t="str">
-        <v>marcaojudobjjmaster</v>
+        <v>pgmarquesantos</v>
       </c>
       <c r="B935">
         <v>0</v>
@@ -13492,7 +13492,7 @@
     </row>
     <row r="936">
       <c r="A936" t="str">
-        <v>sergiorenatocruz1</v>
+        <v>uluukyrgyz_tima</v>
       </c>
       <c r="B936">
         <v>0</v>
@@ -13506,7 +13506,7 @@
     </row>
     <row r="937">
       <c r="A937" t="str">
-        <v>bjjfalkenberg</v>
+        <v>kells2vallone</v>
       </c>
       <c r="B937">
         <v>0</v>
@@ -13520,7 +13520,7 @@
     </row>
     <row r="938">
       <c r="A938" t="str">
-        <v>covil.045</v>
+        <v>personaljakeline</v>
       </c>
       <c r="B938">
         <v>0</v>
@@ -13534,7 +13534,7 @@
     </row>
     <row r="939">
       <c r="A939" t="str">
-        <v>indio_mma</v>
+        <v>marcaojudobjjmaster</v>
       </c>
       <c r="B939">
         <v>0</v>
@@ -13548,7 +13548,7 @@
     </row>
     <row r="940">
       <c r="A940" t="str">
-        <v>alomaraujo</v>
+        <v>sergiorenatocruz1</v>
       </c>
       <c r="B940">
         <v>0</v>
@@ -13562,7 +13562,7 @@
     </row>
     <row r="941">
       <c r="A941" t="str">
-        <v>allandelano</v>
+        <v>bjjfalkenberg</v>
       </c>
       <c r="B941">
         <v>0</v>
@@ -13576,7 +13576,7 @@
     </row>
     <row r="942">
       <c r="A942" t="str">
-        <v>theanimallifemovement</v>
+        <v>covil.045</v>
       </c>
       <c r="B942">
         <v>0</v>
@@ -13590,7 +13590,7 @@
     </row>
     <row r="943">
       <c r="A943" t="str">
-        <v>tombg_64</v>
+        <v>indio_mma</v>
       </c>
       <c r="B943">
         <v>0</v>
@@ -13604,7 +13604,7 @@
     </row>
     <row r="944">
       <c r="A944" t="str">
-        <v>andreichubotaru94</v>
+        <v>alomaraujo</v>
       </c>
       <c r="B944">
         <v>0</v>
@@ -13618,7 +13618,7 @@
     </row>
     <row r="945">
       <c r="A945" t="str">
-        <v>michaeloliveiramma</v>
+        <v>allandelano</v>
       </c>
       <c r="B945">
         <v>0</v>
@@ -13632,7 +13632,7 @@
     </row>
     <row r="946">
       <c r="A946" t="str">
-        <v>helaynecrisl</v>
+        <v>theanimallifemovement</v>
       </c>
       <c r="B946">
         <v>0</v>
@@ -13646,7 +13646,7 @@
     </row>
     <row r="947">
       <c r="A947" t="str">
-        <v>carinhakkz</v>
+        <v>tombg_64</v>
       </c>
       <c r="B947">
         <v>0</v>
@@ -13660,7 +13660,7 @@
     </row>
     <row r="948">
       <c r="A948" t="str">
-        <v>lmk_sport</v>
+        <v>andreichubotaru94</v>
       </c>
       <c r="B948">
         <v>0</v>
@@ -13674,7 +13674,7 @@
     </row>
     <row r="949">
       <c r="A949" t="str">
-        <v>mirnacaroline</v>
+        <v>michaeloliveiramma</v>
       </c>
       <c r="B949">
         <v>0</v>
@@ -13688,7 +13688,7 @@
     </row>
     <row r="950">
       <c r="A950" t="str">
-        <v>udilimaheroi</v>
+        <v>helaynecrisl</v>
       </c>
       <c r="B950">
         <v>0</v>
@@ -13702,7 +13702,7 @@
     </row>
     <row r="951">
       <c r="A951" t="str">
-        <v>oliveiraa_00.11</v>
+        <v>carinhakkz</v>
       </c>
       <c r="B951">
         <v>0</v>
@@ -13716,7 +13716,7 @@
     </row>
     <row r="952">
       <c r="A952" t="str">
-        <v>cristiannogueira.vtt</v>
+        <v>lmk_sport</v>
       </c>
       <c r="B952">
         <v>0</v>
@@ -13730,7 +13730,7 @@
     </row>
     <row r="953">
       <c r="A953" t="str">
-        <v>fher.nando_</v>
+        <v>mirnacaroline</v>
       </c>
       <c r="B953">
         <v>0</v>
@@ -13744,7 +13744,7 @@
     </row>
     <row r="954">
       <c r="A954" t="str">
-        <v>heloisa_elohim</v>
+        <v>udilimaheroi</v>
       </c>
       <c r="B954">
         <v>0</v>
@@ -13758,7 +13758,7 @@
     </row>
     <row r="955">
       <c r="A955" t="str">
-        <v>raulbasilioo</v>
+        <v>oliveiraa_00.11</v>
       </c>
       <c r="B955">
         <v>0</v>
@@ -13772,7 +13772,7 @@
     </row>
     <row r="956">
       <c r="A956" t="str">
-        <v>djuliaarianamma</v>
+        <v>cristiannogueira.vtt</v>
       </c>
       <c r="B956">
         <v>0</v>
@@ -13786,7 +13786,7 @@
     </row>
     <row r="957">
       <c r="A957" t="str">
-        <v>adrianaramosalvesribeiro</v>
+        <v>fher.nando_</v>
       </c>
       <c r="B957">
         <v>0</v>
@@ -13800,7 +13800,7 @@
     </row>
     <row r="958">
       <c r="A958" t="str">
-        <v>alexandrefideliis</v>
+        <v>heloisa_elohim</v>
       </c>
       <c r="B958">
         <v>0</v>
@@ -13814,7 +13814,7 @@
     </row>
     <row r="959">
       <c r="A959" t="str">
-        <v>massoterapeuta_bemestarr</v>
+        <v>raulbasilioo</v>
       </c>
       <c r="B959">
         <v>0</v>
@@ -13828,7 +13828,7 @@
     </row>
     <row r="960">
       <c r="A960" t="str">
-        <v>ellida_guimaraes</v>
+        <v>djuliaarianamma</v>
       </c>
       <c r="B960">
         <v>0</v>
@@ -13842,7 +13842,7 @@
     </row>
     <row r="961">
       <c r="A961" t="str">
-        <v>hostonhugo</v>
+        <v>adrianaramosalvesribeiro</v>
       </c>
       <c r="B961">
         <v>0</v>
@@ -13856,7 +13856,7 @@
     </row>
     <row r="962">
       <c r="A962" t="str">
-        <v>pammygaryo</v>
+        <v>alexandrefideliis</v>
       </c>
       <c r="B962">
         <v>0</v>
@@ -13870,7 +13870,7 @@
     </row>
     <row r="963">
       <c r="A963" t="str">
-        <v>bastazinifilho</v>
+        <v>massoterapeuta_bemestarr</v>
       </c>
       <c r="B963">
         <v>0</v>
@@ -13884,7 +13884,7 @@
     </row>
     <row r="964">
       <c r="A964" t="str">
-        <v>beatrizosilveira</v>
+        <v>ellida_guimaraes</v>
       </c>
       <c r="B964">
         <v>0</v>
@@ -13898,7 +13898,7 @@
     </row>
     <row r="965">
       <c r="A965" t="str">
-        <v>danieldias7s</v>
+        <v>hostonhugo</v>
       </c>
       <c r="B965">
         <v>0</v>
@@ -13912,7 +13912,7 @@
     </row>
     <row r="966">
       <c r="A966" t="str">
-        <v>pepefightteam</v>
+        <v>pammygaryo</v>
       </c>
       <c r="B966">
         <v>0</v>
@@ -13926,7 +13926,7 @@
     </row>
     <row r="967">
       <c r="A967" t="str">
-        <v>ildemarmarajo</v>
+        <v>bastazinifilho</v>
       </c>
       <c r="B967">
         <v>0</v>
@@ -13940,7 +13940,7 @@
     </row>
     <row r="968">
       <c r="A968" t="str">
-        <v>tavaresguu</v>
+        <v>beatrizosilveira</v>
       </c>
       <c r="B968">
         <v>0</v>
@@ -13954,7 +13954,7 @@
     </row>
     <row r="969">
       <c r="A969" t="str">
-        <v>zeferinomma</v>
+        <v>danieldias7s</v>
       </c>
       <c r="B969">
         <v>0</v>
@@ -13968,7 +13968,7 @@
     </row>
     <row r="970">
       <c r="A970" t="str">
-        <v>vitorpaes_personalfight</v>
+        <v>pepefightteam</v>
       </c>
       <c r="B970">
         <v>0</v>
@@ -13982,7 +13982,7 @@
     </row>
     <row r="971">
       <c r="A971" t="str">
-        <v>kaynankruschewsky_ufc</v>
+        <v>ildemarmarajo</v>
       </c>
       <c r="B971">
         <v>0</v>
@@ -13996,7 +13996,7 @@
     </row>
     <row r="972">
       <c r="A972" t="str">
-        <v>fabio.sampaio.90260</v>
+        <v>tavaresguu</v>
       </c>
       <c r="B972">
         <v>0</v>
@@ -14010,7 +14010,7 @@
     </row>
     <row r="973">
       <c r="A973" t="str">
-        <v>marcusvgsz</v>
+        <v>zeferinomma</v>
       </c>
       <c r="B973">
         <v>0</v>
@@ -14024,7 +14024,7 @@
     </row>
     <row r="974">
       <c r="A974" t="str">
-        <v>ganemfelipe</v>
+        <v>vitorpaes_personalfight</v>
       </c>
       <c r="B974">
         <v>0</v>
@@ -14038,7 +14038,7 @@
     </row>
     <row r="975">
       <c r="A975" t="str">
-        <v>ale.lagonegro</v>
+        <v>kaynankruschewsky_ufc</v>
       </c>
       <c r="B975">
         <v>0</v>
@@ -14052,7 +14052,7 @@
     </row>
     <row r="976">
       <c r="A976" t="str">
-        <v>ianrochaf</v>
+        <v>fabio.sampaio.90260</v>
       </c>
       <c r="B976">
         <v>0</v>
@@ -14066,7 +14066,7 @@
     </row>
     <row r="977">
       <c r="A977" t="str">
-        <v>marcotulio_matuto</v>
+        <v>marcusvgsz</v>
       </c>
       <c r="B977">
         <v>0</v>
@@ -14080,7 +14080,7 @@
     </row>
     <row r="978">
       <c r="A978" t="str">
-        <v>anselmo.azevedo</v>
+        <v>ganemfelipe</v>
       </c>
       <c r="B978">
         <v>0</v>
@@ -14094,7 +14094,7 @@
     </row>
     <row r="979">
       <c r="A979" t="str">
-        <v>lincoln__puig77</v>
+        <v>ale.lagonegro</v>
       </c>
       <c r="B979">
         <v>0</v>
@@ -14108,7 +14108,7 @@
     </row>
     <row r="980">
       <c r="A980" t="str">
-        <v>sougustavorosa</v>
+        <v>ianrochaf</v>
       </c>
       <c r="B980">
         <v>0</v>
@@ -14122,7 +14122,7 @@
     </row>
     <row r="981">
       <c r="A981" t="str">
-        <v>sem_saida.12</v>
+        <v>marcotulio_matuto</v>
       </c>
       <c r="B981">
         <v>0</v>
@@ -14136,7 +14136,7 @@
     </row>
     <row r="982">
       <c r="A982" t="str">
-        <v>lyviaestherbjj</v>
+        <v>anselmo.azevedo</v>
       </c>
       <c r="B982">
         <v>0</v>
@@ -14150,7 +14150,7 @@
     </row>
     <row r="983">
       <c r="A983" t="str">
-        <v>macio.almeida_89</v>
+        <v>lincoln__puig77</v>
       </c>
       <c r="B983">
         <v>0</v>
@@ -14164,7 +14164,7 @@
     </row>
     <row r="984">
       <c r="A984" t="str">
-        <v>helman_mma70</v>
+        <v>sougustavorosa</v>
       </c>
       <c r="B984">
         <v>0</v>
@@ -14178,7 +14178,7 @@
     </row>
     <row r="985">
       <c r="A985" t="str">
-        <v>brun_oguerreiro</v>
+        <v>sem_saida.12</v>
       </c>
       <c r="B985">
         <v>0</v>
@@ -14192,7 +14192,7 @@
     </row>
     <row r="986">
       <c r="A986" t="str">
-        <v>ohanna.anselmo</v>
+        <v>lyviaestherbjj</v>
       </c>
       <c r="B986">
         <v>0</v>
@@ -14206,7 +14206,7 @@
     </row>
     <row r="987">
       <c r="A987" t="str">
-        <v>malene_elleen</v>
+        <v>macio.almeida_89</v>
       </c>
       <c r="B987">
         <v>0</v>
@@ -14220,7 +14220,7 @@
     </row>
     <row r="988">
       <c r="A988" t="str">
-        <v>kevinlopes_bjj</v>
+        <v>helman_mma70</v>
       </c>
       <c r="B988">
         <v>0</v>
@@ -14234,7 +14234,7 @@
     </row>
     <row r="989">
       <c r="A989" t="str">
-        <v>caioleonjj</v>
+        <v>brun_oguerreiro</v>
       </c>
       <c r="B989">
         <v>0</v>
@@ -14248,7 +14248,7 @@
     </row>
     <row r="990">
       <c r="A990" t="str">
-        <v>jeferson_tijolo1</v>
+        <v>ohanna.anselmo</v>
       </c>
       <c r="B990">
         <v>0</v>
@@ -14262,7 +14262,7 @@
     </row>
     <row r="991">
       <c r="A991" t="str">
-        <v>fdanieljj</v>
+        <v>malene_elleen</v>
       </c>
       <c r="B991">
         <v>0</v>
@@ -14276,7 +14276,7 @@
     </row>
     <row r="992">
       <c r="A992" t="str">
-        <v>makelele_bjj</v>
+        <v>kevinlopes_bjj</v>
       </c>
       <c r="B992">
         <v>0</v>
@@ -14290,7 +14290,7 @@
     </row>
     <row r="993">
       <c r="A993" t="str">
-        <v>dreamartpro</v>
+        <v>caioleonjj</v>
       </c>
       <c r="B993">
         <v>0</v>
@@ -14304,7 +14304,7 @@
     </row>
     <row r="994">
       <c r="A994" t="str">
-        <v>andressa_bjj_</v>
+        <v>jeferson_tijolo1</v>
       </c>
       <c r="B994">
         <v>0</v>
@@ -14318,7 +14318,7 @@
     </row>
     <row r="995">
       <c r="A995" t="str">
-        <v>karine_killer_ufc</v>
+        <v>fdanieljj</v>
       </c>
       <c r="B995">
         <v>0</v>
@@ -14332,7 +14332,7 @@
     </row>
     <row r="996">
       <c r="A996" t="str">
-        <v>wendel_bjj14</v>
+        <v>makelele_bjj</v>
       </c>
       <c r="B996">
         <v>0</v>
@@ -14346,7 +14346,7 @@
     </row>
     <row r="997">
       <c r="A997" t="str">
-        <v>tamarapq</v>
+        <v>dreamartpro</v>
       </c>
       <c r="B997">
         <v>0</v>
@@ -14360,7 +14360,7 @@
     </row>
     <row r="998">
       <c r="A998" t="str">
-        <v>thaynara_victoria_</v>
+        <v>andressa_bjj_</v>
       </c>
       <c r="B998">
         <v>0</v>
@@ -14374,7 +14374,7 @@
     </row>
     <row r="999">
       <c r="A999" t="str">
-        <v>mma.fisio</v>
+        <v>karine_killer_ufc</v>
       </c>
       <c r="B999">
         <v>0</v>
@@ -14388,7 +14388,7 @@
     </row>
     <row r="1000">
       <c r="A1000" t="str">
-        <v>danielplayboymt</v>
+        <v>wendel_bjj14</v>
       </c>
       <c r="B1000">
         <v>0</v>
@@ -14402,7 +14402,7 @@
     </row>
     <row r="1001">
       <c r="A1001" t="str">
-        <v>chunco_424</v>
+        <v>tamarapq</v>
       </c>
       <c r="B1001">
         <v>0</v>
@@ -14416,7 +14416,7 @@
     </row>
     <row r="1002">
       <c r="A1002" t="str">
-        <v>fix.pec</v>
+        <v>thaynara_victoria_</v>
       </c>
       <c r="B1002">
         <v>0</v>
@@ -14430,7 +14430,7 @@
     </row>
     <row r="1003">
       <c r="A1003" t="str">
-        <v>roxostrike</v>
+        <v>mma.fisio</v>
       </c>
       <c r="B1003">
         <v>0</v>
@@ -14444,7 +14444,7 @@
     </row>
     <row r="1004">
       <c r="A1004" t="str">
-        <v>josita_bjj</v>
+        <v>danielplayboymt</v>
       </c>
       <c r="B1004">
         <v>0</v>
@@ -14458,7 +14458,7 @@
     </row>
     <row r="1005">
       <c r="A1005" t="str">
-        <v>priscilaapbatista</v>
+        <v>chunco_424</v>
       </c>
       <c r="B1005">
         <v>0</v>
@@ -14472,7 +14472,7 @@
     </row>
     <row r="1006">
       <c r="A1006" t="str">
-        <v>denisalagoanobjj</v>
+        <v>fix.pec</v>
       </c>
       <c r="B1006">
         <v>0</v>
@@ -14486,7 +14486,7 @@
     </row>
     <row r="1007">
       <c r="A1007" t="str">
-        <v>shirleypalestrina6</v>
+        <v>roxostrike</v>
       </c>
       <c r="B1007">
         <v>0</v>
@@ -14500,7 +14500,7 @@
     </row>
     <row r="1008">
       <c r="A1008" t="str">
-        <v>flipebiano</v>
+        <v>josita_bjj</v>
       </c>
       <c r="B1008">
         <v>0</v>
@@ -14514,7 +14514,7 @@
     </row>
     <row r="1009">
       <c r="A1009" t="str">
-        <v>lyvia_genuina</v>
+        <v>priscilaapbatista</v>
       </c>
       <c r="B1009">
         <v>0</v>
@@ -14528,7 +14528,7 @@
     </row>
     <row r="1010">
       <c r="A1010" t="str">
-        <v>horadopower</v>
+        <v>denisalagoanobjj</v>
       </c>
       <c r="B1010">
         <v>0</v>
@@ -14542,7 +14542,7 @@
     </row>
     <row r="1011">
       <c r="A1011" t="str">
-        <v>manoel.brum</v>
+        <v>shirleypalestrina6</v>
       </c>
       <c r="B1011">
         <v>0</v>
@@ -14556,7 +14556,7 @@
     </row>
     <row r="1012">
       <c r="A1012" t="str">
-        <v>babimaciel1</v>
+        <v>flipebiano</v>
       </c>
       <c r="B1012">
         <v>0</v>
@@ -14570,7 +14570,7 @@
     </row>
     <row r="1013">
       <c r="A1013" t="str">
-        <v>ruanmiqueias</v>
+        <v>lyvia_genuina</v>
       </c>
       <c r="B1013">
         <v>0</v>
@@ -14584,7 +14584,7 @@
     </row>
     <row r="1014">
       <c r="A1014" t="str">
-        <v>delariva_belem</v>
+        <v>horadopower</v>
       </c>
       <c r="B1014">
         <v>0</v>
@@ -14598,7 +14598,7 @@
     </row>
     <row r="1015">
       <c r="A1015" t="str">
-        <v>joseochoa.mma</v>
+        <v>manoel.brum</v>
       </c>
       <c r="B1015">
         <v>0</v>
@@ -14612,7 +14612,7 @@
     </row>
     <row r="1016">
       <c r="A1016" t="str">
-        <v>reynitaoblitasbustamante</v>
+        <v>babimaciel1</v>
       </c>
       <c r="B1016">
         <v>0</v>
@@ -14626,7 +14626,7 @@
     </row>
     <row r="1017">
       <c r="A1017" t="str">
-        <v>sthefany_ochoao</v>
+        <v>ruanmiqueias</v>
       </c>
       <c r="B1017">
         <v>0</v>
@@ -14640,7 +14640,7 @@
     </row>
     <row r="1018">
       <c r="A1018" t="str">
-        <v>_matheustiberio</v>
+        <v>delariva_belem</v>
       </c>
       <c r="B1018">
         <v>0</v>
@@ -14654,7 +14654,7 @@
     </row>
     <row r="1019">
       <c r="A1019" t="str">
-        <v>gabrielsantosufc_</v>
+        <v>joseochoa.mma</v>
       </c>
       <c r="B1019">
         <v>0</v>
@@ -14668,7 +14668,7 @@
     </row>
     <row r="1020">
       <c r="A1020" t="str">
-        <v>juugxmes</v>
+        <v>reynitaoblitasbustamante</v>
       </c>
       <c r="B1020">
         <v>0</v>
@@ -14682,7 +14682,7 @@
     </row>
     <row r="1021">
       <c r="A1021" t="str">
-        <v>gabriellb.andrade</v>
+        <v>sthefany_ochoao</v>
       </c>
       <c r="B1021">
         <v>0</v>
@@ -14696,7 +14696,7 @@
     </row>
     <row r="1022">
       <c r="A1022" t="str">
-        <v>romelluistro</v>
+        <v>_matheustiberio</v>
       </c>
       <c r="B1022">
         <v>0</v>
@@ -14710,7 +14710,7 @@
     </row>
     <row r="1023">
       <c r="A1023" t="str">
-        <v>yuricapelasso</v>
+        <v>gabrielsantosufc_</v>
       </c>
       <c r="B1023">
         <v>0</v>
@@ -14724,7 +14724,7 @@
     </row>
     <row r="1024">
       <c r="A1024" t="str">
-        <v>lucasfenomeno_ufc</v>
+        <v>juugxmes</v>
       </c>
       <c r="B1024">
         <v>0</v>
@@ -14738,7 +14738,7 @@
     </row>
     <row r="1025">
       <c r="A1025" t="str">
-        <v>matheusdouradomma</v>
+        <v>gabriellb.andrade</v>
       </c>
       <c r="B1025">
         <v>0</v>
@@ -14752,7 +14752,7 @@
     </row>
     <row r="1026">
       <c r="A1026" t="str">
-        <v>lazyboy.ufc</v>
+        <v>romelluistro</v>
       </c>
       <c r="B1026">
         <v>0</v>
@@ -14766,7 +14766,7 @@
     </row>
     <row r="1027">
       <c r="A1027" t="str">
-        <v>gabriell_marcus</v>
+        <v>yuricapelasso</v>
       </c>
       <c r="B1027">
         <v>0</v>
@@ -14780,7 +14780,7 @@
     </row>
     <row r="1028">
       <c r="A1028" t="str">
-        <v>rafaelsouza7586</v>
+        <v>lucasfenomeno_ufc</v>
       </c>
       <c r="B1028">
         <v>0</v>
@@ -14794,7 +14794,7 @@
     </row>
     <row r="1029">
       <c r="A1029" t="str">
-        <v>dodge_big_johnson29</v>
+        <v>matheusdouradomma</v>
       </c>
       <c r="B1029">
         <v>0</v>
@@ -14808,7 +14808,7 @@
     </row>
     <row r="1030">
       <c r="A1030" t="str">
-        <v>land_on_martelo_308</v>
+        <v>lazyboy.ufc</v>
       </c>
       <c r="B1030">
         <v>0</v>
@@ -14822,7 +14822,7 @@
     </row>
     <row r="1031">
       <c r="A1031" t="str">
-        <v>dj__freckles</v>
+        <v>gabriell_marcus</v>
       </c>
       <c r="B1031">
         <v>0</v>
@@ -14836,7 +14836,7 @@
     </row>
     <row r="1032">
       <c r="A1032" t="str">
-        <v>regis18vieira</v>
+        <v>rafaelsouza7586</v>
       </c>
       <c r="B1032">
         <v>0</v>
@@ -14850,7 +14850,7 @@
     </row>
     <row r="1033">
       <c r="A1033" t="str">
-        <v>andy.techera.12</v>
+        <v>dodge_big_johnson29</v>
       </c>
       <c r="B1033">
         <v>0</v>
@@ -14864,7 +14864,7 @@
     </row>
     <row r="1034">
       <c r="A1034" t="str">
-        <v>celiogarcia6</v>
+        <v>land_on_martelo_308</v>
       </c>
       <c r="B1034">
         <v>0</v>
@@ -14878,7 +14878,7 @@
     </row>
     <row r="1035">
       <c r="A1035" t="str">
-        <v>luluakio</v>
+        <v>dj__freckles</v>
       </c>
       <c r="B1035">
         <v>0</v>
@@ -14892,7 +14892,7 @@
     </row>
     <row r="1036">
       <c r="A1036" t="str">
-        <v>lusoaresjj</v>
+        <v>regis18vieira</v>
       </c>
       <c r="B1036">
         <v>0</v>
@@ -14906,7 +14906,7 @@
     </row>
     <row r="1037">
       <c r="A1037" t="str">
-        <v>barreto.boxe</v>
+        <v>andy.techera.12</v>
       </c>
       <c r="B1037">
         <v>0</v>
@@ -14920,7 +14920,7 @@
     </row>
     <row r="1038">
       <c r="A1038" t="str">
-        <v>sharingan_mma</v>
+        <v>celiogarcia6</v>
       </c>
       <c r="B1038">
         <v>0</v>
@@ -14934,7 +14934,7 @@
     </row>
     <row r="1039">
       <c r="A1039" t="str">
-        <v>thaisadantas</v>
+        <v>luluakio</v>
       </c>
       <c r="B1039">
         <v>0</v>
@@ -14948,7 +14948,7 @@
     </row>
     <row r="1040">
       <c r="A1040" t="str">
-        <v>jp.mdc</v>
+        <v>lusoaresjj</v>
       </c>
       <c r="B1040">
         <v>0</v>
@@ -14962,7 +14962,7 @@
     </row>
     <row r="1041">
       <c r="A1041" t="str">
-        <v>danielbzk_</v>
+        <v>barreto.boxe</v>
       </c>
       <c r="B1041">
         <v>0</v>
@@ -14976,7 +14976,7 @@
     </row>
     <row r="1042">
       <c r="A1042" t="str">
-        <v>herbeth_indiomma</v>
+        <v>sharingan_mma</v>
       </c>
       <c r="B1042">
         <v>0</v>
@@ -14990,7 +14990,7 @@
     </row>
     <row r="1043">
       <c r="A1043" t="str">
-        <v>pulsepro.nutrition</v>
+        <v>thaisadantas</v>
       </c>
       <c r="B1043">
         <v>0</v>
@@ -15004,7 +15004,7 @@
     </row>
     <row r="1044">
       <c r="A1044" t="str">
-        <v>1210gi</v>
+        <v>jp.mdc</v>
       </c>
       <c r="B1044">
         <v>0</v>
@@ -15018,7 +15018,7 @@
     </row>
     <row r="1045">
       <c r="A1045" t="str">
-        <v>maicon_mamute_</v>
+        <v>danielbzk_</v>
       </c>
       <c r="B1045">
         <v>0</v>
@@ -15032,7 +15032,7 @@
     </row>
     <row r="1046">
       <c r="A1046" t="str">
-        <v>wildler_borriello</v>
+        <v>herbeth_indiomma</v>
       </c>
       <c r="B1046">
         <v>0</v>
@@ -15046,7 +15046,7 @@
     </row>
     <row r="1047">
       <c r="A1047" t="str">
-        <v>esmeraldasales</v>
+        <v>pulsepro.nutrition</v>
       </c>
       <c r="B1047">
         <v>0</v>
@@ -15060,7 +15060,7 @@
     </row>
     <row r="1048">
       <c r="A1048" t="str">
-        <v>raffaelcerqueira_ufc</v>
+        <v>1210gi</v>
       </c>
       <c r="B1048">
         <v>0</v>
@@ -15074,7 +15074,7 @@
     </row>
     <row r="1049">
       <c r="A1049" t="str">
-        <v>jhonnydavid</v>
+        <v>maicon_mamute_</v>
       </c>
       <c r="B1049">
         <v>0</v>
@@ -15088,7 +15088,7 @@
     </row>
     <row r="1050">
       <c r="A1050" t="str">
-        <v>dannielvieira</v>
+        <v>wildler_borriello</v>
       </c>
       <c r="B1050">
         <v>0</v>
@@ -15102,7 +15102,7 @@
     </row>
     <row r="1051">
       <c r="A1051" t="str">
-        <v>guilherme.leandromma</v>
+        <v>esmeraldasales</v>
       </c>
       <c r="B1051">
         <v>0</v>
@@ -15116,7 +15116,7 @@
     </row>
     <row r="1052">
       <c r="A1052" t="str">
-        <v>siinho</v>
+        <v>raffaelcerqueira_ufc</v>
       </c>
       <c r="B1052">
         <v>0</v>
@@ -15130,7 +15130,7 @@
     </row>
     <row r="1053">
       <c r="A1053" t="str">
-        <v>rnn.neves</v>
+        <v>jhonnydavid</v>
       </c>
       <c r="B1053">
         <v>0</v>
@@ -15144,7 +15144,7 @@
     </row>
     <row r="1054">
       <c r="A1054" t="str">
-        <v>sulafotografia</v>
+        <v>dannielvieira</v>
       </c>
       <c r="B1054">
         <v>0</v>
@@ -15158,7 +15158,7 @@
     </row>
     <row r="1055">
       <c r="A1055" t="str">
-        <v>luisfendt</v>
+        <v>guilherme.leandromma</v>
       </c>
       <c r="B1055">
         <v>0</v>
@@ -15172,7 +15172,7 @@
     </row>
     <row r="1056">
       <c r="A1056" t="str">
-        <v>cipobr</v>
+        <v>siinho</v>
       </c>
       <c r="B1056">
         <v>0</v>
@@ -15186,7 +15186,7 @@
     </row>
     <row r="1057">
       <c r="A1057" t="str">
-        <v>contadoraison</v>
+        <v>rnn.neves</v>
       </c>
       <c r="B1057">
         <v>0</v>
@@ -15200,7 +15200,7 @@
     </row>
     <row r="1058">
       <c r="A1058" t="str">
-        <v>guerreira.doasfalto</v>
+        <v>sulafotografia</v>
       </c>
       <c r="B1058">
         <v>0</v>
@@ -15214,7 +15214,7 @@
     </row>
     <row r="1059">
       <c r="A1059" t="str">
-        <v>jlheitor</v>
+        <v>luisfendt</v>
       </c>
       <c r="B1059">
         <v>0</v>
@@ -15228,7 +15228,7 @@
     </row>
     <row r="1060">
       <c r="A1060" t="str">
-        <v>nostalgia_npt</v>
+        <v>cipobr</v>
       </c>
       <c r="B1060">
         <v>0</v>
@@ -15242,7 +15242,7 @@
     </row>
     <row r="1061">
       <c r="A1061" t="str">
-        <v>rapaduracapoeira</v>
+        <v>contadoraison</v>
       </c>
       <c r="B1061">
         <v>0</v>
@@ -15256,7 +15256,7 @@
     </row>
     <row r="1062">
       <c r="A1062" t="str">
-        <v>cdmurilorossi</v>
+        <v>guerreira.doasfalto</v>
       </c>
       <c r="B1062">
         <v>0</v>
@@ -15270,7 +15270,7 @@
     </row>
     <row r="1063">
       <c r="A1063" t="str">
-        <v>marciosil7</v>
+        <v>jlheitor</v>
       </c>
       <c r="B1063">
         <v>0</v>
@@ -15284,7 +15284,7 @@
     </row>
     <row r="1064">
       <c r="A1064" t="str">
-        <v>s.rodrigobernardoda</v>
+        <v>nostalgia_npt</v>
       </c>
       <c r="B1064">
         <v>0</v>
@@ -15298,7 +15298,7 @@
     </row>
     <row r="1065">
       <c r="A1065" t="str">
-        <v>fe.souza89</v>
+        <v>rapaduracapoeira</v>
       </c>
       <c r="B1065">
         <v>0</v>
@@ -15312,7 +15312,7 @@
     </row>
     <row r="1066">
       <c r="A1066" t="str">
-        <v>yuri.t.bechelli</v>
+        <v>cdmurilorossi</v>
       </c>
       <c r="B1066">
         <v>0</v>
@@ -15326,7 +15326,7 @@
     </row>
     <row r="1067">
       <c r="A1067" t="str">
-        <v>wellington_silva_1995</v>
+        <v>marciosil7</v>
       </c>
       <c r="B1067">
         <v>0</v>
@@ -15340,7 +15340,7 @@
     </row>
     <row r="1068">
       <c r="A1068" t="str">
-        <v>ricardolopes4921</v>
+        <v>s.rodrigobernardoda</v>
       </c>
       <c r="B1068">
         <v>0</v>
@@ -15354,7 +15354,7 @@
     </row>
     <row r="1069">
       <c r="A1069" t="str">
-        <v>nicollebertolinie</v>
+        <v>fe.souza89</v>
       </c>
       <c r="B1069">
         <v>0</v>
@@ -15368,7 +15368,7 @@
     </row>
     <row r="1070">
       <c r="A1070" t="str">
-        <v>leticia_araujo447</v>
+        <v>yuri.t.bechelli</v>
       </c>
       <c r="B1070">
         <v>0</v>
@@ -15382,7 +15382,7 @@
     </row>
     <row r="1071">
       <c r="A1071" t="str">
-        <v>__paulaprada__</v>
+        <v>wellington_silva_1995</v>
       </c>
       <c r="B1071">
         <v>0</v>
@@ -15396,7 +15396,7 @@
     </row>
     <row r="1072">
       <c r="A1072" t="str">
-        <v>alexandresagat.oficial</v>
+        <v>ricardolopes4921</v>
       </c>
       <c r="B1072">
         <v>0</v>
@@ -15410,7 +15410,7 @@
     </row>
     <row r="1073">
       <c r="A1073" t="str">
-        <v>annamarya_silveira</v>
+        <v>nicollebertolinie</v>
       </c>
       <c r="B1073">
         <v>0</v>
@@ -15424,7 +15424,7 @@
     </row>
     <row r="1074">
       <c r="A1074" t="str">
-        <v>sousamaevia</v>
+        <v>leticia_araujo447</v>
       </c>
       <c r="B1074">
         <v>0</v>
@@ -15438,7 +15438,7 @@
     </row>
     <row r="1075">
       <c r="A1075" t="str">
-        <v>eneido_neto</v>
+        <v>__paulaprada__</v>
       </c>
       <c r="B1075">
         <v>0</v>
@@ -15452,7 +15452,7 @@
     </row>
     <row r="1076">
       <c r="A1076" t="str">
-        <v>genillsson_177</v>
+        <v>alexandresagat.oficial</v>
       </c>
       <c r="B1076">
         <v>0</v>
@@ -15466,7 +15466,7 @@
     </row>
     <row r="1077">
       <c r="A1077" t="str">
-        <v>alesiqueira_personal</v>
+        <v>annamarya_silveira</v>
       </c>
       <c r="B1077">
         <v>0</v>
@@ -15480,7 +15480,7 @@
     </row>
     <row r="1078">
       <c r="A1078" t="str">
-        <v>anaclaudialc73</v>
+        <v>sousamaevia</v>
       </c>
       <c r="B1078">
         <v>0</v>
@@ -15494,7 +15494,7 @@
     </row>
     <row r="1079">
       <c r="A1079" t="str">
-        <v>fernandohf32</v>
+        <v>eneido_neto</v>
       </c>
       <c r="B1079">
         <v>0</v>
@@ -15508,7 +15508,7 @@
     </row>
     <row r="1080">
       <c r="A1080" t="str">
-        <v>gleydeolyveeira</v>
+        <v>genillsson_177</v>
       </c>
       <c r="B1080">
         <v>0</v>
@@ -15522,7 +15522,7 @@
     </row>
     <row r="1081">
       <c r="A1081" t="str">
-        <v>rbueno81</v>
+        <v>alesiqueira_personal</v>
       </c>
       <c r="B1081">
         <v>0</v>
@@ -15536,7 +15536,7 @@
     </row>
     <row r="1082">
       <c r="A1082" t="str">
-        <v>rafamakita</v>
+        <v>anaclaudialc73</v>
       </c>
       <c r="B1082">
         <v>0</v>
@@ -15550,7 +15550,7 @@
     </row>
     <row r="1083">
       <c r="A1083" t="str">
-        <v>biia_sousah</v>
+        <v>fernandohf32</v>
       </c>
       <c r="B1083">
         <v>0</v>
@@ -15564,7 +15564,7 @@
     </row>
     <row r="1084">
       <c r="A1084" t="str">
-        <v>ronygoto</v>
+        <v>gleydeolyveeira</v>
       </c>
       <c r="B1084">
         <v>0</v>
@@ -15578,7 +15578,7 @@
     </row>
     <row r="1085">
       <c r="A1085" t="str">
-        <v>igorpatrao</v>
+        <v>rbueno81</v>
       </c>
       <c r="B1085">
         <v>0</v>
@@ -15592,7 +15592,7 @@
     </row>
     <row r="1086">
       <c r="A1086" t="str">
-        <v>fideles8080</v>
+        <v>rafamakita</v>
       </c>
       <c r="B1086">
         <v>0</v>
@@ -15606,7 +15606,7 @@
     </row>
     <row r="1087">
       <c r="A1087" t="str">
-        <v>nadiabarakkat</v>
+        <v>biia_sousah</v>
       </c>
       <c r="B1087">
         <v>0</v>
@@ -15620,7 +15620,7 @@
     </row>
     <row r="1088">
       <c r="A1088" t="str">
-        <v>nofight.nohistory</v>
+        <v>ronygoto</v>
       </c>
       <c r="B1088">
         <v>0</v>
@@ -15634,28 +15634,112 @@
     </row>
     <row r="1089">
       <c r="A1089" t="str">
+        <v>igorpatrao</v>
+      </c>
+      <c r="B1089">
+        <v>0</v>
+      </c>
+      <c r="C1089">
+        <v>1</v>
+      </c>
+      <c r="D1089">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="str">
+        <v>fideles8080</v>
+      </c>
+      <c r="B1090">
+        <v>0</v>
+      </c>
+      <c r="C1090">
+        <v>1</v>
+      </c>
+      <c r="D1090">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="str">
+        <v>nadiabarakkat</v>
+      </c>
+      <c r="B1091">
+        <v>0</v>
+      </c>
+      <c r="C1091">
+        <v>1</v>
+      </c>
+      <c r="D1091">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="str">
+        <v>nofight.nohistory</v>
+      </c>
+      <c r="B1092">
+        <v>0</v>
+      </c>
+      <c r="C1092">
+        <v>1</v>
+      </c>
+      <c r="D1092">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="str">
         <v>andredida</v>
       </c>
-      <c r="B1089">
-        <v>0</v>
-      </c>
-      <c r="C1089">
-        <v>1</v>
-      </c>
-      <c r="D1089">
+      <c r="B1093">
+        <v>0</v>
+      </c>
+      <c r="C1093">
+        <v>1</v>
+      </c>
+      <c r="D1093">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="str">
+        <v>combatcliphubbrasil</v>
+      </c>
+      <c r="B1094">
+        <v>0</v>
+      </c>
+      <c r="C1094">
+        <v>1</v>
+      </c>
+      <c r="D1094">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="str">
+        <v>polastri_ufc</v>
+      </c>
+      <c r="B1095">
+        <v>0</v>
+      </c>
+      <c r="C1095">
+        <v>1</v>
+      </c>
+      <c r="D1095">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D1089"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1095"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D94"/>
+  <dimension ref="A1:D104"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -15676,10 +15760,10 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>16</v>
@@ -15701,7 +15785,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>leonardomesquitamma</v>
+        <v>masonharper_mma</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -15710,74 +15794,74 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>prochapolicarpo</v>
+        <v>leonardomesquitamma</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>_franklinxavier</v>
+        <v>prochapolicarpo</v>
       </c>
       <c r="B6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>luizferrer_br</v>
+        <v>_franklinxavier</v>
       </c>
       <c r="B7">
         <v>2</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>combintel</v>
+        <v>johnmma9</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>masonharper_mma</v>
+        <v>sirleneferreiradiasdias</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -15785,21 +15869,21 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>tiwifenixmma</v>
+        <v>luizferrer_br</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>gustavo_brasil09</v>
+        <v>combintel</v>
       </c>
       <c r="B11">
         <v>1</v>
@@ -15813,7 +15897,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>fabiocesar_1997</v>
+        <v>tiwifenixmma</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -15827,7 +15911,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>josuemoita1205</v>
+        <v>gustavo_brasil09</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -15841,7 +15925,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>milton_pitbull</v>
+        <v>fabiocesar_1997</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -15855,7 +15939,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>enzo.gsilva_</v>
+        <v>josuemoita1205</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -15869,7 +15953,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>raffaoito4</v>
+        <v>milton_pitbull</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -15883,7 +15967,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>rl_figo</v>
+        <v>enzo.gsilva_</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -15897,7 +15981,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>ultraperegrinospelomundo</v>
+        <v>raffaoito4</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -15911,7 +15995,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>claudio_marchese_7</v>
+        <v>rl_figo</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -15925,27 +16009,27 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>eolucasrosa</v>
+        <v>ultraperegrinospelomundo</v>
       </c>
       <c r="B20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>kelly_ottoni</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C21">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -15953,49 +16037,49 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>mvp_lutas</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C22">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D22">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>alexandroscorreia</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>lucifit50</v>
+        <v>mvp_lutas</v>
       </c>
       <c r="B24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>martinscdione</v>
+        <v>alexandroscorreia</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -16009,7 +16093,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>gustavotoi</v>
+        <v>lucifit50</v>
       </c>
       <c r="B26">
         <v>1</v>
@@ -16023,7 +16107,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>erivaldosilva3333</v>
+        <v>martinscdione</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -16037,7 +16121,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>marcos_r_s_</v>
+        <v>gustavotoi</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -16051,7 +16135,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>biazon87</v>
+        <v>erivaldosilva3333</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -16065,7 +16149,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>moys158</v>
+        <v>marcos_r_s_</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -16079,7 +16163,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>viviane_moota</v>
+        <v>biazon87</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -16093,7 +16177,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>ra.imundo8575</v>
+        <v>moys158</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -16107,7 +16191,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>caio.lazzuri</v>
+        <v>viviane_moota</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -16121,7 +16205,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>sambagabrieloficial</v>
+        <v>ra.imundo8575</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -16135,7 +16219,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>rafaella_olliveira08</v>
+        <v>caio.lazzuri</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -16149,7 +16233,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>antoniomarcos84</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -16163,7 +16247,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>hipolito.netoo</v>
+        <v>rafaella_olliveira08</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -16177,7 +16261,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>febcm</v>
+        <v>antoniomarcos84</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -16191,7 +16275,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>gabriel_angello_</v>
+        <v>hipolito.netoo</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -16205,7 +16289,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>dronearcariri</v>
+        <v>febcm</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -16219,7 +16303,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>roncy_068</v>
+        <v>gabriel_angello_</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -16233,7 +16317,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>mmapalpitex</v>
+        <v>dronearcariri</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -16247,7 +16331,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>gustavo_vivancos</v>
+        <v>roncy_068</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -16261,7 +16345,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>jo.aopedro748</v>
+        <v>mmapalpitex</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -16275,7 +16359,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>marcoscesarbodo</v>
+        <v>gustavo_vivancos</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -16289,7 +16373,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>mardonio9549</v>
+        <v>jo.aopedro748</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -16303,7 +16387,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>driigallinucci</v>
+        <v>marcoscesarbodo</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -16317,7 +16401,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>araujodiana1231</v>
+        <v>mardonio9549</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -16331,7 +16415,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>mr.disciplina</v>
+        <v>driigallinucci</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -16345,7 +16429,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>jvxz______</v>
+        <v>araujodiana1231</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -16359,7 +16443,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>carlos_hm_iglesias</v>
+        <v>mr.disciplina</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -16373,7 +16457,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>claudiaottoni2025</v>
+        <v>jvxz______</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -16387,7 +16471,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>carlos_hm_iglesias</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -16401,7 +16485,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>thiagoauper</v>
+        <v>claudiaottoni2025</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -16415,7 +16499,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>pedromadeira.s</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -16429,7 +16513,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>pro_mmabetting</v>
+        <v>thiagoauper</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -16443,7 +16527,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ninjatheorist</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -16457,105 +16541,105 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>aj_mma_</v>
+        <v>pro_mmabetting</v>
       </c>
       <c r="B58">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D58">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>johnmma9</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>blogfabiocosta</v>
+        <v>marcelonascimentojiujitsu</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C60">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D60">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>leo_sousa_cabeleleiro</v>
+        <v>jairinhovibedeejay</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D61">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>markiim_guerreiro</v>
+        <v>vanessa25harreson</v>
       </c>
       <c r="B62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C62">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>god.motivacao</v>
+        <v>eu_isasantana1</v>
       </c>
       <c r="B63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>fe.souza89</v>
+        <v>aj_mma_</v>
       </c>
       <c r="B64">
         <v>0</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D64">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>sirleneferreiradiasdias</v>
+        <v>blogfabiocosta</v>
       </c>
       <c r="B65">
         <v>0</v>
@@ -16564,12 +16648,12 @@
         <v>1</v>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>yuri.t.bechelli</v>
+        <v>leo_sousa_cabeleleiro</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -16578,12 +16662,12 @@
         <v>1</v>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>wellington_silva_1995</v>
+        <v>markiim_guerreiro</v>
       </c>
       <c r="B67">
         <v>0</v>
@@ -16592,12 +16676,12 @@
         <v>1</v>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ricardolopes4921</v>
+        <v>god.motivacao</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -16606,12 +16690,12 @@
         <v>1</v>
       </c>
       <c r="D68">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>nicollebertolinie</v>
+        <v>fe.souza89</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -16625,7 +16709,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>leticia_araujo447</v>
+        <v>yuri.t.bechelli</v>
       </c>
       <c r="B70">
         <v>0</v>
@@ -16639,7 +16723,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>__paulaprada__</v>
+        <v>wellington_silva_1995</v>
       </c>
       <c r="B71">
         <v>0</v>
@@ -16653,7 +16737,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>alexandresagat.oficial</v>
+        <v>ricardolopes4921</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -16667,7 +16751,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>annamarya_silveira</v>
+        <v>nicollebertolinie</v>
       </c>
       <c r="B73">
         <v>0</v>
@@ -16681,7 +16765,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>sousamaevia</v>
+        <v>leticia_araujo447</v>
       </c>
       <c r="B74">
         <v>0</v>
@@ -16695,7 +16779,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>eneido_neto</v>
+        <v>__paulaprada__</v>
       </c>
       <c r="B75">
         <v>0</v>
@@ -16709,7 +16793,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>genillsson_177</v>
+        <v>alexandresagat.oficial</v>
       </c>
       <c r="B76">
         <v>0</v>
@@ -16723,7 +16807,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>alesiqueira_personal</v>
+        <v>annamarya_silveira</v>
       </c>
       <c r="B77">
         <v>0</v>
@@ -16737,7 +16821,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>anaclaudialc73</v>
+        <v>sousamaevia</v>
       </c>
       <c r="B78">
         <v>0</v>
@@ -16751,7 +16835,7 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>fernandohf32</v>
+        <v>eneido_neto</v>
       </c>
       <c r="B79">
         <v>0</v>
@@ -16765,7 +16849,7 @@
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>gleydeolyveeira</v>
+        <v>genillsson_177</v>
       </c>
       <c r="B80">
         <v>0</v>
@@ -16779,7 +16863,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>rbueno81</v>
+        <v>alesiqueira_personal</v>
       </c>
       <c r="B81">
         <v>0</v>
@@ -16793,7 +16877,7 @@
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>rafamakita</v>
+        <v>anaclaudialc73</v>
       </c>
       <c r="B82">
         <v>0</v>
@@ -16807,7 +16891,7 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>biia_sousah</v>
+        <v>fernandohf32</v>
       </c>
       <c r="B83">
         <v>0</v>
@@ -16821,7 +16905,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>ronygoto</v>
+        <v>gleydeolyveeira</v>
       </c>
       <c r="B84">
         <v>0</v>
@@ -16835,7 +16919,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>igorpatrao</v>
+        <v>rbueno81</v>
       </c>
       <c r="B85">
         <v>0</v>
@@ -16849,7 +16933,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>fideles8080</v>
+        <v>rafamakita</v>
       </c>
       <c r="B86">
         <v>0</v>
@@ -16863,7 +16947,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>nadiabarakkat</v>
+        <v>biia_sousah</v>
       </c>
       <c r="B87">
         <v>0</v>
@@ -16877,7 +16961,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>washington_cassisno</v>
+        <v>ronygoto</v>
       </c>
       <c r="B88">
         <v>0</v>
@@ -16891,7 +16975,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>marcelogabrielmma</v>
+        <v>igorpatrao</v>
       </c>
       <c r="B89">
         <v>0</v>
@@ -16905,7 +16989,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>diegopaivajj</v>
+        <v>fideles8080</v>
       </c>
       <c r="B90">
         <v>0</v>
@@ -16919,7 +17003,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>aida_dos_sonhos</v>
+        <v>nadiabarakkat</v>
       </c>
       <c r="B91">
         <v>0</v>
@@ -16933,7 +17017,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>_oliveira09_</v>
+        <v>washington_cassisno</v>
       </c>
       <c r="B92">
         <v>0</v>
@@ -16947,7 +17031,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>nofight.nohistory</v>
+        <v>marcelogabrielmma</v>
       </c>
       <c r="B93">
         <v>0</v>
@@ -16961,21 +17045,161 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
+        <v>diegopaivajj</v>
+      </c>
+      <c r="B94">
+        <v>0</v>
+      </c>
+      <c r="C94">
+        <v>1</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="str">
+        <v>aida_dos_sonhos</v>
+      </c>
+      <c r="B95">
+        <v>0</v>
+      </c>
+      <c r="C95">
+        <v>1</v>
+      </c>
+      <c r="D95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="str">
+        <v>_oliveira09_</v>
+      </c>
+      <c r="B96">
+        <v>0</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="str">
+        <v>nofight.nohistory</v>
+      </c>
+      <c r="B97">
+        <v>0</v>
+      </c>
+      <c r="C97">
+        <v>1</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="str">
         <v>andredida</v>
       </c>
-      <c r="B94">
-        <v>0</v>
-      </c>
-      <c r="C94">
-        <v>1</v>
-      </c>
-      <c r="D94">
+      <c r="B98">
+        <v>0</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>combatcliphubbrasil</v>
+      </c>
+      <c r="B99">
+        <v>0</v>
+      </c>
+      <c r="C99">
+        <v>1</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>enzocardoso.bjj</v>
+      </c>
+      <c r="B100">
+        <v>0</v>
+      </c>
+      <c r="C100">
+        <v>1</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>pg_grappling</v>
+      </c>
+      <c r="B101">
+        <v>0</v>
+      </c>
+      <c r="C101">
+        <v>1</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>polastri_ufc</v>
+      </c>
+      <c r="B102">
+        <v>0</v>
+      </c>
+      <c r="C102">
+        <v>1</v>
+      </c>
+      <c r="D102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>malu832757</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+      <c r="C103">
+        <v>1</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>peacegrappler_podcast</v>
+      </c>
+      <c r="B104">
+        <v>0</v>
+      </c>
+      <c r="C104">
+        <v>1</v>
+      </c>
+      <c r="D104">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D94"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D104"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Engagement Rankings 2026-08.xlsx
+++ b/Engagement Rankings 2026-08.xlsx
@@ -475,13 +475,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B6">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="C6">
         <v>18</v>
       </c>
       <c r="D6">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="7">
@@ -1080,10 +1080,10 @@
         <v>26</v>
       </c>
       <c r="C49">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D49">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50">
@@ -1161,7 +1161,7 @@
         <v>ninjatheorist</v>
       </c>
       <c r="B55">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -1984,44 +1984,44 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>badboykillermma</v>
+        <v>aj_mma_</v>
       </c>
       <c r="B114">
+        <v>5</v>
+      </c>
+      <c r="C114">
         <v>6</v>
       </c>
-      <c r="C114">
-        <v>1</v>
-      </c>
       <c r="D114">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>psi_pedro.madeira</v>
+        <v>badboykillermma</v>
       </c>
       <c r="B115">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D115">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>aj_mma_</v>
+        <v>psi_pedro.madeira</v>
       </c>
       <c r="B116">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C116">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -2432,41 +2432,41 @@
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>sueli_ferreira48</v>
+        <v>mvp_lutas</v>
       </c>
       <c r="B146">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C146">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D146">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>elienelucindo_oficial</v>
+        <v>sueli_ferreira48</v>
       </c>
       <c r="B147">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>emersonriosmma</v>
+        <v>elienelucindo_oficial</v>
       </c>
       <c r="B148">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C148">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D148">
         <v>0</v>
@@ -2474,13 +2474,13 @@
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>edinalvajanjacomo</v>
+        <v>emersonriosmma</v>
       </c>
       <c r="B149">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C149">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D149">
         <v>0</v>
@@ -2488,13 +2488,13 @@
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>combatclubsp</v>
+        <v>edinalvajanjacomo</v>
       </c>
       <c r="B150">
         <v>6</v>
       </c>
       <c r="C150">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D150">
         <v>0</v>
@@ -2502,58 +2502,58 @@
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>eric.shpritz</v>
+        <v>combatclubsp</v>
       </c>
       <c r="B151">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C151">
         <v>2</v>
       </c>
       <c r="D151">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>edaregiao</v>
+        <v>eric.shpritz</v>
       </c>
       <c r="B152">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C152">
         <v>2</v>
       </c>
       <c r="D152">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>f.ostini</v>
+        <v>edaregiao</v>
       </c>
       <c r="B153">
         <v>4</v>
       </c>
       <c r="C153">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D153">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>mvp_lutas</v>
+        <v>f.ostini</v>
       </c>
       <c r="B154">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C154">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D154">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -15760,13 +15760,13 @@
         <v>quemuel_ottoni</v>
       </c>
       <c r="B2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -15897,21 +15897,21 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>tiwifenixmma</v>
+        <v>kelly_ottoni</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>gustavo_brasil09</v>
+        <v>tiwifenixmma</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -15925,7 +15925,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>fabiocesar_1997</v>
+        <v>gustavo_brasil09</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -15939,7 +15939,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>josuemoita1205</v>
+        <v>fabiocesar_1997</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -15953,7 +15953,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>milton_pitbull</v>
+        <v>josuemoita1205</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -15967,7 +15967,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>enzo.gsilva_</v>
+        <v>milton_pitbull</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -15981,7 +15981,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>raffaoito4</v>
+        <v>enzo.gsilva_</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -15995,7 +15995,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>rl_figo</v>
+        <v>raffaoito4</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -16009,7 +16009,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>ultraperegrinospelomundo</v>
+        <v>rl_figo</v>
       </c>
       <c r="B20">
         <v>1</v>
@@ -16023,7 +16023,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>claudio_marchese_7</v>
+        <v>ultraperegrinospelomundo</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -16037,27 +16037,27 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>eolucasrosa</v>
+        <v>mvp_lutas</v>
       </c>
       <c r="B22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>kelly_ottoni</v>
+        <v>claudio_marchese_7</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -16065,24 +16065,24 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>mvp_lutas</v>
+        <v>eolucasrosa</v>
       </c>
       <c r="B24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C24">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>alexandroscorreia</v>
+        <v>ninjatheorist</v>
       </c>
       <c r="B25">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C25">
         <v>0</v>
@@ -16093,21 +16093,21 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>lucifit50</v>
+        <v>aj_mma_</v>
       </c>
       <c r="B26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>martinscdione</v>
+        <v>alexandroscorreia</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -16121,7 +16121,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>gustavotoi</v>
+        <v>lucifit50</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -16135,7 +16135,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>erivaldosilva3333</v>
+        <v>martinscdione</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -16149,7 +16149,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>marcos_r_s_</v>
+        <v>gustavotoi</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -16163,7 +16163,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>biazon87</v>
+        <v>erivaldosilva3333</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -16177,7 +16177,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>moys158</v>
+        <v>marcos_r_s_</v>
       </c>
       <c r="B32">
         <v>1</v>
@@ -16191,7 +16191,7 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>viviane_moota</v>
+        <v>biazon87</v>
       </c>
       <c r="B33">
         <v>1</v>
@@ -16205,7 +16205,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ra.imundo8575</v>
+        <v>moys158</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -16219,7 +16219,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>caio.lazzuri</v>
+        <v>viviane_moota</v>
       </c>
       <c r="B35">
         <v>1</v>
@@ -16233,7 +16233,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>sambagabrieloficial</v>
+        <v>ra.imundo8575</v>
       </c>
       <c r="B36">
         <v>1</v>
@@ -16247,7 +16247,7 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>rafaella_olliveira08</v>
+        <v>caio.lazzuri</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -16261,7 +16261,7 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>antoniomarcos84</v>
+        <v>sambagabrieloficial</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -16275,7 +16275,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>hipolito.netoo</v>
+        <v>rafaella_olliveira08</v>
       </c>
       <c r="B39">
         <v>1</v>
@@ -16289,7 +16289,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>febcm</v>
+        <v>antoniomarcos84</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -16303,7 +16303,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>gabriel_angello_</v>
+        <v>hipolito.netoo</v>
       </c>
       <c r="B41">
         <v>1</v>
@@ -16317,7 +16317,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>dronearcariri</v>
+        <v>febcm</v>
       </c>
       <c r="B42">
         <v>1</v>
@@ -16331,7 +16331,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>roncy_068</v>
+        <v>gabriel_angello_</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -16345,7 +16345,7 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>mmapalpitex</v>
+        <v>dronearcariri</v>
       </c>
       <c r="B44">
         <v>1</v>
@@ -16359,7 +16359,7 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>gustavo_vivancos</v>
+        <v>roncy_068</v>
       </c>
       <c r="B45">
         <v>1</v>
@@ -16373,7 +16373,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>jo.aopedro748</v>
+        <v>mmapalpitex</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -16387,7 +16387,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>marcoscesarbodo</v>
+        <v>gustavo_vivancos</v>
       </c>
       <c r="B47">
         <v>1</v>
@@ -16401,7 +16401,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>mardonio9549</v>
+        <v>jo.aopedro748</v>
       </c>
       <c r="B48">
         <v>1</v>
@@ -16415,7 +16415,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>driigallinucci</v>
+        <v>marcoscesarbodo</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -16429,7 +16429,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>araujodiana1231</v>
+        <v>mardonio9549</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -16443,7 +16443,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>mr.disciplina</v>
+        <v>driigallinucci</v>
       </c>
       <c r="B51">
         <v>1</v>
@@ -16457,7 +16457,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>jvxz______</v>
+        <v>araujodiana1231</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -16471,7 +16471,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>carlos_hm_iglesias</v>
+        <v>mr.disciplina</v>
       </c>
       <c r="B53">
         <v>1</v>
@@ -16485,7 +16485,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>claudiaottoni2025</v>
+        <v>jvxz______</v>
       </c>
       <c r="B54">
         <v>1</v>
@@ -16499,7 +16499,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>danielcarmonaconsultor</v>
+        <v>carlos_hm_iglesias</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -16513,7 +16513,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>thiagoauper</v>
+        <v>claudiaottoni2025</v>
       </c>
       <c r="B56">
         <v>1</v>
@@ -16527,7 +16527,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>pedromadeira.s</v>
+        <v>danielcarmonaconsultor</v>
       </c>
       <c r="B57">
         <v>1</v>
@@ -16541,7 +16541,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>pro_mmabetting</v>
+        <v>thiagoauper</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -16555,7 +16555,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ninjatheorist</v>
+        <v>pedromadeira.s</v>
       </c>
       <c r="B59">
         <v>1</v>
@@ -16569,7 +16569,7 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>marcelonascimentojiujitsu</v>
+        <v>pro_mmabetting</v>
       </c>
       <c r="B60">
         <v>1</v>
@@ -16583,7 +16583,7 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>jairinhovibedeejay</v>
+        <v>marcelonascimentojiujitsu</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -16597,7 +16597,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>vanessa25harreson</v>
+        <v>jairinhovibedeejay</v>
       </c>
       <c r="B62">
         <v>1</v>
@@ -16611,7 +16611,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>eu_isasantana1</v>
+        <v>vanessa25harreson</v>
       </c>
       <c r="B63">
         <v>1</v>
@@ -16625,16 +16625,16 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>aj_mma_</v>
+        <v>eu_isasantana1</v>
       </c>
       <c r="B64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C64">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D64">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
